--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE155"/>
+  <dimension ref="A1:AE153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49930-2024</t>
+          <t>A 74306-2021</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45597</v>
+        <v>44559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -727,45 +727,381 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>16.6</v>
+        <v>14.6</v>
       </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
         <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
       </c>
       <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Dvärglin
+Kösa
+Åkerrödtoppa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 74306-2021 artfynd.xlsx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 74306-2021 karta.png", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 74306-2021 georefererad karta.tif", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 74306-2021 FSC-klagomål.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 74306-2021 FSC-klagomål mail.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 74306-2021 tillsynsbegäran.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 74306-2021 tillsynsbegäran mail.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 14805-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
         <v>6</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönsångare
+Kambräken
+Purpurmylia</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 65099-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45288</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Blockskapania
+Knärot
+Grov fjädermossa
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 49930-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Svart trolldruva
@@ -773,368 +1109,32 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 14805-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>6</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönsångare
-Kambräken
-Purpurmylia</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 74306-2021</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44559</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>4</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Dvärglin
-Kösa
-Åkerrödtoppa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 74306-2021 artfynd.xlsx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 74306-2021 karta.png", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 74306-2021 georefererad karta.tif", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 74306-2021 FSC-klagomål.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 74306-2021 FSC-klagomål mail.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 74306-2021 tillsynsbegäran.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 74306-2021 tillsynsbegäran mail.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 65099-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45288</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Blockskapania
-Knärot
-Grov fjädermossa
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
         <v/>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
         <v>44546</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45336</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1663-2024</t>
+          <t>A 63419-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45306</v>
+        <v>45274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1432,156 +1432,156 @@
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Björktrast
+Rödvingetrast
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 1663-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45306</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Blåbär
 Sälg
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 1663-2024 artfynd.xlsx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 1663-2024 karta.png", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 1663-2024 georefererad karta.tif", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 1663-2024 FSC-klagomål.docx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 1663-2024 FSC-klagomål mail.docx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 1663-2024 tillsynsbegäran.docx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 1663-2024 tillsynsbegäran mail.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 63419-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45274</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Björktrast
-Rödvingetrast
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13220-2024</t>
+          <t>A 56035-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1591,14 +1591,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45386</v>
+        <v>45973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>15.9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1644,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1655,42 +1655,42 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 24618-2024</t>
+          <t>A 40270-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45460</v>
+        <v>45554</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1732,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1744,10 +1744,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1756,46 +1756,50 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 771-2023</t>
+          <t>A 12722-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1809,10 +1813,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44931</v>
+        <v>46091</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1825,7 +1829,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1837,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1849,10 +1853,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1865,46 +1869,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5634-2025</t>
+          <t>A 6986-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1918,10 +1922,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45693</v>
+        <v>45343</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1938,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1946,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1958,62 +1962,58 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 12722-2026</t>
+          <t>A 49047-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46091</v>
+        <v>45937</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2043,19 +2043,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2083,46 +2083,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
-        <v/>
-      </c>
-      <c r="Z15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 49047-2025</t>
+          <t>A 23921-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2136,10 +2132,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45937</v>
+        <v>46167</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,16 +2148,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2176,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2192,42 +2188,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 56035-2025</t>
+          <t>A 31028-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2237,14 +2233,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45973</v>
+        <v>46213</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2257,19 +2253,19 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>15.9</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2281,62 +2277,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
-        <v/>
-      </c>
-      <c r="Z17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 5617-2024</t>
+          <t>A 41056-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2350,10 +2342,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45334</v>
+        <v>45898</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2366,19 +2358,19 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2390,10 +2382,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2402,50 +2394,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
-        <v/>
-      </c>
-      <c r="Z18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 44233-2023</t>
+          <t>A 771-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2459,10 +2447,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45183</v>
+        <v>44931</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2475,7 +2463,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2487,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2499,10 +2487,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2515,46 +2503,46 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
-        <v/>
-      </c>
-      <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6986-2024</t>
+          <t>A 13220-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2568,10 +2556,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45343</v>
+        <v>45386</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2584,7 +2572,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2596,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2608,58 +2596,62 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20086-2023</t>
+          <t>A 24618-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2673,10 +2665,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45054</v>
+        <v>45460</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2689,7 +2681,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>9.5</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2701,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2713,10 +2705,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2725,50 +2717,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
-        <v/>
-      </c>
-      <c r="Z21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23921-2026</t>
+          <t>A 20709-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2782,10 +2770,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46167</v>
+        <v>45058</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2798,20 +2786,20 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -2822,58 +2810,62 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
+        <v/>
+      </c>
+      <c r="Z22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31028-2026</t>
+          <t>A 5617-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2887,10 +2879,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46213</v>
+        <v>45334</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2903,20 +2895,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -2927,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2939,46 +2931,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
+        <v/>
+      </c>
+      <c r="Z23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20709-2023</t>
+          <t>A 44233-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2992,10 +2988,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45058</v>
+        <v>45183</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3008,7 +3004,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3041,10 +3037,10 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
@@ -3052,42 +3048,42 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41056-2025</t>
+          <t>A 5634-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3101,10 +3097,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45898</v>
+        <v>45693</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3117,20 +3113,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3141,58 +3137,62 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 40270-2024</t>
+          <t>A 20086-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45554</v>
+        <v>45054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3266,35 +3266,35 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
         <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44566</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44657</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34380-2022</t>
+          <t>A 62369-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44792</v>
+        <v>45268</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59309-2023</t>
+          <t>A 34217-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45253</v>
+        <v>44791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39206-2024</t>
+          <t>A 57877-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45548</v>
+        <v>44899</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23682-2024</t>
+          <t>A 22750-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45454</v>
+        <v>45448</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28109-2024</t>
+          <t>A 36999-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45476</v>
+        <v>45155</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 5714-2024</t>
+          <t>A 19005-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45334</v>
+        <v>45045</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55777-2022</t>
+          <t>A 59309-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44888</v>
+        <v>45253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 49822-2022</t>
+          <t>A 13521-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44862</v>
+        <v>45736</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57878-2022</t>
+          <t>A 13536-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44899</v>
+        <v>45736</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.6</v>
+        <v>0.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 49115-2024</t>
+          <t>A 24321-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45594</v>
+        <v>45797</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 30440-2024</t>
+          <t>A 34046-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45491</v>
+        <v>45523</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62516-2022</t>
+          <t>A 44754-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44924</v>
+        <v>45574</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 40743-2024</t>
+          <t>A 44417-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45558</v>
+        <v>45573</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 49134-2021</t>
+          <t>A 55777-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5350,14 +5350,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44453</v>
+        <v>44888</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5369,13 +5369,8 @@
           <t>ORUST</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5418,7 +5413,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22750-2024</t>
+          <t>A 27555-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5432,10 +5427,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45448</v>
+        <v>45813</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5448,7 +5443,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5491,7 +5486,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 49617-2023</t>
+          <t>A 54279-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5505,10 +5500,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45211</v>
+        <v>45616</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5521,7 +5516,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.4</v>
+        <v>6.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5564,7 +5559,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8457-2026</t>
+          <t>A 2435-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5578,10 +5573,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46065</v>
+        <v>46036</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5594,7 +5589,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5637,7 +5632,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1288-2025</t>
+          <t>A 2436-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5651,10 +5646,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45667</v>
+        <v>46036</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5667,7 +5662,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5710,7 +5705,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9344-2026</t>
+          <t>A 41063-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5724,10 +5719,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46070</v>
+        <v>45898</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5740,7 +5735,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5783,7 +5778,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 9194-2026</t>
+          <t>A 47884-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5797,10 +5792,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46070</v>
+        <v>45588</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5813,7 +5808,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5856,7 +5851,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20131-2025</t>
+          <t>A 41881-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5870,10 +5865,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45772</v>
+        <v>45903</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5886,7 +5881,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5929,7 +5924,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33300-2025</t>
+          <t>A 42457-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5943,10 +5938,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45840</v>
+        <v>45905</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5959,7 +5954,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6002,7 +5997,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33295-2025</t>
+          <t>A 4114-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6016,10 +6011,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45840</v>
+        <v>46044</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6032,7 +6027,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>7.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6075,7 +6070,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33299-2025</t>
+          <t>A 43752-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6089,10 +6084,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45840</v>
+        <v>45187</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6105,7 +6100,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6148,7 +6143,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 51993-2022</t>
+          <t>A 30440-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6162,10 +6157,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44872</v>
+        <v>45491</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6178,7 +6173,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6221,7 +6216,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 41063-2025</t>
+          <t>A 33300-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6235,10 +6230,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45898</v>
+        <v>45840</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6251,7 +6246,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6294,7 +6289,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 47884-2024</t>
+          <t>A 33295-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6308,10 +6303,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45588</v>
+        <v>45840</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6324,7 +6319,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6367,7 +6362,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34502-2025</t>
+          <t>A 33299-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6381,10 +6376,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6397,7 +6392,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6440,7 +6435,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 41881-2025</t>
+          <t>A 49115-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6454,10 +6449,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45903</v>
+        <v>45594</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6470,7 +6465,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6513,7 +6508,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42457-2025</t>
+          <t>A 6739-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6527,10 +6522,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45905</v>
+        <v>46056</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6543,7 +6538,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6586,7 +6581,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 36722-2025</t>
+          <t>A 34502-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6600,10 +6595,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45872</v>
+        <v>45847</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6616,7 +6611,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6659,7 +6654,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10118-2026</t>
+          <t>A 8457-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6673,10 +6668,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46075</v>
+        <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6689,7 +6684,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6732,7 +6727,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34354-2023</t>
+          <t>A 9194-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6746,10 +6741,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45139</v>
+        <v>46070</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6762,7 +6757,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6805,7 +6800,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 50532-2024</t>
+          <t>A 9344-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6819,10 +6814,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45601</v>
+        <v>46070</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6835,7 +6830,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6878,7 +6873,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 33454-2023</t>
+          <t>A 48419-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6892,10 +6887,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45130</v>
+        <v>45934</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6908,7 +6903,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6951,7 +6946,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38322-2023</t>
+          <t>A 36722-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6965,10 +6960,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45161</v>
+        <v>45872</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6981,7 +6976,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7024,7 +7019,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48419-2025</t>
+          <t>A 10118-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7038,10 +7033,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45934</v>
+        <v>46075</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7054,7 +7049,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>7.7</v>
+        <v>3.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7114,7 +7109,7 @@
         <v>45938</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7170,7 +7165,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 57445-2024</t>
+          <t>A 71890-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7184,10 +7179,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45629</v>
+        <v>44543</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7200,7 +7195,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7243,7 +7238,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 12087-2026</t>
+          <t>A 50532-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7257,10 +7252,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46086</v>
+        <v>45601</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7273,7 +7268,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.6</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7316,7 +7311,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 14802-2023</t>
+          <t>A 6957-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7330,10 +7325,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45014</v>
+        <v>45343</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7346,7 +7341,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7389,7 +7384,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 17426-2026</t>
+          <t>A 1288-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7403,10 +7398,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46120</v>
+        <v>45667</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7419,7 +7414,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7462,7 +7457,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 18431-2026</t>
+          <t>A 51993-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7476,10 +7471,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46127</v>
+        <v>44872</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7492,7 +7487,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7535,7 +7530,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58852-2025</t>
+          <t>A 12087-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7549,10 +7544,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45987</v>
+        <v>46086</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7565,7 +7560,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7608,7 +7603,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36404-2024</t>
+          <t>A 13378-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7622,10 +7617,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45535</v>
+        <v>45005</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7638,7 +7633,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7681,7 +7676,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 58853-2025</t>
+          <t>A 25925-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7695,10 +7690,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45987</v>
+        <v>45467</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7711,7 +7706,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7754,7 +7749,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 59834-2025</t>
+          <t>A 17426-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7768,10 +7763,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45992</v>
+        <v>46120</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7784,7 +7779,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7827,7 +7822,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 61319-2025</t>
+          <t>A 18431-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7841,10 +7836,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46000</v>
+        <v>46127</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7857,7 +7852,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7900,7 +7895,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20089-2025</t>
+          <t>A 62516-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7914,10 +7909,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45771</v>
+        <v>44924</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7930,7 +7925,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7973,7 +7968,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56496-2021</t>
+          <t>A 58853-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7987,10 +7982,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44480</v>
+        <v>45987</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8003,7 +7998,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>10.3</v>
+        <v>3.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8046,7 +8041,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 40328-2025</t>
+          <t>A 58852-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8060,10 +8055,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45895</v>
+        <v>45987</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8076,7 +8071,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8119,7 +8114,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 27277-2025</t>
+          <t>A 23258-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8133,10 +8128,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45812</v>
+        <v>45791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8149,7 +8144,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8192,7 +8187,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 23258-2025</t>
+          <t>A 59834-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8206,10 +8201,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45791</v>
+        <v>45992</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8222,7 +8217,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8265,7 +8260,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33296-2025</t>
+          <t>A 34500-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8279,10 +8274,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45840</v>
+        <v>45847</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8295,7 +8290,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8338,7 +8333,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 2435-2026</t>
+          <t>A 5926-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8352,10 +8347,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46036</v>
+        <v>45336</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8368,7 +8363,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8411,7 +8406,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 2436-2026</t>
+          <t>A 27277-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8425,10 +8420,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46036</v>
+        <v>45812</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8441,7 +8436,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8484,7 +8479,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 4114-2026</t>
+          <t>A 61319-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8498,10 +8493,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46044</v>
+        <v>46000</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8514,7 +8509,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8557,7 +8552,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 62086-2022</t>
+          <t>A 40328-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8571,10 +8566,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44919</v>
+        <v>45895</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8587,7 +8582,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8630,7 +8625,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6957-2024</t>
+          <t>A 33296-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8644,10 +8639,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45343</v>
+        <v>45840</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8660,7 +8655,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8703,7 +8698,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 6739-2026</t>
+          <t>A 56496-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8717,10 +8712,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46056</v>
+        <v>44480</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8733,7 +8728,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.8</v>
+        <v>10.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8776,7 +8771,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34500-2025</t>
+          <t>A 20089-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8790,10 +8785,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45847</v>
+        <v>45771</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8806,7 +8801,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.4</v>
+        <v>2.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8849,7 +8844,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 2632-2024</t>
+          <t>A 61302-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8863,10 +8858,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45313</v>
+        <v>45645</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8879,7 +8874,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8939,7 +8934,7 @@
         <v>44529</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8995,7 +8990,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 54128-2025</t>
+          <t>A 20675-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9009,10 +9004,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45964</v>
+        <v>46141</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9025,7 +9020,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9068,7 +9063,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 32175-2024</t>
+          <t>A 5714-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9082,10 +9077,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45511</v>
+        <v>45334</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9098,7 +9093,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9141,7 +9136,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 63626-2023</t>
+          <t>A 34380-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9155,10 +9150,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45275</v>
+        <v>44792</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9171,7 +9166,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9214,7 +9209,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 37130-2024</t>
+          <t>A 54128-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9228,10 +9223,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45539</v>
+        <v>45964</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9244,7 +9239,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9287,7 +9282,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20675-2026</t>
+          <t>A 13377-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9301,10 +9296,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46141</v>
+        <v>45005</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9317,7 +9312,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9360,7 +9355,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 5926-2024</t>
+          <t>A 37130-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9374,10 +9369,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45336</v>
+        <v>45539</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9390,7 +9385,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9433,7 +9428,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 20819-2023</t>
+          <t>A 59915-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9447,10 +9442,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45058</v>
+        <v>45641</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9463,7 +9458,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9523,7 +9518,7 @@
         <v>45396</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9579,7 +9574,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 49072-2025</t>
+          <t>A 42712-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9593,10 +9588,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45937</v>
+        <v>45181</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9609,7 +9604,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9652,7 +9647,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 24605-2026</t>
+          <t>A 50562-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9666,10 +9661,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46170</v>
+        <v>45601</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9682,7 +9677,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9725,7 +9720,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 43752-2023</t>
+          <t>A 24605-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9739,10 +9734,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45187</v>
+        <v>46170</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9755,7 +9750,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>9.300000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9798,7 +9793,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 25123-2026</t>
+          <t>A 49072-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9812,10 +9807,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46175</v>
+        <v>45937</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9828,7 +9823,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9871,7 +9866,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 25138-2026</t>
+          <t>A 25123-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9888,7 +9883,7 @@
         <v>46175</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9901,7 +9896,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9944,7 +9939,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 34217-2022</t>
+          <t>A 25138-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9958,10 +9953,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44791</v>
+        <v>46175</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9974,7 +9969,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10034,7 +10029,7 @@
         <v>46181</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10090,7 +10085,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 5715-2024</t>
+          <t>A 20131-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10104,10 +10099,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45334</v>
+        <v>45772</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10180,7 +10175,7 @@
         <v>45692</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10236,7 +10231,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 19005-2023</t>
+          <t>A 33789-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10250,10 +10245,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45045</v>
+        <v>46251</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10309,7 +10304,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 34056-2024</t>
+          <t>A 40722-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10323,10 +10318,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45523</v>
+        <v>45558</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10339,7 +10334,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10382,7 +10377,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 59915-2024</t>
+          <t>A 36404-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10396,10 +10391,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45641</v>
+        <v>45535</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10412,7 +10407,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10455,7 +10450,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 57877-2022</t>
+          <t>A 31029-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10469,10 +10464,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44899</v>
+        <v>46213</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10485,7 +10480,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10528,7 +10523,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 13378-2023</t>
+          <t>A 57445-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10542,10 +10537,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45005</v>
+        <v>45629</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10558,7 +10553,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10601,7 +10596,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 25925-2024</t>
+          <t>A 36428-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10615,10 +10610,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45467</v>
+        <v>46269</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10631,7 +10626,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10674,7 +10669,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 34155-2024</t>
+          <t>A 49822-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10688,10 +10683,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45524</v>
+        <v>44862</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10704,7 +10699,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10747,7 +10742,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 33789-2026</t>
+          <t>A 38322-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10761,10 +10756,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46251</v>
+        <v>45161</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10777,7 +10772,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10820,7 +10815,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 18791-2023</t>
+          <t>A 40743-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10834,10 +10829,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45044</v>
+        <v>45558</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10850,7 +10845,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10893,7 +10888,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 42712-2023</t>
+          <t>A 20819-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10907,10 +10902,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45181</v>
+        <v>45058</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10923,7 +10918,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10966,7 +10961,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 31029-2026</t>
+          <t>A 34354-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10980,10 +10975,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46213</v>
+        <v>45139</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10996,7 +10991,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11039,7 +11034,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 71890-2021</t>
+          <t>A 6485-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11053,10 +11048,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44543</v>
+        <v>45339</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11069,7 +11064,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11112,7 +11107,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 49134-2021</t>
+          <t>A 49617-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11122,14 +11117,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44453</v>
+        <v>45211</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11141,13 +11136,8 @@
           <t>ORUST</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11190,7 +11180,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 46708-2023</t>
+          <t>A 23682-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11204,10 +11194,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45198</v>
+        <v>45454</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11220,7 +11210,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11263,7 +11253,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 40722-2024</t>
+          <t>A 39206-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11277,10 +11267,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45558</v>
+        <v>45548</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11293,7 +11283,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11336,7 +11326,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 62369-2023</t>
+          <t>A 5715-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11350,10 +11340,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45268</v>
+        <v>45334</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11366,7 +11356,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11409,7 +11399,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 14547-2022</t>
+          <t>A 34056-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11423,10 +11413,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44655</v>
+        <v>45523</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11439,7 +11429,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11482,7 +11472,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 36428-2026</t>
+          <t>A 14547-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11496,10 +11486,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46269</v>
+        <v>44655</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11512,7 +11502,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11555,7 +11545,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 6485-2024</t>
+          <t>A 18791-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11569,10 +11559,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45339</v>
+        <v>45044</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11585,7 +11575,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11628,7 +11618,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 13377-2023</t>
+          <t>A 28109-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11642,10 +11632,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45005</v>
+        <v>45476</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11658,7 +11648,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11701,7 +11691,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 61302-2024</t>
+          <t>A 63626-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11715,10 +11705,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45645</v>
+        <v>45275</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11731,7 +11721,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11774,7 +11764,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 50562-2024</t>
+          <t>A 32175-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11788,10 +11778,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45601</v>
+        <v>45511</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11804,7 +11794,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11847,7 +11837,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 36999-2023</t>
+          <t>A 34155-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11861,10 +11851,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45155</v>
+        <v>45524</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11877,7 +11867,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11920,7 +11910,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 22959-2025</t>
+          <t>A 46708-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11934,10 +11924,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45790</v>
+        <v>45198</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11950,7 +11940,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11993,7 +11983,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 9937-2025</t>
+          <t>A 62086-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12007,10 +11997,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45718</v>
+        <v>44919</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12023,7 +12013,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12066,7 +12056,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 13521-2025</t>
+          <t>A 57878-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12080,10 +12070,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45736</v>
+        <v>44899</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12096,7 +12086,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12139,7 +12129,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 13536-2025</t>
+          <t>A 14802-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12153,10 +12143,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45736</v>
+        <v>45014</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12169,7 +12159,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12212,7 +12202,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 14760-2025</t>
+          <t>A 2632-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12226,10 +12216,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45742</v>
+        <v>45313</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12242,7 +12232,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12285,7 +12275,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 34046-2024</t>
+          <t>A 33454-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12299,10 +12289,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45523</v>
+        <v>45130</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12315,7 +12305,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12358,7 +12348,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24321-2025</t>
+          <t>A 22959-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12372,10 +12362,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45797</v>
+        <v>45790</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12431,7 +12421,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 44417-2024</t>
+          <t>A 14760-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12445,10 +12435,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45573</v>
+        <v>45742</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12461,7 +12451,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12504,7 +12494,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 44754-2024</t>
+          <t>A 9937-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12518,10 +12508,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45574</v>
+        <v>45718</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12534,7 +12524,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12574,27 +12564,27 @@
       </c>
       <c r="V152" s="2" t="inlineStr"/>
     </row>
-    <row r="153" ht="15" customHeight="1">
+    <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 27555-2025</t>
+          <t>S 2776-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45813</v>
+        <v>45937</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12607,7 +12597,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12646,152 +12636,6 @@
         <v>0</v>
       </c>
       <c r="V153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154" ht="15" customHeight="1">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>A 54279-2024</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D154" s="1" t="n">
-        <v>45616</v>
-      </c>
-      <c r="E154" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I154" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J154" t="n">
-        <v>0</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" t="n">
-        <v>0</v>
-      </c>
-      <c r="M154" t="n">
-        <v>0</v>
-      </c>
-      <c r="N154" t="n">
-        <v>0</v>
-      </c>
-      <c r="O154" t="n">
-        <v>0</v>
-      </c>
-      <c r="P154" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
-      <c r="R154" t="n">
-        <v>0</v>
-      </c>
-      <c r="S154" t="n">
-        <v>0</v>
-      </c>
-      <c r="T154" t="n">
-        <v>0</v>
-      </c>
-      <c r="U154" t="n">
-        <v>0</v>
-      </c>
-      <c r="V154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>S 2776-2025</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D155" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E155" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I155" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" t="n">
-        <v>0</v>
-      </c>
-      <c r="M155" t="n">
-        <v>0</v>
-      </c>
-      <c r="N155" t="n">
-        <v>0</v>
-      </c>
-      <c r="O155" t="n">
-        <v>0</v>
-      </c>
-      <c r="P155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0</v>
-      </c>
-      <c r="S155" t="n">
-        <v>0</v>
-      </c>
-      <c r="T155" t="n">
-        <v>0</v>
-      </c>
-      <c r="U155" t="n">
-        <v>0</v>
-      </c>
-      <c r="V155" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE153"/>
+  <dimension ref="A1:AE154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14805-2023</t>
+          <t>A 49930-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45014</v>
+        <v>45597</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -835,34 +835,34 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>16.6</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -871,9 +871,117 @@
         <v>6</v>
       </c>
       <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Svart trolldruva
+Revlummer
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 14805-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Grönsångare
@@ -881,115 +989,115 @@
 Purpurmylia</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 65099-2023</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>45288</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>17.8</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>2</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>2</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Blockskapania
 Knärot
@@ -997,151 +1105,43 @@
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 49930-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45597</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Svart trolldruva
-Revlummer
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 72588-2021</t>
+          <t>A 63419-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44546</v>
+        <v>45274</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1171,19 +1171,19 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>21.8</v>
+        <v>6.4</v>
       </c>
       <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1195,10 +1195,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1207,267 +1207,267 @@
         <v>3</v>
       </c>
       <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Björktrast
+Rödvingetrast
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 72588-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44546</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Kambräken
 Spillkråka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 72588-2021 artfynd.xlsx", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 72588-2021 karta.png", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 72588-2021 georefererad karta.tif", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 72588-2021 karta knärot.png", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 72588-2021 FSC-klagomål.docx", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 72588-2021 FSC-klagomål mail.docx", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 72588-2021 tillsynsbegäran.docx", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 72588-2021 tillsynsbegäran mail.docx", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 72588-2021 prioriterade fågelarter.docx", "A 72588-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 6055-2024</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>45336</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>24.1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>5</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>3</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)
 Revlummer
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6055-2024 artfynd.xlsx", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6055-2024 karta.png", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6055-2024 georefererad karta.tif", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6055-2024 FSC-klagomål.docx", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6055-2024 FSC-klagomål mail.docx", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6055-2024 tillsynsbegäran.docx", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6055-2024 tillsynsbegäran mail.docx", "A 6055-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 63419-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45274</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Björktrast
-Rödvingetrast
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
         <v/>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         <v>45306</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 56035-2025</t>
+          <t>A 13220-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1591,14 +1591,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45973</v>
+        <v>45386</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>15.9</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1644,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1655,42 +1655,42 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 40270-2024</t>
+          <t>A 12722-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45554</v>
+        <v>46091</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>7.4</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1756,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
@@ -1764,42 +1764,42 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12722-2026</t>
+          <t>A 6986-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46091</v>
+        <v>45343</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1853,10 +1853,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1865,50 +1865,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 6986-2024</t>
+          <t>A 24618-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1922,10 +1918,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45343</v>
+        <v>45460</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1938,7 +1934,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1974,39 +1970,39 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
     </row>
@@ -2030,7 +2026,7 @@
         <v>45937</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2118,7 +2114,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 23921-2026</t>
+          <t>A 771-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2132,10 +2128,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46167</v>
+        <v>44931</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2148,13 +2144,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2188,42 +2184,46 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 31028-2026</t>
+          <t>A 20086-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46213</v>
+        <v>45054</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2253,20 +2253,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2277,10 +2277,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2289,46 +2289,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
+        <v/>
+      </c>
+      <c r="Z17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41056-2025</t>
+          <t>A 5634-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2342,10 +2346,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45898</v>
+        <v>45693</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2358,20 +2362,20 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
@@ -2382,58 +2386,62 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <v/>
+      </c>
+      <c r="Z18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 771-2023</t>
+          <t>A 56035-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2443,14 +2451,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44931</v>
+        <v>45973</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2463,7 +2471,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>15.9</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2475,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2487,62 +2495,62 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 13220-2024</t>
+          <t>A 20709-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2556,10 +2564,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45386</v>
+        <v>45058</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2572,7 +2580,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2605,10 +2613,10 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
@@ -2616,42 +2624,42 @@
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24618-2024</t>
+          <t>A 5617-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2665,10 +2673,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45460</v>
+        <v>45334</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2681,7 +2689,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>9.5</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2693,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2705,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2717,46 +2725,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
+        <v/>
+      </c>
+      <c r="Z21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20709-2023</t>
+          <t>A 44233-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2770,10 +2782,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45058</v>
+        <v>45183</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2786,7 +2798,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2819,10 +2831,10 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
@@ -2830,42 +2842,42 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Z22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5617-2024</t>
+          <t>A 23921-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2879,10 +2891,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45334</v>
+        <v>46167</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2895,19 +2907,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2919,10 +2931,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2931,50 +2943,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
-        <v/>
-      </c>
-      <c r="Z23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44233-2023</t>
+          <t>A 31028-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2988,10 +2996,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45183</v>
+        <v>46213</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3004,19 +3012,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3028,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3044,46 +3052,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5634-2025</t>
+          <t>A 41056-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3097,10 +3101,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45693</v>
+        <v>45898</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3113,19 +3117,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3137,62 +3141,58 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20086-2023</t>
+          <t>A 40270-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45054</v>
+        <v>45554</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3266,35 +3266,35 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
         <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44566</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44657</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52012-2022</t>
+          <t>A 69196-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44872</v>
+        <v>44531</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4318,7 +4318,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 69196-2021</t>
+          <t>A 34380-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44531</v>
+        <v>44792</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62369-2023</t>
+          <t>A 43752-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45268</v>
+        <v>45187</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34217-2022</t>
+          <t>A 59309-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44791</v>
+        <v>45253</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57877-2022</t>
+          <t>A 34217-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44899</v>
+        <v>44791</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22750-2024</t>
+          <t>A 52012-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45448</v>
+        <v>44872</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 36999-2023</t>
+          <t>A 50532-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45155</v>
+        <v>45601</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19005-2023</t>
+          <t>A 39206-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45045</v>
+        <v>45548</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59309-2023</t>
+          <t>A 1288-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45253</v>
+        <v>45667</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13521-2025</t>
+          <t>A 23682-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45736</v>
+        <v>45454</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 13536-2025</t>
+          <t>A 22750-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45736</v>
+        <v>45448</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24321-2025</t>
+          <t>A 28109-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45797</v>
+        <v>45476</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5121,7 +5121,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34046-2024</t>
+          <t>A 12087-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45523</v>
+        <v>46086</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 44754-2024</t>
+          <t>A 5714-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45574</v>
+        <v>45334</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 44417-2024</t>
+          <t>A 55777-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45573</v>
+        <v>44888</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55777-2022</t>
+          <t>A 41063-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44888</v>
+        <v>45898</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27555-2025</t>
+          <t>A 47884-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45813</v>
+        <v>45588</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 54279-2024</t>
+          <t>A 41881-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45616</v>
+        <v>45903</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5559,7 +5559,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2435-2026</t>
+          <t>A 49822-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46036</v>
+        <v>44862</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2436-2026</t>
+          <t>A 57878-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46036</v>
+        <v>44899</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 41063-2025</t>
+          <t>A 42457-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45898</v>
+        <v>45905</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47884-2024</t>
+          <t>A 49115-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45588</v>
+        <v>45594</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41881-2025</t>
+          <t>A 30440-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45903</v>
+        <v>45491</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 42457-2025</t>
+          <t>A 62516-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45905</v>
+        <v>44924</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4114-2026</t>
+          <t>A 5715-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46044</v>
+        <v>45334</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 43752-2023</t>
+          <t>A 5454-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45187</v>
+        <v>45692</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>9.300000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30440-2024</t>
+          <t>A 40743-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45491</v>
+        <v>45558</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33300-2025</t>
+          <t>A 17426-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45840</v>
+        <v>46120</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 33295-2025</t>
+          <t>A 19005-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45840</v>
+        <v>45045</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 33299-2025</t>
+          <t>A 49617-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45840</v>
+        <v>45211</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6435,7 +6435,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49115-2024</t>
+          <t>A 34056-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45594</v>
+        <v>45523</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6508,7 +6508,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6739-2026</t>
+          <t>A 18431-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46056</v>
+        <v>46127</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 34502-2025</t>
+          <t>A 59915-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45847</v>
+        <v>45641</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6654,7 +6654,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8457-2026</t>
+          <t>A 48419-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46065</v>
+        <v>45934</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>7.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9194-2026</t>
+          <t>A 57877-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46070</v>
+        <v>44899</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 9344-2026</t>
+          <t>A 49365-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46070</v>
+        <v>45938</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 48419-2025</t>
+          <t>A 13378-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45934</v>
+        <v>45005</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36722-2025</t>
+          <t>A 20131-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45872</v>
+        <v>45772</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10118-2026</t>
+          <t>A 51993-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46075</v>
+        <v>44872</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 49365-2025</t>
+          <t>A 56496-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45938</v>
+        <v>44480</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>10.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7165,7 +7165,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 71890-2021</t>
+          <t>A 40328-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44543</v>
+        <v>45895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 50532-2024</t>
+          <t>A 27277-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45601</v>
+        <v>45812</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6957-2024</t>
+          <t>A 23258-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45343</v>
+        <v>45791</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 1288-2025</t>
+          <t>A 33296-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45667</v>
+        <v>45840</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 51993-2022</t>
+          <t>A 34354-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44872</v>
+        <v>45139</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7530,7 +7530,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12087-2026</t>
+          <t>A 33454-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46086</v>
+        <v>45130</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13378-2023</t>
+          <t>A 34500-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45005</v>
+        <v>45847</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>7.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 25925-2024</t>
+          <t>A 68727-2021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45467</v>
+        <v>44529</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 17426-2026</t>
+          <t>A 38322-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46120</v>
+        <v>45161</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18431-2026</t>
+          <t>A 54128-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46127</v>
+        <v>45964</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 62516-2022</t>
+          <t>A 58852-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44924</v>
+        <v>45987</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
         <v>45987</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 58852-2025</t>
+          <t>A 59834-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23258-2025</t>
+          <t>A 20675-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45791</v>
+        <v>46141</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59834-2025</t>
+          <t>A 57445-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45992</v>
+        <v>45629</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 34500-2025</t>
+          <t>A 61319-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45847</v>
+        <v>46000</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>7.4</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 5926-2024</t>
+          <t>A 25925-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45336</v>
+        <v>45467</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 27277-2025</t>
+          <t>A 14802-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45812</v>
+        <v>45014</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 61319-2025</t>
+          <t>A 14609-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46000</v>
+        <v>45396</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 40328-2025</t>
+          <t>A 36404-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45895</v>
+        <v>45535</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 33296-2025</t>
+          <t>A 2435-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45840</v>
+        <v>46036</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 56496-2021</t>
+          <t>A 2436-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44480</v>
+        <v>46036</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>10.3</v>
+        <v>2.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20089-2025</t>
+          <t>A 49072-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45771</v>
+        <v>45937</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61302-2024</t>
+          <t>A 4114-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45645</v>
+        <v>46044</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>7.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 68727-2021</t>
+          <t>A 34155-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44529</v>
+        <v>45524</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 20675-2026</t>
+          <t>A 24605-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 5714-2024</t>
+          <t>A 25123-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45334</v>
+        <v>46175</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 34380-2022</t>
+          <t>A 25138-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44792</v>
+        <v>46175</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 54128-2025</t>
+          <t>A 18791-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45964</v>
+        <v>45044</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 13377-2023</t>
+          <t>A 20089-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45005</v>
+        <v>45771</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 37130-2024</t>
+          <t>A 6739-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45539</v>
+        <v>46056</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 59915-2024</t>
+          <t>A 25963-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45641</v>
+        <v>46181</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 14609-2024</t>
+          <t>A 42712-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45396</v>
+        <v>45181</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 42712-2023</t>
+          <t>A 8457-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45181</v>
+        <v>46065</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 50562-2024</t>
+          <t>A 9344-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45601</v>
+        <v>46070</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 24605-2026</t>
+          <t>A 9194-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46170</v>
+        <v>46070</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 49072-2025</t>
+          <t>A 10118-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45937</v>
+        <v>46075</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 25123-2026</t>
+          <t>A 62086-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46175</v>
+        <v>44919</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 25138-2026</t>
+          <t>A 6957-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9953,10 +9953,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46175</v>
+        <v>45343</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 25963-2026</t>
+          <t>A 2632-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46181</v>
+        <v>45313</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10085,7 +10085,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20131-2025</t>
+          <t>A 71890-2021</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45772</v>
+        <v>44543</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10158,7 +10158,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 5454-2025</t>
+          <t>A 32175-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10172,10 +10172,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45692</v>
+        <v>45511</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10231,7 +10231,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 33789-2026</t>
+          <t>A 63626-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46251</v>
+        <v>45275</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10304,7 +10304,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 40722-2024</t>
+          <t>A 37130-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10318,10 +10318,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45558</v>
+        <v>45539</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10377,7 +10377,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 36404-2024</t>
+          <t>A 5926-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45535</v>
+        <v>45336</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 31029-2026</t>
+          <t>A 33789-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46213</v>
+        <v>46251</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 57445-2024</t>
+          <t>A 20819-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45629</v>
+        <v>45058</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10596,7 +10596,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 36428-2026</t>
+          <t>A 46708-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46269</v>
+        <v>45198</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10669,7 +10669,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 49822-2022</t>
+          <t>A 40722-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44862</v>
+        <v>45558</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10742,7 +10742,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 38322-2023</t>
+          <t>A 31029-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10756,10 +10756,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45161</v>
+        <v>46213</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10815,7 +10815,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 40743-2024</t>
+          <t>A 62369-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10829,10 +10829,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45558</v>
+        <v>45268</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20819-2023</t>
+          <t>A 14547-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45058</v>
+        <v>44655</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10961,7 +10961,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 34354-2023</t>
+          <t>A 36428-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45139</v>
+        <v>46269</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11051,7 +11051,7 @@
         <v>45339</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 49617-2023</t>
+          <t>A 13377-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11121,10 +11121,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45211</v>
+        <v>45005</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 23682-2024</t>
+          <t>A 61302-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45454</v>
+        <v>45645</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11253,7 +11253,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 39206-2024</t>
+          <t>A 50562-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11267,10 +11267,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45548</v>
+        <v>45601</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 5715-2024</t>
+          <t>A 36999-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11340,10 +11340,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45334</v>
+        <v>45155</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11399,7 +11399,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 34056-2024</t>
+          <t>A 37948-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45523</v>
+        <v>46280</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11472,7 +11472,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 14547-2022</t>
+          <t>A 22959-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11486,10 +11486,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44655</v>
+        <v>45790</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11545,7 +11545,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 18791-2023</t>
+          <t>A 9937-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11559,10 +11559,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45044</v>
+        <v>45718</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11618,7 +11618,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 28109-2024</t>
+          <t>A 13521-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11632,10 +11632,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45476</v>
+        <v>45736</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 63626-2023</t>
+          <t>A 13536-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11705,10 +11705,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45275</v>
+        <v>45736</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.4</v>
+        <v>0.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11764,7 +11764,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 32175-2024</t>
+          <t>A 14760-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45511</v>
+        <v>45742</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11837,7 +11837,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 34155-2024</t>
+          <t>A 34046-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45524</v>
+        <v>45523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 46708-2023</t>
+          <t>A 24321-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11924,10 +11924,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45198</v>
+        <v>45797</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11983,7 +11983,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 62086-2022</t>
+          <t>A 44417-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44919</v>
+        <v>45573</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 57878-2022</t>
+          <t>A 44754-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44899</v>
+        <v>45574</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12129,7 +12129,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 14802-2023</t>
+          <t>A 27555-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12143,10 +12143,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45014</v>
+        <v>45813</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12202,7 +12202,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 2632-2024</t>
+          <t>A 54279-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12216,10 +12216,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45313</v>
+        <v>45616</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12275,7 +12275,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33454-2023</t>
+          <t>A 33300-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12289,10 +12289,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45130</v>
+        <v>45840</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12348,7 +12348,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 22959-2025</t>
+          <t>A 33295-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45790</v>
+        <v>45840</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12421,7 +12421,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 14760-2025</t>
+          <t>A 33299-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45742</v>
+        <v>45840</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 9937-2025</t>
+          <t>A 34502-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12508,10 +12508,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45718</v>
+        <v>45847</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12564,78 +12564,151 @@
       </c>
       <c r="V152" s="2" t="inlineStr"/>
     </row>
-    <row r="153">
+    <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
+          <t>A 36722-2025</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D153" s="1" t="n">
+        <v>45872</v>
+      </c>
+      <c r="E153" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
           <t>S 2776-2025</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D153" s="1" t="n">
+      <c r="D154" s="1" t="n">
         <v>45937</v>
       </c>
-      <c r="E153" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I153" t="n">
+      <c r="E154" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
         <v>1.1</v>
       </c>
-      <c r="J153" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" t="n">
-        <v>0</v>
-      </c>
-      <c r="M153" t="n">
-        <v>0</v>
-      </c>
-      <c r="N153" t="n">
-        <v>0</v>
-      </c>
-      <c r="O153" t="n">
-        <v>0</v>
-      </c>
-      <c r="P153" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
-      <c r="R153" t="n">
-        <v>0</v>
-      </c>
-      <c r="S153" t="n">
-        <v>0</v>
-      </c>
-      <c r="T153" t="n">
-        <v>0</v>
-      </c>
-      <c r="U153" t="n">
-        <v>0</v>
-      </c>
-      <c r="V153" s="2" t="inlineStr"/>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 49930-2024</t>
+          <t>A 14805-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45597</v>
+        <v>45014</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>16.6</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
         <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -871,9 +871,237 @@
         <v>6</v>
       </c>
       <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönsångare
+Kambräken
+Purpurmylia</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 65099-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45288</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Blockskapania
+Knärot
+Grov fjädermossa
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 49930-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Svart trolldruva
@@ -881,267 +1109,39 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 14805-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>6</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönsångare
-Kambräken
-Purpurmylia</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 65099-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45288</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Blockskapania
-Knärot
-Grov fjädermossa
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 63419-2023</t>
+          <t>A 72588-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45274</v>
+        <v>44546</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1171,19 +1171,19 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>6.4</v>
+        <v>21.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1195,10 +1195,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1207,267 +1207,267 @@
         <v>3</v>
       </c>
       <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Kambräken
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 72588-2021 artfynd.xlsx", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 72588-2021 karta.png", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 72588-2021 georefererad karta.tif", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 72588-2021 karta knärot.png", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 72588-2021 FSC-klagomål.docx", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 72588-2021 FSC-klagomål mail.docx", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 72588-2021 tillsynsbegäran.docx", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 72588-2021 tillsynsbegäran mail.docx", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 72588-2021 prioriterade fågelarter.docx", "A 72588-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 6055-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45336</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)
+Revlummer
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6055-2024 artfynd.xlsx", "A 6055-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6055-2024 karta.png", "A 6055-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6055-2024 georefererad karta.tif", "A 6055-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6055-2024 FSC-klagomål.docx", "A 6055-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6055-2024 FSC-klagomål mail.docx", "A 6055-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6055-2024 tillsynsbegäran.docx", "A 6055-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6055-2024 tillsynsbegäran mail.docx", "A 6055-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 63419-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45274</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Björktrast
 Rödvingetrast
 Gröngöling</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 72588-2021</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44546</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Kambräken
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 72588-2021 artfynd.xlsx", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 72588-2021 karta.png", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 72588-2021 georefererad karta.tif", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 72588-2021 karta knärot.png", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 72588-2021 FSC-klagomål.docx", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 72588-2021 FSC-klagomål mail.docx", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 72588-2021 tillsynsbegäran.docx", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 72588-2021 tillsynsbegäran mail.docx", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 72588-2021 prioriterade fågelarter.docx", "A 72588-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 6055-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45336</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)
-Revlummer
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6055-2024 artfynd.xlsx", "A 6055-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6055-2024 karta.png", "A 6055-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6055-2024 georefererad karta.tif", "A 6055-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6055-2024 FSC-klagomål.docx", "A 6055-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6055-2024 FSC-klagomål mail.docx", "A 6055-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6055-2024 tillsynsbegäran.docx", "A 6055-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6055-2024 tillsynsbegäran mail.docx", "A 6055-2024")</f>
         <v/>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         <v>45306</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13220-2024</t>
+          <t>A 40270-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45386</v>
+        <v>45554</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1644,10 +1644,10 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1655,42 +1655,42 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 12722-2026</t>
+          <t>A 56035-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1700,14 +1700,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46091</v>
+        <v>45973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7.4</v>
+        <v>15.9</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1753,7 +1753,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1764,35 +1764,35 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
         <v>45343</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24618-2024</t>
+          <t>A 12722-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45460</v>
+        <v>46091</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>9.5</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1958,10 +1958,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1974,35 +1974,39 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
     </row>
@@ -2026,7 +2030,7 @@
         <v>45937</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2131,7 +2135,7 @@
         <v>44931</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2223,7 +2227,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20086-2023</t>
+          <t>A 13220-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2237,10 +2241,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45054</v>
+        <v>45386</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2253,7 +2257,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2286,10 +2290,10 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
@@ -2297,42 +2301,42 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Z17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 5634-2025</t>
+          <t>A 24618-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2346,10 +2350,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45693</v>
+        <v>45460</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2362,7 +2366,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>9.5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2374,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2386,62 +2390,58 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
-        <v/>
-      </c>
-      <c r="Z18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 56035-2025</t>
+          <t>A 20709-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2451,14 +2451,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45973</v>
+        <v>45058</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>15.9</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2504,10 +2504,10 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
@@ -2515,42 +2515,42 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20709-2023</t>
+          <t>A 5617-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45058</v>
+        <v>45334</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2613,10 +2613,10 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
@@ -2624,42 +2624,42 @@
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5617-2024</t>
+          <t>A 23921-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45334</v>
+        <v>46167</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2713,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2725,43 +2725,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
-        <v/>
-      </c>
-      <c r="Z21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
     </row>
@@ -2785,7 +2781,7 @@
         <v>45183</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2877,7 +2873,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23921-2026</t>
+          <t>A 31028-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2891,10 +2887,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46167</v>
+        <v>46213</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2907,7 +2903,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2947,42 +2943,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31028-2026</t>
+          <t>A 5634-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2996,10 +2992,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46213</v>
+        <v>45693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3012,20 +3008,20 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -3036,51 +3032,55 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <v/>
+      </c>
+      <c r="Z24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
         <v>45898</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 40270-2024</t>
+          <t>A 20086-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45554</v>
+        <v>45054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3266,35 +3266,35 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
         <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44566</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44657</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 69196-2021</t>
+          <t>A 52012-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44531</v>
+        <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4318,7 +4318,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34380-2022</t>
+          <t>A 69196-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44792</v>
+        <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 43752-2023</t>
+          <t>A 62369-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45187</v>
+        <v>45268</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>9.300000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59309-2023</t>
+          <t>A 34217-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45253</v>
+        <v>44791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34217-2022</t>
+          <t>A 57877-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44791</v>
+        <v>44899</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52012-2022</t>
+          <t>A 36999-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44872</v>
+        <v>45155</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 50532-2024</t>
+          <t>A 22750-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45601</v>
+        <v>45448</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 39206-2024</t>
+          <t>A 19005-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45548</v>
+        <v>45045</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1288-2025</t>
+          <t>A 59309-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45667</v>
+        <v>45253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 23682-2024</t>
+          <t>A 55777-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45454</v>
+        <v>44888</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22750-2024</t>
+          <t>A 44754-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45448</v>
+        <v>45574</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28109-2024</t>
+          <t>A 44417-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45476</v>
+        <v>45573</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5121,7 +5121,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12087-2026</t>
+          <t>A 27555-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46086</v>
+        <v>45813</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 5714-2024</t>
+          <t>A 43752-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45334</v>
+        <v>45187</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 55777-2022</t>
+          <t>A 30440-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44888</v>
+        <v>45491</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 41063-2025</t>
+          <t>A 54279-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45898</v>
+        <v>45616</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>6.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 47884-2024</t>
+          <t>A 41063-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45588</v>
+        <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 41881-2025</t>
+          <t>A 47884-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45903</v>
+        <v>45588</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5559,7 +5559,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49822-2022</t>
+          <t>A 41881-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44862</v>
+        <v>45903</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57878-2022</t>
+          <t>A 49115-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44899</v>
+        <v>45594</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5722,7 +5722,7 @@
         <v>45905</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49115-2024</t>
+          <t>A 2435-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45594</v>
+        <v>46036</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30440-2024</t>
+          <t>A 2436-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45491</v>
+        <v>46036</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 62516-2022</t>
+          <t>A 33300-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44924</v>
+        <v>45840</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>6.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 5715-2024</t>
+          <t>A 33295-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45334</v>
+        <v>45840</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5454-2025</t>
+          <t>A 33299-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45692</v>
+        <v>45840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 40743-2024</t>
+          <t>A 34502-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45558</v>
+        <v>45847</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17426-2026</t>
+          <t>A 71890-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46120</v>
+        <v>44543</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19005-2023</t>
+          <t>A 6957-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45045</v>
+        <v>45343</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49617-2023</t>
+          <t>A 51993-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45211</v>
+        <v>44872</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6435,7 +6435,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 34056-2024</t>
+          <t>A 13378-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45523</v>
+        <v>45005</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6508,7 +6508,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18431-2026</t>
+          <t>A 48419-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46127</v>
+        <v>45934</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59915-2024</t>
+          <t>A 36722-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45641</v>
+        <v>45872</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6654,7 +6654,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 48419-2025</t>
+          <t>A 25925-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45934</v>
+        <v>45467</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.7</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 57877-2022</t>
+          <t>A 49365-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44899</v>
+        <v>45938</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 49365-2025</t>
+          <t>A 4114-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45938</v>
+        <v>46044</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13378-2023</t>
+          <t>A 50532-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45005</v>
+        <v>45601</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20131-2025</t>
+          <t>A 1288-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45772</v>
+        <v>45667</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 51993-2022</t>
+          <t>A 6739-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44872</v>
+        <v>46056</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 56496-2021</t>
+          <t>A 8457-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44480</v>
+        <v>46065</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>10.3</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7165,7 +7165,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 40328-2025</t>
+          <t>A 62516-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45895</v>
+        <v>44924</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 27277-2025</t>
+          <t>A 9194-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45812</v>
+        <v>46070</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 23258-2025</t>
+          <t>A 9344-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45791</v>
+        <v>46070</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33296-2025</t>
+          <t>A 10118-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45840</v>
+        <v>46075</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 34354-2023</t>
+          <t>A 58853-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45139</v>
+        <v>45987</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7530,7 +7530,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 33454-2023</t>
+          <t>A 58852-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45130</v>
+        <v>45987</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34500-2025</t>
+          <t>A 5926-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45847</v>
+        <v>45336</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 68727-2021</t>
+          <t>A 59834-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44529</v>
+        <v>45992</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 38322-2023</t>
+          <t>A 12087-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45161</v>
+        <v>46086</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 54128-2025</t>
+          <t>A 61319-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45964</v>
+        <v>46000</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58852-2025</t>
+          <t>A 20089-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45987</v>
+        <v>45771</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 58853-2025</t>
+          <t>A 61302-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45987</v>
+        <v>45645</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59834-2025</t>
+          <t>A 5714-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45992</v>
+        <v>45334</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20675-2026</t>
+          <t>A 34380-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46141</v>
+        <v>44792</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 57445-2024</t>
+          <t>A 13377-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45629</v>
+        <v>45005</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 61319-2025</t>
+          <t>A 37130-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46000</v>
+        <v>45539</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 25925-2024</t>
+          <t>A 59915-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45467</v>
+        <v>45641</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14802-2023</t>
+          <t>A 42712-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45014</v>
+        <v>45181</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14609-2024</t>
+          <t>A 17426-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45396</v>
+        <v>46120</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 36404-2024</t>
+          <t>A 50562-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45535</v>
+        <v>45601</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 2435-2026</t>
+          <t>A 18431-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46036</v>
+        <v>46127</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 2436-2026</t>
+          <t>A 20131-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46036</v>
+        <v>45772</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 49072-2025</t>
+          <t>A 5454-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45937</v>
+        <v>45692</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 4114-2026</t>
+          <t>A 40722-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46044</v>
+        <v>45558</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7.1</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 34155-2024</t>
+          <t>A 36404-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45524</v>
+        <v>45535</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24605-2026</t>
+          <t>A 57445-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46170</v>
+        <v>45629</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25123-2026</t>
+          <t>A 23258-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46175</v>
+        <v>45791</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 25138-2026</t>
+          <t>A 34500-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46175</v>
+        <v>45847</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>7.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 18791-2023</t>
+          <t>A 27277-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45044</v>
+        <v>45812</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20089-2025</t>
+          <t>A 40328-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45771</v>
+        <v>45895</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 6739-2026</t>
+          <t>A 33296-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46056</v>
+        <v>45840</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 25963-2026</t>
+          <t>A 56496-2021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46181</v>
+        <v>44480</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.8</v>
+        <v>10.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 42712-2023</t>
+          <t>A 49822-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45181</v>
+        <v>44862</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 8457-2026</t>
+          <t>A 68727-2021</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46065</v>
+        <v>44529</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 9344-2026</t>
+          <t>A 20675-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46070</v>
+        <v>46141</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 9194-2026</t>
+          <t>A 54128-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46070</v>
+        <v>45964</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 10118-2026</t>
+          <t>A 38322-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46075</v>
+        <v>45161</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 62086-2022</t>
+          <t>A 40743-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44919</v>
+        <v>45558</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 6957-2024</t>
+          <t>A 14609-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9953,10 +9953,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45343</v>
+        <v>45396</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 2632-2024</t>
+          <t>A 20819-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45313</v>
+        <v>45058</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>8.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10085,7 +10085,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 71890-2021</t>
+          <t>A 34354-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44543</v>
+        <v>45139</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10158,7 +10158,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 32175-2024</t>
+          <t>A 24605-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10172,10 +10172,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45511</v>
+        <v>46170</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.3</v>
+        <v>4.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10231,7 +10231,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 63626-2023</t>
+          <t>A 49072-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45275</v>
+        <v>45937</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10304,7 +10304,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 37130-2024</t>
+          <t>A 25123-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10318,10 +10318,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45539</v>
+        <v>46175</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10377,7 +10377,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 5926-2024</t>
+          <t>A 25138-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45336</v>
+        <v>46175</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 33789-2026</t>
+          <t>A 6485-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46251</v>
+        <v>45339</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 20819-2023</t>
+          <t>A 25963-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45058</v>
+        <v>46181</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10596,7 +10596,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 46708-2023</t>
+          <t>A 49617-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45198</v>
+        <v>45211</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10669,7 +10669,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 40722-2024</t>
+          <t>A 23682-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45558</v>
+        <v>45454</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10742,7 +10742,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31029-2026</t>
+          <t>A 39206-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10756,10 +10756,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46213</v>
+        <v>45548</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 62369-2023</t>
+          <t>A 5715-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10829,10 +10829,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45268</v>
+        <v>45334</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 14547-2022</t>
+          <t>A 34056-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44655</v>
+        <v>45523</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10961,7 +10961,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 36428-2026</t>
+          <t>A 33789-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46269</v>
+        <v>46251</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11034,7 +11034,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 6485-2024</t>
+          <t>A 14547-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11048,10 +11048,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45339</v>
+        <v>44655</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11107,7 +11107,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 13377-2023</t>
+          <t>A 18791-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11121,10 +11121,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45005</v>
+        <v>45044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 61302-2024</t>
+          <t>A 28109-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45645</v>
+        <v>45476</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11253,7 +11253,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 50562-2024</t>
+          <t>A 31029-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11267,10 +11267,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45601</v>
+        <v>46213</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 36999-2023</t>
+          <t>A 63626-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11340,10 +11340,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45155</v>
+        <v>45275</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11399,7 +11399,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 37948-2026</t>
+          <t>A 32175-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46280</v>
+        <v>45511</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11472,7 +11472,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 22959-2025</t>
+          <t>A 34155-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11486,10 +11486,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45790</v>
+        <v>45524</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11545,7 +11545,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 9937-2025</t>
+          <t>A 46708-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11559,10 +11559,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45718</v>
+        <v>45198</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11618,7 +11618,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 13521-2025</t>
+          <t>A 62086-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11632,10 +11632,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45736</v>
+        <v>44919</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11691,7 +11691,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 13536-2025</t>
+          <t>A 36428-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11705,10 +11705,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45736</v>
+        <v>46269</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.1</v>
+        <v>5.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11764,7 +11764,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 14760-2025</t>
+          <t>A 57878-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45742</v>
+        <v>44899</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11837,7 +11837,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 34046-2024</t>
+          <t>A 14802-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45523</v>
+        <v>45014</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 24321-2025</t>
+          <t>A 2632-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11924,10 +11924,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45797</v>
+        <v>45313</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11983,7 +11983,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 44417-2024</t>
+          <t>A 33454-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45573</v>
+        <v>45130</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 44754-2024</t>
+          <t>A 37948-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45574</v>
+        <v>46280</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12129,7 +12129,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 27555-2025</t>
+          <t>A 22959-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12143,10 +12143,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45813</v>
+        <v>45790</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12202,7 +12202,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 54279-2024</t>
+          <t>A 14760-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12216,10 +12216,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45616</v>
+        <v>45742</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>6.9</v>
+        <v>4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12275,7 +12275,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33300-2025</t>
+          <t>A 9937-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12289,10 +12289,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45840</v>
+        <v>45718</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>6.4</v>
+        <v>2.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12348,7 +12348,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 33295-2025</t>
+          <t>A 13521-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45840</v>
+        <v>45736</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12421,7 +12421,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33299-2025</t>
+          <t>A 13536-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45840</v>
+        <v>45736</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 34502-2025</t>
+          <t>A 24321-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12508,10 +12508,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45847</v>
+        <v>45797</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 36722-2025</t>
+          <t>A 34046-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12581,10 +12581,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45872</v>
+        <v>45523</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12657,7 +12657,7 @@
         <v>45937</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>

--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 74306-2021</t>
+          <t>A 49930-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44559</v>
+        <v>45597</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -727,45 +727,269 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.6</v>
+        <v>16.6</v>
       </c>
       <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
       </c>
       <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Svart trolldruva
+Revlummer
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 14805-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
         <v>4</v>
       </c>
-      <c r="U3" t="n">
+      <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönsångare
+Kambräken
+Purpurmylia</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 74306-2021</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44559</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
         <v>4</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Dvärglin
 Kösa
@@ -773,223 +997,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 74306-2021 artfynd.xlsx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 74306-2021 karta.png", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 74306-2021 georefererad karta.tif", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 74306-2021 FSC-klagomål.docx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 74306-2021 FSC-klagomål mail.docx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 74306-2021 tillsynsbegäran.docx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 74306-2021 tillsynsbegäran mail.docx", "A 74306-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 14805-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 65099-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45288</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>2</v>
       </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="n">
-        <v>6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>6</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönsångare
-Kambräken
-Purpurmylia</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 65099-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45288</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="T6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Blockskapania
 Knärot
@@ -997,144 +1105,36 @@
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 49930-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45597</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Svart trolldruva
-Revlummer
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
         <v/>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
         <v>44546</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45336</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 63419-2023</t>
+          <t>A 1663-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45274</v>
+        <v>45306</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1432,156 +1432,156 @@
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Blåbär
+Sälg
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 1663-2024 artfynd.xlsx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 1663-2024 karta.png", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 1663-2024 georefererad karta.tif", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 1663-2024 FSC-klagomål.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 1663-2024 FSC-klagomål mail.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 1663-2024 tillsynsbegäran.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 1663-2024 tillsynsbegäran mail.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 63419-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45274</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Björktrast
 Rödvingetrast
 Gröngöling</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 1663-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Blåbär
-Sälg
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 1663-2024 artfynd.xlsx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 1663-2024 karta.png", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 1663-2024 georefererad karta.tif", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 1663-2024 FSC-klagomål.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 1663-2024 FSC-klagomål mail.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 1663-2024 tillsynsbegäran.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 1663-2024 tillsynsbegäran mail.docx", "A 1663-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 40270-2024</t>
+          <t>A 13220-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45554</v>
+        <v>45386</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1644,10 +1644,10 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1655,42 +1655,42 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 56035-2025</t>
+          <t>A 24618-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1700,14 +1700,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45973</v>
+        <v>45460</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>15.9</v>
+        <v>9.5</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1732,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1744,62 +1744,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 6986-2024</t>
+          <t>A 12722-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1813,10 +1809,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45343</v>
+        <v>46091</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1829,7 +1825,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1841,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1853,10 +1849,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1865,46 +1861,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 12722-2026</t>
+          <t>A 771-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46091</v>
+        <v>44931</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1958,10 +1958,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1974,46 +1974,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 49047-2025</t>
+          <t>A 5634-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45937</v>
+        <v>45693</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2043,19 +2043,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2070,55 +2070,59 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <v/>
+      </c>
+      <c r="Z15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 771-2023</t>
+          <t>A 49047-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2132,10 +2136,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44931</v>
+        <v>45937</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2148,17 +2152,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2172,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2188,46 +2192,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13220-2024</t>
+          <t>A 5617-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45386</v>
+        <v>45334</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2290,10 +2290,10 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
@@ -2301,42 +2301,42 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Z17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24618-2024</t>
+          <t>A 44233-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45460</v>
+        <v>45183</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>9.5</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2390,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2406,42 +2406,46 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
+        <v/>
+      </c>
+      <c r="Z18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20709-2023</t>
+          <t>A 23921-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2455,10 +2459,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45058</v>
+        <v>46167</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2471,19 +2475,19 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2495,62 +2499,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
-        <v/>
-      </c>
-      <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 5617-2024</t>
+          <t>A 31028-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45334</v>
+        <v>46213</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2580,19 +2580,19 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2604,10 +2604,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2616,50 +2616,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23921-2026</t>
+          <t>A 41056-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2673,10 +2669,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46167</v>
+        <v>45898</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2689,7 +2685,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2729,42 +2725,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 44233-2023</t>
+          <t>A 6986-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2778,10 +2774,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45183</v>
+        <v>45343</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2794,7 +2790,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2806,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2818,10 +2814,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2830,50 +2826,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
-        <v/>
-      </c>
-      <c r="Z22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31028-2026</t>
+          <t>A 20086-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2887,10 +2879,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46213</v>
+        <v>45054</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2903,20 +2895,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -2927,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2939,46 +2931,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
+        <v/>
+      </c>
+      <c r="Z23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 5634-2025</t>
+          <t>A 56035-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2988,14 +2984,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45693</v>
+        <v>45973</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3008,7 +3004,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>15.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3041,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -3052,42 +3048,42 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41056-2025</t>
+          <t>A 20709-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3101,10 +3097,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45898</v>
+        <v>45058</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3117,20 +3113,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3141,58 +3137,62 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20086-2023</t>
+          <t>A 40270-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45054</v>
+        <v>45554</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3266,35 +3266,35 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
         <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44566</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44657</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62369-2023</t>
+          <t>A 34380-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45268</v>
+        <v>44792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34217-2022</t>
+          <t>A 59309-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44791</v>
+        <v>45253</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57877-2022</t>
+          <t>A 39206-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44899</v>
+        <v>45548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 36999-2023</t>
+          <t>A 23682-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45155</v>
+        <v>45454</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22750-2024</t>
+          <t>A 5714-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45448</v>
+        <v>45334</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19005-2023</t>
+          <t>A 28109-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45045</v>
+        <v>45476</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59309-2023</t>
+          <t>A 55777-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45253</v>
+        <v>44888</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55777-2022</t>
+          <t>A 49822-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44888</v>
+        <v>44862</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 44754-2024</t>
+          <t>A 22750-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45574</v>
+        <v>45448</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 44417-2024</t>
+          <t>A 57878-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45573</v>
+        <v>44899</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5121,7 +5121,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27555-2025</t>
+          <t>A 49115-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45813</v>
+        <v>45594</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43752-2023</t>
+          <t>A 30440-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45187</v>
+        <v>45491</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>9.300000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30440-2024</t>
+          <t>A 40743-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45491</v>
+        <v>45558</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54279-2024</t>
+          <t>A 62516-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45616</v>
+        <v>44924</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 41063-2025</t>
+          <t>A 8457-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45898</v>
+        <v>46065</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47884-2024</t>
+          <t>A 49617-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45588</v>
+        <v>45211</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5559,7 +5559,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 41881-2025</t>
+          <t>A 1288-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45903</v>
+        <v>45667</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 49115-2024</t>
+          <t>A 9344-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45594</v>
+        <v>46070</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 42457-2025</t>
+          <t>A 9194-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45905</v>
+        <v>46070</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2435-2026</t>
+          <t>A 10118-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46036</v>
+        <v>46075</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 2436-2026</t>
+          <t>A 20131-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46036</v>
+        <v>45772</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33300-2025</t>
+          <t>A 51993-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45840</v>
+        <v>44872</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33295-2025</t>
+          <t>A 12087-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45840</v>
+        <v>46086</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>7.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33299-2025</t>
+          <t>A 33300-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6087,7 +6087,7 @@
         <v>45840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34502-2025</t>
+          <t>A 33295-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 71890-2021</t>
+          <t>A 33299-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44543</v>
+        <v>45840</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 6957-2024</t>
+          <t>A 34502-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45343</v>
+        <v>45847</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 51993-2022</t>
+          <t>A 34354-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44872</v>
+        <v>45139</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6435,7 +6435,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13378-2023</t>
+          <t>A 33454-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45005</v>
+        <v>45130</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6508,7 +6508,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 48419-2025</t>
+          <t>A 36722-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45934</v>
+        <v>45872</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>7.7</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 36722-2025</t>
+          <t>A 38322-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45872</v>
+        <v>45161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6654,7 +6654,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25925-2024</t>
+          <t>A 17426-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45467</v>
+        <v>46120</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 49365-2025</t>
+          <t>A 50532-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45938</v>
+        <v>45601</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4114-2026</t>
+          <t>A 41063-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46044</v>
+        <v>45898</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50532-2024</t>
+          <t>A 18431-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45601</v>
+        <v>46127</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 1288-2025</t>
+          <t>A 47884-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45667</v>
+        <v>45588</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6739-2026</t>
+          <t>A 57445-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46056</v>
+        <v>45629</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8457-2026</t>
+          <t>A 41881-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46065</v>
+        <v>45903</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7165,7 +7165,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 62516-2022</t>
+          <t>A 42457-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44924</v>
+        <v>45905</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 9194-2026</t>
+          <t>A 56496-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46070</v>
+        <v>44480</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>10.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9344-2026</t>
+          <t>A 40328-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46070</v>
+        <v>45895</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10118-2026</t>
+          <t>A 27277-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46075</v>
+        <v>45812</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58853-2025</t>
+          <t>A 23258-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45987</v>
+        <v>45791</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7530,7 +7530,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58852-2025</t>
+          <t>A 33296-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45987</v>
+        <v>45840</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5926-2024</t>
+          <t>A 14802-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45336</v>
+        <v>45014</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 59834-2025</t>
+          <t>A 34500-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45992</v>
+        <v>45847</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 12087-2026</t>
+          <t>A 68727-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46086</v>
+        <v>44529</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7.6</v>
+        <v>2.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 61319-2025</t>
+          <t>A 54128-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46000</v>
+        <v>45964</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20089-2025</t>
+          <t>A 36404-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45771</v>
+        <v>45535</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 61302-2024</t>
+          <t>A 20675-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45645</v>
+        <v>46141</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 5714-2024</t>
+          <t>A 20089-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45334</v>
+        <v>45771</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 34380-2022</t>
+          <t>A 48419-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44792</v>
+        <v>45934</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13377-2023</t>
+          <t>A 49365-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45005</v>
+        <v>45938</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 37130-2024</t>
+          <t>A 14609-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45539</v>
+        <v>45396</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 59915-2024</t>
+          <t>A 62086-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45641</v>
+        <v>44919</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 42712-2023</t>
+          <t>A 49072-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45181</v>
+        <v>45937</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17426-2026</t>
+          <t>A 6957-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46120</v>
+        <v>45343</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 50562-2024</t>
+          <t>A 2632-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45601</v>
+        <v>45313</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 18431-2026</t>
+          <t>A 24605-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46127</v>
+        <v>46170</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>4.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20131-2025</t>
+          <t>A 25123-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45772</v>
+        <v>46175</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 5454-2025</t>
+          <t>A 25138-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45692</v>
+        <v>46175</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 40722-2024</t>
+          <t>A 32175-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45558</v>
+        <v>45511</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 36404-2024</t>
+          <t>A 63626-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45535</v>
+        <v>45275</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 57445-2024</t>
+          <t>A 37130-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45629</v>
+        <v>45539</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 23258-2025</t>
+          <t>A 25963-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45791</v>
+        <v>46181</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 34500-2025</t>
+          <t>A 5926-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45847</v>
+        <v>45336</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 27277-2025</t>
+          <t>A 20819-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45812</v>
+        <v>45058</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 40328-2025</t>
+          <t>A 43752-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45895</v>
+        <v>45187</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33296-2025</t>
+          <t>A 33789-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45840</v>
+        <v>46251</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56496-2021</t>
+          <t>A 34217-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44480</v>
+        <v>44791</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>10.3</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 49822-2022</t>
+          <t>A 58852-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44862</v>
+        <v>45987</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 68727-2021</t>
+          <t>A 58853-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44529</v>
+        <v>45987</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 20675-2026</t>
+          <t>A 59834-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46141</v>
+        <v>45992</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 54128-2025</t>
+          <t>A 31029-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45964</v>
+        <v>46213</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 38322-2023</t>
+          <t>A 61319-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45161</v>
+        <v>46000</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 40743-2024</t>
+          <t>A 5715-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45558</v>
+        <v>45334</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 14609-2024</t>
+          <t>A 36428-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9953,10 +9953,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45396</v>
+        <v>46269</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 20819-2023</t>
+          <t>A 5454-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45058</v>
+        <v>45692</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10085,7 +10085,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 34354-2023</t>
+          <t>A 19005-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45139</v>
+        <v>45045</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10158,7 +10158,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 24605-2026</t>
+          <t>A 34056-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10172,10 +10172,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46170</v>
+        <v>45523</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10231,7 +10231,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 49072-2025</t>
+          <t>A 59915-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45937</v>
+        <v>45641</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10304,7 +10304,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 25123-2026</t>
+          <t>A 57877-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10318,10 +10318,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46175</v>
+        <v>44899</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10377,7 +10377,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 25138-2026</t>
+          <t>A 13378-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46175</v>
+        <v>45005</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 6485-2024</t>
+          <t>A 37948-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45339</v>
+        <v>46280</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 25963-2026</t>
+          <t>A 25925-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46181</v>
+        <v>45467</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10596,7 +10596,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 49617-2023</t>
+          <t>A 2435-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45211</v>
+        <v>46036</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10669,7 +10669,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 23682-2024</t>
+          <t>A 2436-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45454</v>
+        <v>46036</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10742,7 +10742,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 39206-2024</t>
+          <t>A 34155-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10756,10 +10756,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45548</v>
+        <v>45524</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10815,7 +10815,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 5715-2024</t>
+          <t>A 18791-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10829,10 +10829,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45334</v>
+        <v>45044</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 34056-2024</t>
+          <t>A 4114-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45523</v>
+        <v>46044</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.8</v>
+        <v>7.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10961,7 +10961,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 33789-2026</t>
+          <t>A 42712-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46251</v>
+        <v>45181</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11034,7 +11034,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 14547-2022</t>
+          <t>A 6739-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11048,10 +11048,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44655</v>
+        <v>46056</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11107,7 +11107,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 18791-2023</t>
+          <t>A 71890-2021</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11121,10 +11121,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45044</v>
+        <v>44543</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 28109-2024</t>
+          <t>A 46708-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45476</v>
+        <v>45198</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11253,7 +11253,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 31029-2026</t>
+          <t>A 40722-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11267,10 +11267,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46213</v>
+        <v>45558</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 63626-2023</t>
+          <t>A 62369-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11340,10 +11340,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45275</v>
+        <v>45268</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11399,7 +11399,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 32175-2024</t>
+          <t>A 14547-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45511</v>
+        <v>44655</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11472,7 +11472,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 34155-2024</t>
+          <t>A 6485-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11486,10 +11486,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45524</v>
+        <v>45339</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11545,7 +11545,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 46708-2023</t>
+          <t>A 13377-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11559,10 +11559,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45198</v>
+        <v>45005</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11618,7 +11618,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 62086-2022</t>
+          <t>A 61302-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11632,10 +11632,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44919</v>
+        <v>45645</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11691,7 +11691,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 36428-2026</t>
+          <t>A 50562-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11705,10 +11705,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46269</v>
+        <v>45601</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11764,7 +11764,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 57878-2022</t>
+          <t>A 36999-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44899</v>
+        <v>45155</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11837,7 +11837,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 14802-2023</t>
+          <t>A 22959-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45014</v>
+        <v>45790</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 2632-2024</t>
+          <t>A 9937-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11924,10 +11924,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45313</v>
+        <v>45718</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>8.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11983,7 +11983,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 33454-2023</t>
+          <t>A 13521-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45130</v>
+        <v>45736</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 37948-2026</t>
+          <t>A 13536-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46280</v>
+        <v>45736</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.4</v>
+        <v>0.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12129,7 +12129,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 22959-2025</t>
+          <t>A 14760-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12143,10 +12143,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45790</v>
+        <v>45742</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12202,7 +12202,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 14760-2025</t>
+          <t>A 34046-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12216,10 +12216,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45742</v>
+        <v>45523</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12275,7 +12275,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 9937-2025</t>
+          <t>A 24321-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12289,10 +12289,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45718</v>
+        <v>45797</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12348,7 +12348,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 13521-2025</t>
+          <t>A 44417-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45736</v>
+        <v>45573</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12421,7 +12421,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 13536-2025</t>
+          <t>A 44754-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45736</v>
+        <v>45574</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 24321-2025</t>
+          <t>A 27555-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12508,10 +12508,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45797</v>
+        <v>45813</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12567,7 +12567,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 34046-2024</t>
+          <t>A 54279-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12581,10 +12581,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45523</v>
+        <v>45616</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.2</v>
+        <v>6.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12657,7 +12657,7 @@
         <v>45937</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>

--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49930-2024</t>
+          <t>A 74306-2021</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45597</v>
+        <v>44559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -727,45 +727,381 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>16.6</v>
+        <v>14.6</v>
       </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
         <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
       </c>
       <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Dvärglin
+Kösa
+Åkerrödtoppa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 74306-2021 artfynd.xlsx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 74306-2021 karta.png", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 74306-2021 georefererad karta.tif", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 74306-2021 FSC-klagomål.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 74306-2021 FSC-klagomål mail.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 74306-2021 tillsynsbegäran.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 74306-2021 tillsynsbegäran mail.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 14805-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
         <v>6</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönsångare
+Kambräken
+Purpurmylia</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 65099-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45288</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Blockskapania
+Knärot
+Grov fjädermossa
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 49930-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Svart trolldruva
@@ -773,368 +1109,32 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 14805-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>6</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönsångare
-Kambräken
-Purpurmylia</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 74306-2021</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44559</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>4</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Dvärglin
-Kösa
-Åkerrödtoppa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 74306-2021 artfynd.xlsx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 74306-2021 karta.png", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 74306-2021 georefererad karta.tif", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 74306-2021 FSC-klagomål.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 74306-2021 FSC-klagomål mail.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 74306-2021 tillsynsbegäran.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 74306-2021 tillsynsbegäran mail.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 65099-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45288</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Blockskapania
-Knärot
-Grov fjädermossa
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
         <v/>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
         <v>44546</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45336</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1663-2024</t>
+          <t>A 63419-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45306</v>
+        <v>45274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1432,156 +1432,156 @@
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Björktrast
+Rödvingetrast
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 1663-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45306</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Blåbär
 Sälg
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 1663-2024 artfynd.xlsx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 1663-2024 karta.png", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 1663-2024 georefererad karta.tif", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 1663-2024 FSC-klagomål.docx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 1663-2024 FSC-klagomål mail.docx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 1663-2024 tillsynsbegäran.docx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 1663-2024 tillsynsbegäran mail.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 63419-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45274</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Björktrast
-Rödvingetrast
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13220-2024</t>
+          <t>A 40270-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45386</v>
+        <v>45554</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1644,10 +1644,10 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1655,42 +1655,42 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 24618-2024</t>
+          <t>A 6986-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45460</v>
+        <v>45343</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1756,46 +1756,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12722-2026</t>
+          <t>A 49047-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46091</v>
+        <v>45937</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1825,19 +1825,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1865,39 +1865,35 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
     </row>
@@ -1921,7 +1917,7 @@
         <v>44931</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2013,7 +2009,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 5634-2025</t>
+          <t>A 13220-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2027,10 +2023,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45693</v>
+        <v>45386</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2043,7 +2039,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2087,42 +2083,42 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Z15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 49047-2025</t>
+          <t>A 56035-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2132,14 +2128,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45937</v>
+        <v>45973</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,19 +2148,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>15.9</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2179,55 +2175,59 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
+        <v/>
+      </c>
+      <c r="Z16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 5617-2024</t>
+          <t>A 24618-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45334</v>
+        <v>45460</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2293,50 +2293,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
-        <v/>
-      </c>
-      <c r="Z17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 44233-2023</t>
+          <t>A 20709-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2350,10 +2346,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45183</v>
+        <v>45058</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2366,7 +2362,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2399,10 +2395,10 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
@@ -2410,42 +2406,42 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Z18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 23921-2026</t>
+          <t>A 12722-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2459,10 +2455,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46167</v>
+        <v>46091</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2475,20 +2471,20 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
@@ -2499,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2515,42 +2511,46 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31028-2026</t>
+          <t>A 5617-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46213</v>
+        <v>45334</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2580,20 +2580,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -2604,10 +2604,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2616,46 +2616,50 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 41056-2025</t>
+          <t>A 44233-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2669,10 +2673,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45898</v>
+        <v>45183</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2685,20 +2689,20 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
@@ -2709,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2725,42 +2729,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
+        <v/>
+      </c>
+      <c r="Z21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 6986-2024</t>
+          <t>A 5634-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2774,10 +2782,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45343</v>
+        <v>45693</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2790,7 +2798,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2802,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2814,58 +2822,62 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <v/>
+      </c>
+      <c r="Z22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 20086-2023</t>
+          <t>A 23921-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2879,10 +2891,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45054</v>
+        <v>46167</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2895,19 +2907,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2919,10 +2931,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2931,50 +2943,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
-        <v/>
-      </c>
-      <c r="Z23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 56035-2025</t>
+          <t>A 20086-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2984,14 +2992,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45973</v>
+        <v>45054</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3004,7 +3012,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>15.9</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3037,10 +3045,10 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
@@ -3048,42 +3056,42 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20709-2023</t>
+          <t>A 31028-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3097,10 +3105,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45058</v>
+        <v>46213</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3113,19 +3121,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3137,62 +3145,58 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 40270-2024</t>
+          <t>A 41056-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3206,10 +3210,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45554</v>
+        <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3222,19 +3226,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3246,10 +3250,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3258,43 +3262,39 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
-        <v/>
-      </c>
-      <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
         <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44566</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44657</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34380-2022</t>
+          <t>A 62369-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44792</v>
+        <v>45268</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59309-2023</t>
+          <t>A 34217-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45253</v>
+        <v>44791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39206-2024</t>
+          <t>A 57877-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45548</v>
+        <v>44899</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23682-2024</t>
+          <t>A 22750-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45454</v>
+        <v>45448</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 5714-2024</t>
+          <t>A 36999-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45334</v>
+        <v>45155</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28109-2024</t>
+          <t>A 19005-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45476</v>
+        <v>45045</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55777-2022</t>
+          <t>A 59309-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44888</v>
+        <v>45253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 49822-2022</t>
+          <t>A 55777-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44862</v>
+        <v>44888</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22750-2024</t>
+          <t>A 30440-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45448</v>
+        <v>45491</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57878-2022</t>
+          <t>A 43752-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44899</v>
+        <v>45187</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5138,7 +5138,7 @@
         <v>45594</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 30440-2024</t>
+          <t>A 6957-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45491</v>
+        <v>45343</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 40743-2024</t>
+          <t>A 71890-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45558</v>
+        <v>44543</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62516-2022</t>
+          <t>A 13378-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44924</v>
+        <v>45005</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8457-2026</t>
+          <t>A 51993-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46065</v>
+        <v>44872</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 49617-2023</t>
+          <t>A 25925-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45211</v>
+        <v>45467</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5559,7 +5559,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1288-2025</t>
+          <t>A 62516-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45667</v>
+        <v>44924</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9344-2026</t>
+          <t>A 23258-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46070</v>
+        <v>45791</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9194-2026</t>
+          <t>A 34500-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46070</v>
+        <v>45847</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10118-2026</t>
+          <t>A 5926-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46075</v>
+        <v>45336</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20131-2025</t>
+          <t>A 27277-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45772</v>
+        <v>45812</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51993-2022</t>
+          <t>A 40328-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44872</v>
+        <v>45895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12087-2026</t>
+          <t>A 20089-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46086</v>
+        <v>45771</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.6</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33300-2025</t>
+          <t>A 41063-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45840</v>
+        <v>45898</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 33295-2025</t>
+          <t>A 47884-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45840</v>
+        <v>45588</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33299-2025</t>
+          <t>A 41881-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45840</v>
+        <v>45903</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34502-2025</t>
+          <t>A 61302-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45847</v>
+        <v>45645</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34354-2023</t>
+          <t>A 33296-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45139</v>
+        <v>45840</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6435,7 +6435,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 33454-2023</t>
+          <t>A 56496-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45130</v>
+        <v>44480</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6</v>
+        <v>10.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6508,7 +6508,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36722-2025</t>
+          <t>A 42457-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45872</v>
+        <v>45905</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38322-2023</t>
+          <t>A 68727-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45161</v>
+        <v>44529</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6654,7 +6654,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17426-2026</t>
+          <t>A 5714-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46120</v>
+        <v>45334</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50532-2024</t>
+          <t>A 20675-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45601</v>
+        <v>46141</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 41063-2025</t>
+          <t>A 34380-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45898</v>
+        <v>44792</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18431-2026</t>
+          <t>A 54128-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46127</v>
+        <v>45964</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 47884-2024</t>
+          <t>A 13377-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45588</v>
+        <v>45005</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 57445-2024</t>
+          <t>A 37130-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45629</v>
+        <v>45539</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 41881-2025</t>
+          <t>A 59915-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45903</v>
+        <v>45641</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7165,7 +7165,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42457-2025</t>
+          <t>A 48419-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45905</v>
+        <v>45934</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56496-2021</t>
+          <t>A 49365-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44480</v>
+        <v>45938</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>10.3</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 40328-2025</t>
+          <t>A 42712-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45895</v>
+        <v>45181</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 27277-2025</t>
+          <t>A 50562-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45812</v>
+        <v>45601</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 23258-2025</t>
+          <t>A 20131-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45791</v>
+        <v>45772</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 33296-2025</t>
+          <t>A 5454-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45840</v>
+        <v>45692</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 14802-2023</t>
+          <t>A 40722-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45014</v>
+        <v>45558</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34500-2025</t>
+          <t>A 36404-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45847</v>
+        <v>45535</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 68727-2021</t>
+          <t>A 57445-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44529</v>
+        <v>45629</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 54128-2025</t>
+          <t>A 58853-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45964</v>
+        <v>45987</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 36404-2024</t>
+          <t>A 58852-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45535</v>
+        <v>45987</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 20675-2026</t>
+          <t>A 14609-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46141</v>
+        <v>45396</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20089-2025</t>
+          <t>A 49822-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45771</v>
+        <v>44862</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48419-2025</t>
+          <t>A 59834-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45934</v>
+        <v>45992</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7.7</v>
+        <v>3.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 49365-2025</t>
+          <t>A 61319-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45938</v>
+        <v>46000</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 14609-2024</t>
+          <t>A 38322-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45396</v>
+        <v>45161</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 62086-2022</t>
+          <t>A 40743-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44919</v>
+        <v>45558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 49072-2025</t>
+          <t>A 24605-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45937</v>
+        <v>46170</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 6957-2024</t>
+          <t>A 49072-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45343</v>
+        <v>45937</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 2632-2024</t>
+          <t>A 2435-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45313</v>
+        <v>46036</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 24605-2026</t>
+          <t>A 2436-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46170</v>
+        <v>46036</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 25123-2026</t>
+          <t>A 4114-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46175</v>
+        <v>46044</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.2</v>
+        <v>7.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 25138-2026</t>
+          <t>A 20819-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46175</v>
+        <v>45058</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 32175-2024</t>
+          <t>A 25123-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45511</v>
+        <v>46175</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 63626-2023</t>
+          <t>A 25138-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45275</v>
+        <v>46175</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37130-2024</t>
+          <t>A 34354-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45539</v>
+        <v>45139</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25963-2026</t>
+          <t>A 6739-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46181</v>
+        <v>46056</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 5926-2024</t>
+          <t>A 8457-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45336</v>
+        <v>46065</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20819-2023</t>
+          <t>A 25963-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45058</v>
+        <v>46181</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 43752-2023</t>
+          <t>A 9194-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45187</v>
+        <v>46070</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>9.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33789-2026</t>
+          <t>A 9344-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46251</v>
+        <v>46070</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 34217-2022</t>
+          <t>A 6485-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44791</v>
+        <v>45339</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 58852-2025</t>
+          <t>A 10118-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45987</v>
+        <v>46075</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 58853-2025</t>
+          <t>A 49617-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45987</v>
+        <v>45211</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 59834-2025</t>
+          <t>A 12087-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45992</v>
+        <v>46086</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 31029-2026</t>
+          <t>A 23682-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46213</v>
+        <v>45454</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61319-2025</t>
+          <t>A 39206-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46000</v>
+        <v>45548</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9883,7 +9883,7 @@
         <v>45334</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 36428-2026</t>
+          <t>A 17426-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9953,10 +9953,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46269</v>
+        <v>46120</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 5454-2025</t>
+          <t>A 34056-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45692</v>
+        <v>45523</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10085,7 +10085,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 19005-2023</t>
+          <t>A 18431-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45045</v>
+        <v>46127</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10158,7 +10158,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 34056-2024</t>
+          <t>A 14547-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10172,10 +10172,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45523</v>
+        <v>44655</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10231,7 +10231,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 59915-2024</t>
+          <t>A 18791-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45641</v>
+        <v>45044</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10304,7 +10304,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 57877-2022</t>
+          <t>A 28109-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10318,10 +10318,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44899</v>
+        <v>45476</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10377,7 +10377,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 13378-2023</t>
+          <t>A 33789-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45005</v>
+        <v>46251</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 37948-2026</t>
+          <t>A 63626-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46280</v>
+        <v>45275</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 25925-2024</t>
+          <t>A 32175-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45467</v>
+        <v>45511</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10596,7 +10596,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 2435-2026</t>
+          <t>A 34155-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46036</v>
+        <v>45524</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10669,7 +10669,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 2436-2026</t>
+          <t>A 46708-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46036</v>
+        <v>45198</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10742,7 +10742,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 34155-2024</t>
+          <t>A 62086-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10756,10 +10756,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45524</v>
+        <v>44919</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10815,7 +10815,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 18791-2023</t>
+          <t>A 31029-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10829,10 +10829,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45044</v>
+        <v>46213</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 4114-2026</t>
+          <t>A 57878-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46044</v>
+        <v>44899</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>7.1</v>
+        <v>4.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10961,7 +10961,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 42712-2023</t>
+          <t>A 14802-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45181</v>
+        <v>45014</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11034,7 +11034,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 6739-2026</t>
+          <t>A 2632-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11048,10 +11048,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46056</v>
+        <v>45313</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11107,7 +11107,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 71890-2021</t>
+          <t>A 33454-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11121,10 +11121,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44543</v>
+        <v>45130</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 46708-2023</t>
+          <t>A 36428-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45198</v>
+        <v>46269</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11253,7 +11253,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 40722-2024</t>
+          <t>A 22959-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11267,10 +11267,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45558</v>
+        <v>45790</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 62369-2023</t>
+          <t>A 37948-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11340,10 +11340,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45268</v>
+        <v>46280</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11399,7 +11399,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 14547-2022</t>
+          <t>A 14760-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44655</v>
+        <v>45742</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11472,7 +11472,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 6485-2024</t>
+          <t>A 9937-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11486,10 +11486,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45339</v>
+        <v>45718</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11545,7 +11545,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 13377-2023</t>
+          <t>A 13521-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11559,10 +11559,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45005</v>
+        <v>45736</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11618,7 +11618,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 61302-2024</t>
+          <t>A 13536-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11632,10 +11632,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45645</v>
+        <v>45736</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11691,7 +11691,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 50562-2024</t>
+          <t>A 24321-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11705,10 +11705,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45601</v>
+        <v>45797</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11764,7 +11764,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 36999-2023</t>
+          <t>A 34046-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45155</v>
+        <v>45523</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11837,7 +11837,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 22959-2025</t>
+          <t>A 44754-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45790</v>
+        <v>45574</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 9937-2025</t>
+          <t>A 44417-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11924,10 +11924,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45718</v>
+        <v>45573</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11983,7 +11983,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 13521-2025</t>
+          <t>A 27555-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45736</v>
+        <v>45813</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 13536-2025</t>
+          <t>A 54279-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45736</v>
+        <v>45616</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.1</v>
+        <v>6.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12129,7 +12129,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 14760-2025</t>
+          <t>A 33300-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12143,10 +12143,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45742</v>
+        <v>45840</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12202,7 +12202,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 34046-2024</t>
+          <t>A 33295-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12216,10 +12216,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45523</v>
+        <v>45840</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12275,7 +12275,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 24321-2025</t>
+          <t>A 33299-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12289,10 +12289,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45797</v>
+        <v>45840</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12348,7 +12348,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 44417-2024</t>
+          <t>A 34502-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45573</v>
+        <v>45847</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12421,7 +12421,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 44754-2024</t>
+          <t>A 36722-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45574</v>
+        <v>45872</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 27555-2025</t>
+          <t>A 50532-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12508,10 +12508,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45813</v>
+        <v>45601</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12567,7 +12567,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 54279-2024</t>
+          <t>A 1288-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12581,10 +12581,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45616</v>
+        <v>45667</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>6.9</v>
+        <v>1.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12657,7 +12657,7 @@
         <v>45937</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>

--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>45014</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>45288</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45597</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44546</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45336</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>45306</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45554</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45343</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>45937</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>44931</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45386</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45973</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45460</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45058</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46091</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45334</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>45183</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>45693</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>46167</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45054</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>46213</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44566</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44657</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>45268</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>44791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>44899</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45448</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>45155</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>45045</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>45253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>44888</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45491</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>45187</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45594</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>45343</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>44543</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>45005</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>44872</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>45467</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>44924</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45791</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>45847</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>45336</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>45812</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>45771</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>45898</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>45588</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>45903</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>45645</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>45840</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44480</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45905</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44529</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>45334</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>46141</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>44792</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>45964</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45005</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>45539</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>45641</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>45934</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>45938</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>45181</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>45601</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>45772</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45692</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45558</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>45535</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45629</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>45987</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45987</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45396</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44862</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>45992</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>46000</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>45161</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>45558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>46170</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>45937</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>46036</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>46036</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>46044</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>45058</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>46175</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>46175</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45139</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>46056</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>46065</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>46181</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>46070</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>46070</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45339</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>46075</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45211</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>46086</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45454</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>45548</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45334</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>46120</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45523</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>46127</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>44655</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45044</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45476</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>46251</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45275</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45511</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45524</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45198</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>44919</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>46213</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44899</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45014</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45313</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45130</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>46269</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45790</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>46280</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45742</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45718</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45736</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45736</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45797</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45523</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45574</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45573</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45813</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45616</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45840</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45840</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45840</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45847</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45872</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45601</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45667</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45937</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>

--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE154"/>
+  <dimension ref="A1:AE153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>45014</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>45288</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45597</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 72588-2021</t>
+          <t>A 6055-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44546</v>
+        <v>45336</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1171,19 +1171,19 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>21.8</v>
+        <v>24.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1195,168 +1195,168 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
       </c>
       <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)
+Revlummer
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6055-2024 artfynd.xlsx", "A 6055-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6055-2024 karta.png", "A 6055-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6055-2024 georefererad karta.tif", "A 6055-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6055-2024 FSC-klagomål.docx", "A 6055-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6055-2024 FSC-klagomål mail.docx", "A 6055-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6055-2024 tillsynsbegäran.docx", "A 6055-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6055-2024 tillsynsbegäran mail.docx", "A 6055-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 72588-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44546</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Kambräken
 Spillkråka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 72588-2021 artfynd.xlsx", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 72588-2021 karta.png", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 72588-2021 georefererad karta.tif", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 72588-2021 karta knärot.png", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 72588-2021 FSC-klagomål.docx", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 72588-2021 FSC-klagomål mail.docx", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 72588-2021 tillsynsbegäran.docx", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 72588-2021 tillsynsbegäran mail.docx", "A 72588-2021")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 72588-2021 prioriterade fågelarter.docx", "A 72588-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 6055-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45336</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)
-Revlummer
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6055-2024 artfynd.xlsx", "A 6055-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6055-2024 karta.png", "A 6055-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6055-2024 georefererad karta.tif", "A 6055-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6055-2024 FSC-klagomål.docx", "A 6055-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6055-2024 FSC-klagomål mail.docx", "A 6055-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6055-2024 tillsynsbegäran.docx", "A 6055-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6055-2024 tillsynsbegäran mail.docx", "A 6055-2024")</f>
         <v/>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>45274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>45306</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45554</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 6986-2024</t>
+          <t>A 49047-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45343</v>
+        <v>45937</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1720,17 +1720,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1756,46 +1756,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 49047-2025</t>
+          <t>A 6986-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45937</v>
+        <v>45343</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1825,16 +1825,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1861,46 +1861,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 771-2023</t>
+          <t>A 56035-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1910,14 +1910,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44931</v>
+        <v>45973</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>15.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1954,62 +1954,62 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 13220-2024</t>
+          <t>A 771-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45386</v>
+        <v>44931</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2051,7 +2051,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2063,62 +2063,62 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
-        <v/>
-      </c>
-      <c r="Z15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 56035-2025</t>
+          <t>A 12722-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2128,14 +2128,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45973</v>
+        <v>46091</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>15.9</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2181,7 +2181,7 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2192,42 +2192,42 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24618-2024</t>
+          <t>A 13220-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45460</v>
+        <v>45386</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>9.5</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2281,58 +2281,62 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
+        <v/>
+      </c>
+      <c r="Z17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20709-2023</t>
+          <t>A 24618-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2346,10 +2350,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45058</v>
+        <v>45460</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2362,7 +2366,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.3</v>
+        <v>9.5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2374,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2386,62 +2390,58 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
-        <v/>
-      </c>
-      <c r="Z18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12722-2026</t>
+          <t>A 20709-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46091</v>
+        <v>45058</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2504,10 +2504,10 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
@@ -2515,42 +2515,42 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 5617-2024</t>
+          <t>A 23921-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45334</v>
+        <v>46167</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2580,19 +2580,19 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2604,10 +2604,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2616,50 +2616,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 44233-2023</t>
+          <t>A 5617-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2673,10 +2669,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45183</v>
+        <v>45334</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2689,7 +2685,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2725,7 +2721,7 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
@@ -2733,42 +2729,42 @@
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Z21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 5634-2025</t>
+          <t>A 31028-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2782,10 +2778,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45693</v>
+        <v>46213</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2798,19 +2794,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2822,62 +2818,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
-        <v/>
-      </c>
-      <c r="Z22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23921-2026</t>
+          <t>A 41056-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2891,10 +2883,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46167</v>
+        <v>45898</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2907,7 +2899,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2947,42 +2939,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20086-2023</t>
+          <t>A 44233-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2996,10 +2988,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45054</v>
+        <v>45183</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3012,7 +3004,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3048,7 +3040,7 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
@@ -3056,42 +3048,42 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31028-2026</t>
+          <t>A 5634-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3105,10 +3097,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46213</v>
+        <v>45693</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3121,20 +3113,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3145,58 +3137,62 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41056-2025</t>
+          <t>A 20086-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3210,10 +3206,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45898</v>
+        <v>45054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3226,20 +3222,20 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
@@ -3250,10 +3246,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3262,39 +3258,43 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
+        <v/>
+      </c>
+      <c r="Z26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
         <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44566</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44657</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>45268</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>44791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>44899</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45448</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>45155</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>45045</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>45253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>44888</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30440-2024</t>
+          <t>A 43752-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45491</v>
+        <v>45187</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43752-2023</t>
+          <t>A 30440-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45187</v>
+        <v>45491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>9.300000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5138,7 +5138,7 @@
         <v>45594</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>45343</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>44543</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>45005</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>44872</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>45467</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62516-2022</t>
+          <t>A 50532-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44924</v>
+        <v>45601</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23258-2025</t>
+          <t>A 1288-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45791</v>
+        <v>45667</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34500-2025</t>
+          <t>A 23258-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45847</v>
+        <v>45791</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 5926-2024</t>
+          <t>A 62516-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45336</v>
+        <v>44924</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 27277-2025</t>
+          <t>A 34500-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45812</v>
+        <v>45847</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>7.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 40328-2025</t>
+          <t>A 41063-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45895</v>
+        <v>45898</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20089-2025</t>
+          <t>A 47884-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45771</v>
+        <v>45588</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 41063-2025</t>
+          <t>A 41881-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45898</v>
+        <v>45903</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 47884-2024</t>
+          <t>A 27277-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45588</v>
+        <v>45812</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 41881-2025</t>
+          <t>A 42457-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45903</v>
+        <v>45905</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 61302-2024</t>
+          <t>A 40328-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45645</v>
+        <v>45895</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6379,7 +6379,7 @@
         <v>45840</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44480</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42457-2025</t>
+          <t>A 68727-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45905</v>
+        <v>44529</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 68727-2021</t>
+          <t>A 5926-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44529</v>
+        <v>45336</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6654,7 +6654,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5714-2024</t>
+          <t>A 20675-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45334</v>
+        <v>46141</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20675-2026</t>
+          <t>A 48419-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46141</v>
+        <v>45934</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>7.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34380-2022</t>
+          <t>A 54128-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44792</v>
+        <v>45964</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54128-2025</t>
+          <t>A 20089-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45964</v>
+        <v>45771</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13377-2023</t>
+          <t>A 61302-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45005</v>
+        <v>45645</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37130-2024</t>
+          <t>A 49365-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45539</v>
+        <v>45938</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 59915-2024</t>
+          <t>A 5714-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45641</v>
+        <v>45334</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48419-2025</t>
+          <t>A 34380-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45934</v>
+        <v>44792</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.7</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 49365-2025</t>
+          <t>A 14609-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45938</v>
+        <v>45396</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 42712-2023</t>
+          <t>A 13377-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45181</v>
+        <v>45005</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 50562-2024</t>
+          <t>A 37130-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45601</v>
+        <v>45539</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20131-2025</t>
+          <t>A 59915-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45772</v>
+        <v>45641</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7530,7 +7530,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 5454-2025</t>
+          <t>A 42712-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45692</v>
+        <v>45181</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 40722-2024</t>
+          <t>A 50562-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45558</v>
+        <v>45601</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 36404-2024</t>
+          <t>A 58853-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45535</v>
+        <v>45987</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 57445-2024</t>
+          <t>A 58852-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45629</v>
+        <v>45987</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58853-2025</t>
+          <t>A 24605-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45987</v>
+        <v>46170</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58852-2025</t>
+          <t>A 49072-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45987</v>
+        <v>45937</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 14609-2024</t>
+          <t>A 20131-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45396</v>
+        <v>45772</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 49822-2022</t>
+          <t>A 59834-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44862</v>
+        <v>45992</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 59834-2025</t>
+          <t>A 5454-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45992</v>
+        <v>45692</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
         <v>46000</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 38322-2023</t>
+          <t>A 25123-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45161</v>
+        <v>46175</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 40743-2024</t>
+          <t>A 25138-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45558</v>
+        <v>46175</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24605-2026</t>
+          <t>A 40722-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46170</v>
+        <v>45558</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 49072-2025</t>
+          <t>A 36404-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45937</v>
+        <v>45535</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 2435-2026</t>
+          <t>A 57445-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46036</v>
+        <v>45629</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 2436-2026</t>
+          <t>A 25963-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46036</v>
+        <v>46181</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 4114-2026</t>
+          <t>A 49822-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46044</v>
+        <v>44862</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20819-2023</t>
+          <t>A 2435-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45058</v>
+        <v>46036</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 25123-2026</t>
+          <t>A 2436-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46175</v>
+        <v>46036</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 25138-2026</t>
+          <t>A 4114-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46175</v>
+        <v>46044</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>7.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34354-2023</t>
+          <t>A 6739-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45139</v>
+        <v>46056</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 6739-2026</t>
+          <t>A 38322-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46056</v>
+        <v>45161</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
         <v>46065</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 25963-2026</t>
+          <t>A 40743-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46181</v>
+        <v>45558</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9299,7 +9299,7 @@
         <v>46070</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>46070</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 6485-2024</t>
+          <t>A 10118-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45339</v>
+        <v>46075</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 10118-2026</t>
+          <t>A 12087-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46075</v>
+        <v>46086</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 49617-2023</t>
+          <t>A 20819-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45211</v>
+        <v>45058</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 12087-2026</t>
+          <t>A 34354-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46086</v>
+        <v>45139</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>7.6</v>
+        <v>3.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 23682-2024</t>
+          <t>A 17426-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45454</v>
+        <v>46120</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 39206-2024</t>
+          <t>A 6485-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45548</v>
+        <v>45339</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 5715-2024</t>
+          <t>A 33789-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45334</v>
+        <v>46251</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 17426-2026</t>
+          <t>A 49617-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9953,10 +9953,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46120</v>
+        <v>45211</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 34056-2024</t>
+          <t>A 23682-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45523</v>
+        <v>45454</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10085,7 +10085,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 18431-2026</t>
+          <t>A 39206-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46127</v>
+        <v>45548</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10158,7 +10158,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 14547-2022</t>
+          <t>A 5715-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10172,10 +10172,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44655</v>
+        <v>45334</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10231,7 +10231,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 18791-2023</t>
+          <t>A 31029-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45044</v>
+        <v>46213</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10304,7 +10304,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28109-2024</t>
+          <t>A 34056-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10318,10 +10318,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45476</v>
+        <v>45523</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10377,7 +10377,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 33789-2026</t>
+          <t>A 36428-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46251</v>
+        <v>46269</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 63626-2023</t>
+          <t>A 14547-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45275</v>
+        <v>44655</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 32175-2024</t>
+          <t>A 18791-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45511</v>
+        <v>45044</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10596,7 +10596,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 34155-2024</t>
+          <t>A 28109-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45524</v>
+        <v>45476</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10669,7 +10669,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 46708-2023</t>
+          <t>A 63626-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45198</v>
+        <v>45275</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10742,7 +10742,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 62086-2022</t>
+          <t>A 32175-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10756,10 +10756,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44919</v>
+        <v>45511</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10815,7 +10815,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 31029-2026</t>
+          <t>A 34155-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10829,10 +10829,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46213</v>
+        <v>45524</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 57878-2022</t>
+          <t>A 37948-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44899</v>
+        <v>46280</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10961,7 +10961,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 14802-2023</t>
+          <t>A 46708-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45014</v>
+        <v>45198</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11034,7 +11034,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 2632-2024</t>
+          <t>A 62086-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11048,10 +11048,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45313</v>
+        <v>44919</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>8.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11107,7 +11107,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 33454-2023</t>
+          <t>A 57878-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11121,10 +11121,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45130</v>
+        <v>44899</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 36428-2026</t>
+          <t>A 14802-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46269</v>
+        <v>45014</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11253,7 +11253,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 22959-2025</t>
+          <t>A 2632-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11267,10 +11267,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45790</v>
+        <v>45313</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 37948-2026</t>
+          <t>A 33454-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11340,10 +11340,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46280</v>
+        <v>45130</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11399,7 +11399,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 14760-2025</t>
+          <t>A 22959-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45742</v>
+        <v>45790</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11472,7 +11472,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 9937-2025</t>
+          <t>A 14760-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11486,10 +11486,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45718</v>
+        <v>45742</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11545,7 +11545,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 13521-2025</t>
+          <t>A 9937-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11559,10 +11559,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45736</v>
+        <v>45718</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11618,7 +11618,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 13536-2025</t>
+          <t>A 13521-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11635,7 +11635,7 @@
         <v>45736</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11691,7 +11691,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 24321-2025</t>
+          <t>A 13536-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11705,10 +11705,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45797</v>
+        <v>45736</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11764,7 +11764,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 34046-2024</t>
+          <t>A 24321-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45523</v>
+        <v>45797</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11837,7 +11837,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 44754-2024</t>
+          <t>A 34046-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45574</v>
+        <v>45523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 44417-2024</t>
+          <t>A 44754-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11924,10 +11924,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45573</v>
+        <v>45574</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11983,7 +11983,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 27555-2025</t>
+          <t>A 44417-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45813</v>
+        <v>45573</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 54279-2024</t>
+          <t>A 27555-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45616</v>
+        <v>45813</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>6.9</v>
+        <v>1.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12129,7 +12129,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 33300-2025</t>
+          <t>A 54279-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12143,10 +12143,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45840</v>
+        <v>45616</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12202,7 +12202,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 33295-2025</t>
+          <t>A 33300-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12219,7 +12219,7 @@
         <v>45840</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12275,7 +12275,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33299-2025</t>
+          <t>A 33295-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12292,7 +12292,7 @@
         <v>45840</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 34502-2025</t>
+          <t>A 33299-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12421,7 +12421,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 36722-2025</t>
+          <t>A 34502-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45872</v>
+        <v>45847</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 50532-2024</t>
+          <t>A 36722-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12508,10 +12508,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45601</v>
+        <v>45872</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12564,27 +12564,27 @@
       </c>
       <c r="V152" s="2" t="inlineStr"/>
     </row>
-    <row r="153" ht="15" customHeight="1">
+    <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 1288-2025</t>
+          <t>S 2776-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45667</v>
+        <v>45937</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12636,79 +12636,6 @@
         <v>0</v>
       </c>
       <c r="V153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>S 2776-2025</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D154" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E154" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I154" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J154" t="n">
-        <v>0</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" t="n">
-        <v>0</v>
-      </c>
-      <c r="M154" t="n">
-        <v>0</v>
-      </c>
-      <c r="N154" t="n">
-        <v>0</v>
-      </c>
-      <c r="O154" t="n">
-        <v>0</v>
-      </c>
-      <c r="P154" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
-      <c r="R154" t="n">
-        <v>0</v>
-      </c>
-      <c r="S154" t="n">
-        <v>0</v>
-      </c>
-      <c r="T154" t="n">
-        <v>0</v>
-      </c>
-      <c r="U154" t="n">
-        <v>0</v>
-      </c>
-      <c r="V154" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 74306-2021</t>
+          <t>A 14805-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44559</v>
+        <v>45014</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.6</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -760,12 +760,236 @@
         <v>4</v>
       </c>
       <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönsångare
+Kambräken
+Purpurmylia</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Z3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 49930-2024</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>4</v>
       </c>
-      <c r="U3" t="n">
+      <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Svart trolldruva
+Revlummer
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 74306-2021</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44559</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
         <v>4</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Dvärglin
 Kösa
@@ -773,223 +997,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 74306-2021 artfynd.xlsx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 74306-2021 karta.png", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 74306-2021 georefererad karta.tif", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 74306-2021 FSC-klagomål.docx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 74306-2021 FSC-klagomål mail.docx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 74306-2021 tillsynsbegäran.docx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 74306-2021 tillsynsbegäran mail.docx", "A 74306-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 14805-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 65099-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45288</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>2</v>
       </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="n">
-        <v>6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>6</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönsångare
-Kambräken
-Purpurmylia</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 65099-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45288</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="T6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Blockskapania
 Knärot
@@ -997,144 +1105,36 @@
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 49930-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45597</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Svart trolldruva
-Revlummer
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
         <v/>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
         <v>45336</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44546</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 63419-2023</t>
+          <t>A 1663-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45274</v>
+        <v>45306</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1432,156 +1432,156 @@
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Blåbär
+Sälg
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 1663-2024 artfynd.xlsx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 1663-2024 karta.png", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 1663-2024 georefererad karta.tif", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 1663-2024 FSC-klagomål.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 1663-2024 FSC-klagomål mail.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 1663-2024 tillsynsbegäran.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 1663-2024 tillsynsbegäran mail.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 63419-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45274</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Björktrast
 Rödvingetrast
 Gröngöling</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 1663-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Blåbär
-Sälg
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 1663-2024 artfynd.xlsx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 1663-2024 karta.png", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 1663-2024 georefererad karta.tif", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 1663-2024 FSC-klagomål.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 1663-2024 FSC-klagomål mail.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 1663-2024 tillsynsbegäran.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 1663-2024 tillsynsbegäran mail.docx", "A 1663-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 40270-2024</t>
+          <t>A 13243-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45554</v>
+        <v>45002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1647,50 +1647,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13243-2023 artfynd.xlsx", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13243-2023 karta.png", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13243-2023 georefererad karta.tif", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13243-2023 FSC-klagomål.docx", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13243-2023 FSC-klagomål mail.docx", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13243-2023 tillsynsbegäran.docx", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13243-2023 tillsynsbegäran mail.docx", "A 13243-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49047-2025</t>
+          <t>A 5634-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1704,10 +1700,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45937</v>
+        <v>45693</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1720,19 +1716,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1747,55 +1743,59 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 6986-2024</t>
+          <t>A 13220-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45343</v>
+        <v>45386</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1849,58 +1849,62 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 56035-2025</t>
+          <t>A 5617-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1910,14 +1914,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45973</v>
+        <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1930,7 +1934,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>15.9</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1963,10 +1967,10 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
@@ -1974,42 +1978,42 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 771-2023</t>
+          <t>A 44233-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2023,10 +2027,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44931</v>
+        <v>45183</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2039,7 +2043,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2051,7 +2055,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2063,10 +2067,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2079,46 +2083,46 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
+        <v/>
+      </c>
+      <c r="Z15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 12722-2026</t>
+          <t>A 24618-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2132,10 +2136,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46091</v>
+        <v>45460</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2148,7 +2152,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>9.5</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2160,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2172,10 +2176,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2188,46 +2192,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
-        <v/>
-      </c>
-      <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13220-2024</t>
+          <t>A 771-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45386</v>
+        <v>44931</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2281,62 +2281,62 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
-        <v/>
-      </c>
-      <c r="Z17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24618-2024</t>
+          <t>A 56035-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2346,14 +2346,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45460</v>
+        <v>45973</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>9.5</v>
+        <v>15.9</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2390,58 +2390,62 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
+        <v/>
+      </c>
+      <c r="Z18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20709-2023</t>
+          <t>A 6986-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2455,10 +2459,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45058</v>
+        <v>45343</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2471,7 +2475,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2483,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2495,62 +2499,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
-        <v/>
-      </c>
-      <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23921-2026</t>
+          <t>A 12722-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46167</v>
+        <v>46091</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2580,20 +2580,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -2604,10 +2604,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2620,42 +2620,46 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5617-2024</t>
+          <t>A 20086-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2669,10 +2673,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45334</v>
+        <v>45054</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2685,7 +2689,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2729,42 +2733,42 @@
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Z21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31028-2026</t>
+          <t>A 20709-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2778,10 +2782,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46213</v>
+        <v>45058</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2794,20 +2798,20 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -2818,58 +2822,62 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
+        <v/>
+      </c>
+      <c r="Z22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41056-2025</t>
+          <t>A 49047-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2883,10 +2891,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45898</v>
+        <v>45937</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2899,17 +2907,17 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -2923,7 +2931,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2939,42 +2947,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44233-2023</t>
+          <t>A 40270-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2988,10 +2996,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45183</v>
+        <v>45554</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3004,7 +3012,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3040,7 +3048,7 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
@@ -3048,42 +3056,42 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5634-2025</t>
+          <t>A 23921-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3097,10 +3105,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45693</v>
+        <v>46167</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3113,19 +3121,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3137,62 +3145,58 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20086-2023</t>
+          <t>A 31028-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3206,10 +3210,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45054</v>
+        <v>46213</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3222,19 +3226,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3246,10 +3250,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3258,50 +3262,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
-        <v/>
-      </c>
-      <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13243-2023</t>
+          <t>A 41056-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45002</v>
+        <v>45898</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3331,16 +3331,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3371,35 +3371,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13243-2023 artfynd.xlsx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13243-2023 karta.png", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13243-2023 georefererad karta.tif", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13243-2023 FSC-klagomål.docx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13243-2023 FSC-klagomål mail.docx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13243-2023 tillsynsbegäran.docx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13243-2023 tillsynsbegäran mail.docx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44566</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55791-2022</t>
+          <t>A 63141-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44888</v>
+        <v>44505</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 63141-2021</t>
+          <t>A 55791-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44505</v>
+        <v>44888</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3897,7 +3897,7 @@
         <v>44657</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52012-2022</t>
+          <t>A 57445-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44872</v>
+        <v>45629</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 69196-2021</t>
+          <t>A 52012-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44531</v>
+        <v>44872</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62369-2023</t>
+          <t>A 69196-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45268</v>
+        <v>44531</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34217-2022</t>
+          <t>A 22959-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44791</v>
+        <v>45790</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57877-2022</t>
+          <t>A 9937-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44899</v>
+        <v>45718</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22750-2024</t>
+          <t>A 34380-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45448</v>
+        <v>44792</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 36999-2023</t>
+          <t>A 14802-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45155</v>
+        <v>45014</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19005-2023</t>
+          <t>A 13521-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45045</v>
+        <v>45736</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59309-2023</t>
+          <t>A 13536-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45253</v>
+        <v>45736</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55777-2022</t>
+          <t>A 14760-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44888</v>
+        <v>45742</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 43752-2023</t>
+          <t>A 59309-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45187</v>
+        <v>45253</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9.300000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30440-2024</t>
+          <t>A 36404-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45491</v>
+        <v>45535</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5121,7 +5121,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49115-2024</t>
+          <t>A 34046-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45594</v>
+        <v>45523</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6957-2024</t>
+          <t>A 1288-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45343</v>
+        <v>45667</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 71890-2021</t>
+          <t>A 39206-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44543</v>
+        <v>45548</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13378-2023</t>
+          <t>A 20089-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45005</v>
+        <v>45771</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 51993-2022</t>
+          <t>A 24321-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44872</v>
+        <v>45797</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 25925-2024</t>
+          <t>A 23682-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45467</v>
+        <v>45454</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5559,7 +5559,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50532-2024</t>
+          <t>A 41063-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45601</v>
+        <v>45898</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1288-2025</t>
+          <t>A 47884-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45667</v>
+        <v>45588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23258-2025</t>
+          <t>A 22750-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45791</v>
+        <v>45448</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 62516-2022</t>
+          <t>A 41881-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44924</v>
+        <v>45903</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 34500-2025</t>
+          <t>A 28109-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45847</v>
+        <v>45476</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.4</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 41063-2025</t>
+          <t>A 42457-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45898</v>
+        <v>45905</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47884-2024</t>
+          <t>A 5714-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45588</v>
+        <v>45334</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 41881-2025</t>
+          <t>A 62086-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45903</v>
+        <v>44919</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27277-2025</t>
+          <t>A 55777-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45812</v>
+        <v>44888</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 42457-2025</t>
+          <t>A 6957-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45905</v>
+        <v>45343</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 40328-2025</t>
+          <t>A 49822-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45895</v>
+        <v>44862</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 33296-2025</t>
+          <t>A 57878-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45840</v>
+        <v>44899</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6435,7 +6435,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56496-2021</t>
+          <t>A 2632-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44480</v>
+        <v>45313</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>10.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6508,7 +6508,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 68727-2021</t>
+          <t>A 49115-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44529</v>
+        <v>45594</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 5926-2024</t>
+          <t>A 32175-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45336</v>
+        <v>45511</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6654,7 +6654,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20675-2026</t>
+          <t>A 63626-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46141</v>
+        <v>45275</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 48419-2025</t>
+          <t>A 30440-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45934</v>
+        <v>45491</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7.7</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 54128-2025</t>
+          <t>A 37130-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45964</v>
+        <v>45539</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20089-2025</t>
+          <t>A 44417-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45771</v>
+        <v>45573</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61302-2024</t>
+          <t>A 44754-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45645</v>
+        <v>45574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 49365-2025</t>
+          <t>A 62516-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45938</v>
+        <v>44924</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 5714-2024</t>
+          <t>A 48419-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45334</v>
+        <v>45934</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7165,7 +7165,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34380-2022</t>
+          <t>A 49365-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44792</v>
+        <v>45938</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14609-2024</t>
+          <t>A 27555-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45396</v>
+        <v>45813</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13377-2023</t>
+          <t>A 5926-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45005</v>
+        <v>45336</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37130-2024</t>
+          <t>A 40743-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45539</v>
+        <v>45558</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 59915-2024</t>
+          <t>A 49617-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45641</v>
+        <v>45211</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7530,7 +7530,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 42712-2023</t>
+          <t>A 54279-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45181</v>
+        <v>45616</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>6.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50562-2024</t>
+          <t>A 20131-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45601</v>
+        <v>45772</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 58853-2025</t>
+          <t>A 51993-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45987</v>
+        <v>44872</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58852-2025</t>
+          <t>A 20819-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45987</v>
+        <v>45058</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24605-2026</t>
+          <t>A 34354-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46170</v>
+        <v>45139</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 49072-2025</t>
+          <t>A 33454-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45937</v>
+        <v>45130</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 20131-2025</t>
+          <t>A 43752-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45772</v>
+        <v>45187</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59834-2025</t>
+          <t>A 38322-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45992</v>
+        <v>45161</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 5454-2025</t>
+          <t>A 58852-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45692</v>
+        <v>45987</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 61319-2025</t>
+          <t>A 34217-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46000</v>
+        <v>44791</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25123-2026</t>
+          <t>A 58853-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46175</v>
+        <v>45987</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 25138-2026</t>
+          <t>A 59834-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46175</v>
+        <v>45992</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 40722-2024</t>
+          <t>A 61319-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45558</v>
+        <v>46000</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 36404-2024</t>
+          <t>A 2435-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45535</v>
+        <v>46036</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 57445-2024</t>
+          <t>A 2436-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45629</v>
+        <v>46036</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 25963-2026</t>
+          <t>A 4114-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46181</v>
+        <v>46044</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>7.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 49822-2022</t>
+          <t>A 33300-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44862</v>
+        <v>45840</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 2435-2026</t>
+          <t>A 6739-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46036</v>
+        <v>46056</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 2436-2026</t>
+          <t>A 5715-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46036</v>
+        <v>45334</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 4114-2026</t>
+          <t>A 5454-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46044</v>
+        <v>45692</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.1</v>
+        <v>2.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6739-2026</t>
+          <t>A 19005-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46056</v>
+        <v>45045</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 38322-2023</t>
+          <t>A 34056-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45161</v>
+        <v>45523</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
         <v>46065</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 40743-2024</t>
+          <t>A 59915-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45558</v>
+        <v>45641</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 9194-2026</t>
+          <t>A 33295-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46070</v>
+        <v>45840</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9344-2026</t>
+          <t>A 33299-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46070</v>
+        <v>45840</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 10118-2026</t>
+          <t>A 9344-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46075</v>
+        <v>46070</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 12087-2026</t>
+          <t>A 9194-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46086</v>
+        <v>46070</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20819-2023</t>
+          <t>A 57877-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45058</v>
+        <v>44899</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 34354-2023</t>
+          <t>A 13378-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45139</v>
+        <v>45005</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 17426-2026</t>
+          <t>A 10118-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46120</v>
+        <v>46075</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 6485-2024</t>
+          <t>A 12087-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45339</v>
+        <v>46086</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>7.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 33789-2026</t>
+          <t>A 34502-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46251</v>
+        <v>45847</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 49617-2023</t>
+          <t>A 25925-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9953,10 +9953,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45211</v>
+        <v>45467</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 23682-2024</t>
+          <t>A 34155-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45454</v>
+        <v>45524</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10085,7 +10085,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 39206-2024</t>
+          <t>A 18791-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45548</v>
+        <v>45044</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10158,7 +10158,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 5715-2024</t>
+          <t>A 42712-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10172,10 +10172,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45334</v>
+        <v>45181</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10231,7 +10231,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 31029-2026</t>
+          <t>A 17426-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46213</v>
+        <v>46120</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10304,7 +10304,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 34056-2024</t>
+          <t>A 36722-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10318,10 +10318,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45523</v>
+        <v>45872</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10377,7 +10377,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 36428-2026</t>
+          <t>A 71890-2021</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46269</v>
+        <v>44543</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 14547-2022</t>
+          <t>A 50532-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44655</v>
+        <v>45601</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 18791-2023</t>
+          <t>A 56496-2021</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45044</v>
+        <v>44480</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>10.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10596,7 +10596,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 28109-2024</t>
+          <t>A 40328-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45476</v>
+        <v>45895</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10669,7 +10669,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 63626-2023</t>
+          <t>A 46708-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45275</v>
+        <v>45198</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10742,7 +10742,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 32175-2024</t>
+          <t>A 40722-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10756,10 +10756,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45511</v>
+        <v>45558</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10815,7 +10815,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 34155-2024</t>
+          <t>A 62369-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10829,10 +10829,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45524</v>
+        <v>45268</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 37948-2026</t>
+          <t>A 14547-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46280</v>
+        <v>44655</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10961,7 +10961,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 46708-2023</t>
+          <t>A 27277-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45198</v>
+        <v>45812</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11034,7 +11034,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 62086-2022</t>
+          <t>A 23258-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11048,10 +11048,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44919</v>
+        <v>45791</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11107,7 +11107,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 57878-2022</t>
+          <t>A 33296-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11121,10 +11121,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44899</v>
+        <v>45840</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 14802-2023</t>
+          <t>A 34500-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45014</v>
+        <v>45847</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11253,7 +11253,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 2632-2024</t>
+          <t>A 68727-2021</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11267,10 +11267,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45313</v>
+        <v>44529</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 33454-2023</t>
+          <t>A 54128-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11340,10 +11340,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45130</v>
+        <v>45964</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11399,7 +11399,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 22959-2025</t>
+          <t>A 6485-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45790</v>
+        <v>45339</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11472,7 +11472,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 14760-2025</t>
+          <t>A 13377-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11486,10 +11486,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45742</v>
+        <v>45005</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11545,7 +11545,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 9937-2025</t>
+          <t>A 61302-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11559,10 +11559,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45718</v>
+        <v>45645</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11618,7 +11618,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 13521-2025</t>
+          <t>A 50562-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11632,10 +11632,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45736</v>
+        <v>45601</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11691,7 +11691,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 13536-2025</t>
+          <t>A 20675-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11705,10 +11705,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45736</v>
+        <v>46141</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11764,7 +11764,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 24321-2025</t>
+          <t>A 36999-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45797</v>
+        <v>45155</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11837,7 +11837,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 34046-2024</t>
+          <t>A 14609-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45523</v>
+        <v>45396</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 44754-2024</t>
+          <t>A 49072-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11924,10 +11924,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45574</v>
+        <v>45937</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11983,7 +11983,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 44417-2024</t>
+          <t>A 24605-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45573</v>
+        <v>46170</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 27555-2025</t>
+          <t>A 25123-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45813</v>
+        <v>46175</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12129,7 +12129,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 54279-2024</t>
+          <t>A 25138-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12143,10 +12143,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45616</v>
+        <v>46175</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>6.9</v>
+        <v>0.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12202,7 +12202,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 33300-2025</t>
+          <t>A 25963-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12216,10 +12216,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45840</v>
+        <v>46181</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12275,7 +12275,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33295-2025</t>
+          <t>A 33789-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12289,10 +12289,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45840</v>
+        <v>46251</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12348,7 +12348,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 33299-2025</t>
+          <t>A 31029-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45840</v>
+        <v>46213</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12421,7 +12421,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 34502-2025</t>
+          <t>A 36428-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45847</v>
+        <v>46269</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 36722-2025</t>
+          <t>A 37948-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12508,10 +12508,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45872</v>
+        <v>46280</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12584,7 +12584,7 @@
         <v>45937</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>

--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 14805-2023</t>
+          <t>A 74306-2021</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45014</v>
+        <v>44559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>14.6</v>
       </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -760,12 +760,120 @@
         <v>4</v>
       </c>
       <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Dvärglin
+Kösa
+Åkerrödtoppa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 74306-2021 artfynd.xlsx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 74306-2021 karta.png", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 74306-2021 georefererad karta.tif", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 74306-2021 FSC-klagomål.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 74306-2021 FSC-klagomål mail.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 74306-2021 tillsynsbegäran.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 74306-2021 tillsynsbegäran mail.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 14805-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
         <v>6</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>6</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Grönsångare
@@ -773,115 +881,227 @@
 Purpurmylia</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="Z3">
+      <c r="Z4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 65099-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45288</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Blockskapania
+Knärot
+Grov fjädermossa
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 49930-2024</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>45597</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>16.6</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J6" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T6" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Svart trolldruva
@@ -889,259 +1109,39 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 74306-2021</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44559</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>4</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Dvärglin
-Kösa
-Åkerrödtoppa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 74306-2021 artfynd.xlsx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 74306-2021 karta.png", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 74306-2021 georefererad karta.tif", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 74306-2021 FSC-klagomål.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 74306-2021 FSC-klagomål mail.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 74306-2021 tillsynsbegäran.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 74306-2021 tillsynsbegäran mail.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 65099-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45288</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Blockskapania
-Knärot
-Grov fjädermossa
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6055-2024</t>
+          <t>A 72588-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45336</v>
+        <v>44546</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1171,19 +1171,19 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>24.1</v>
+        <v>21.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1195,175 +1195,175 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
       </c>
       <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Kambräken
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 72588-2021 artfynd.xlsx", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 72588-2021 karta.png", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 72588-2021 georefererad karta.tif", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 72588-2021 karta knärot.png", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 72588-2021 FSC-klagomål.docx", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 72588-2021 FSC-klagomål mail.docx", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 72588-2021 tillsynsbegäran.docx", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 72588-2021 tillsynsbegäran mail.docx", "A 72588-2021")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 72588-2021 prioriterade fågelarter.docx", "A 72588-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 6055-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45336</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>3</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)
 Revlummer
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6055-2024 artfynd.xlsx", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6055-2024 karta.png", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6055-2024 georefererad karta.tif", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6055-2024 FSC-klagomål.docx", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6055-2024 FSC-klagomål mail.docx", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6055-2024 tillsynsbegäran.docx", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6055-2024 tillsynsbegäran mail.docx", "A 6055-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 72588-2021</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44546</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Kambräken
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 72588-2021 artfynd.xlsx", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 72588-2021 karta.png", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 72588-2021 georefererad karta.tif", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 72588-2021 karta knärot.png", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 72588-2021 FSC-klagomål.docx", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 72588-2021 FSC-klagomål mail.docx", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 72588-2021 tillsynsbegäran.docx", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 72588-2021 tillsynsbegäran mail.docx", "A 72588-2021")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 72588-2021 prioriterade fågelarter.docx", "A 72588-2021")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1663-2024</t>
+          <t>A 63419-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45306</v>
+        <v>45274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1432,156 +1432,156 @@
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Björktrast
+Rödvingetrast
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 1663-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45306</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Blåbär
 Sälg
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 1663-2024 artfynd.xlsx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 1663-2024 karta.png", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 1663-2024 georefererad karta.tif", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 1663-2024 FSC-klagomål.docx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 1663-2024 FSC-klagomål mail.docx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 1663-2024 tillsynsbegäran.docx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 1663-2024 tillsynsbegäran mail.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 63419-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45274</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Björktrast
-Rödvingetrast
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13243-2023</t>
+          <t>A 40270-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45002</v>
+        <v>45554</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1647,46 +1647,50 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13243-2023 artfynd.xlsx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13243-2023 karta.png", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13243-2023 georefererad karta.tif", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13243-2023 FSC-klagomål.docx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13243-2023 FSC-klagomål mail.docx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13243-2023 tillsynsbegäran.docx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13243-2023 tillsynsbegäran mail.docx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 5634-2025</t>
+          <t>A 6986-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1700,10 +1704,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45693</v>
+        <v>45343</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1716,7 +1720,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1728,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,62 +1744,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13220-2024</t>
+          <t>A 49047-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45386</v>
+        <v>45937</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1825,19 +1825,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1852,59 +1852,55 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5617-2024</t>
+          <t>A 56035-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1914,14 +1910,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45334</v>
+        <v>45973</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1930,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>15.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1967,10 +1963,10 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
@@ -1978,42 +1974,42 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 44233-2023</t>
+          <t>A 771-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2027,10 +2023,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45183</v>
+        <v>44931</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2043,7 +2039,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2055,7 +2051,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2067,10 +2063,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2083,46 +2079,46 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
-        <v/>
-      </c>
-      <c r="Z15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24618-2024</t>
+          <t>A 12722-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2136,10 +2132,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45460</v>
+        <v>46091</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2148,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>9.5</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2164,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2176,10 +2172,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2192,42 +2188,46 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
+        <v/>
+      </c>
+      <c r="Z16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 771-2023</t>
+          <t>A 13220-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44931</v>
+        <v>45386</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2281,62 +2281,62 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
+        <v/>
+      </c>
+      <c r="Z17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 56035-2025</t>
+          <t>A 24618-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2346,14 +2346,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45973</v>
+        <v>45460</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15.9</v>
+        <v>9.5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2390,62 +2390,58 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
-        <v/>
-      </c>
-      <c r="Z18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6986-2024</t>
+          <t>A 20709-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2459,10 +2455,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45343</v>
+        <v>45058</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2475,7 +2471,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2487,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2499,58 +2495,62 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12722-2026</t>
+          <t>A 5617-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46091</v>
+        <v>45334</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2616,7 +2616,7 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
@@ -2624,42 +2624,42 @@
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20086-2023</t>
+          <t>A 23921-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45054</v>
+        <v>46167</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2713,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2725,50 +2725,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
-        <v/>
-      </c>
-      <c r="Z21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20709-2023</t>
+          <t>A 31028-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2782,10 +2778,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45058</v>
+        <v>46213</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2798,19 +2794,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2822,62 +2818,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
-        <v/>
-      </c>
-      <c r="Z22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49047-2025</t>
+          <t>A 44233-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2891,10 +2883,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45937</v>
+        <v>45183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2907,19 +2899,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2934,7 +2926,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2947,42 +2939,46 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
+        <v/>
+      </c>
+      <c r="Z23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 40270-2024</t>
+          <t>A 41056-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2996,10 +2992,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45554</v>
+        <v>45898</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3012,19 +3008,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3036,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3048,50 +3044,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 23921-2026</t>
+          <t>A 5634-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3105,10 +3097,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46167</v>
+        <v>45693</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3121,20 +3113,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3145,58 +3137,62 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31028-2026</t>
+          <t>A 20086-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3210,10 +3206,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46213</v>
+        <v>45054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3226,20 +3222,20 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
@@ -3250,10 +3246,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3262,46 +3258,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
+        <v/>
+      </c>
+      <c r="Z26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 41056-2025</t>
+          <t>A 13243-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45898</v>
+        <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3331,17 +3331,17 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3371,35 +3371,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13243-2023 artfynd.xlsx", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13243-2023 karta.png", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13243-2023 georefererad karta.tif", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13243-2023 FSC-klagomål.docx", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13243-2023 FSC-klagomål mail.docx", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13243-2023 tillsynsbegäran.docx", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13243-2023 tillsynsbegäran mail.docx", "A 13243-2023")</f>
         <v/>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44566</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 63141-2021</t>
+          <t>A 55791-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44505</v>
+        <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55791-2022</t>
+          <t>A 63141-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44888</v>
+        <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3897,7 +3897,7 @@
         <v>44657</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57445-2024</t>
+          <t>A 52012-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45629</v>
+        <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52012-2022</t>
+          <t>A 69196-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44872</v>
+        <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 69196-2021</t>
+          <t>A 62369-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44531</v>
+        <v>45268</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22959-2025</t>
+          <t>A 34217-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45790</v>
+        <v>44791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9937-2025</t>
+          <t>A 57877-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45718</v>
+        <v>44899</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34380-2022</t>
+          <t>A 22750-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44792</v>
+        <v>45448</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14802-2023</t>
+          <t>A 36999-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45014</v>
+        <v>45155</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13521-2025</t>
+          <t>A 19005-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45736</v>
+        <v>45045</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13536-2025</t>
+          <t>A 59309-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45736</v>
+        <v>45253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.1</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14760-2025</t>
+          <t>A 55777-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45742</v>
+        <v>44888</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59309-2023</t>
+          <t>A 43752-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45253</v>
+        <v>45187</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 36404-2024</t>
+          <t>A 30440-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45535</v>
+        <v>45491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5121,7 +5121,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34046-2024</t>
+          <t>A 49115-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45523</v>
+        <v>45594</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 1288-2025</t>
+          <t>A 6957-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45667</v>
+        <v>45343</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 39206-2024</t>
+          <t>A 13378-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45548</v>
+        <v>45005</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20089-2025</t>
+          <t>A 51993-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45771</v>
+        <v>44872</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24321-2025</t>
+          <t>A 25925-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45797</v>
+        <v>45467</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23682-2024</t>
+          <t>A 36722-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45454</v>
+        <v>45872</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5559,7 +5559,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 41063-2025</t>
+          <t>A 71890-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45898</v>
+        <v>44543</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 47884-2024</t>
+          <t>A 50532-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45588</v>
+        <v>45601</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22750-2024</t>
+          <t>A 1288-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45448</v>
+        <v>45667</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 41881-2025</t>
+          <t>A 41063-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45903</v>
+        <v>45898</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28109-2024</t>
+          <t>A 47884-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45476</v>
+        <v>45588</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 42457-2025</t>
+          <t>A 41881-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45905</v>
+        <v>45903</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 5714-2024</t>
+          <t>A 42457-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45334</v>
+        <v>45905</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62086-2022</t>
+          <t>A 62516-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44919</v>
+        <v>44924</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55777-2022</t>
+          <t>A 5926-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44888</v>
+        <v>45336</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6957-2024</t>
+          <t>A 23258-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45343</v>
+        <v>45791</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 49822-2022</t>
+          <t>A 34500-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44862</v>
+        <v>45847</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 57878-2022</t>
+          <t>A 27277-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44899</v>
+        <v>45812</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6435,7 +6435,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2632-2024</t>
+          <t>A 20089-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45313</v>
+        <v>45771</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6508,7 +6508,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49115-2024</t>
+          <t>A 61302-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45594</v>
+        <v>45645</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32175-2024</t>
+          <t>A 48419-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45511</v>
+        <v>45934</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.3</v>
+        <v>7.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6654,7 +6654,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 63626-2023</t>
+          <t>A 40328-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45275</v>
+        <v>45895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30440-2024</t>
+          <t>A 49365-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45491</v>
+        <v>45938</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37130-2024</t>
+          <t>A 5714-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45539</v>
+        <v>45334</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44417-2024</t>
+          <t>A 34380-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45573</v>
+        <v>44792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44754-2024</t>
+          <t>A 33296-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45574</v>
+        <v>45840</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 62516-2022</t>
+          <t>A 56496-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44924</v>
+        <v>44480</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>10.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48419-2025</t>
+          <t>A 13377-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45934</v>
+        <v>45005</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>7.7</v>
+        <v>2.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7165,7 +7165,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 49365-2025</t>
+          <t>A 37130-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45938</v>
+        <v>45539</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 27555-2025</t>
+          <t>A 68727-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45813</v>
+        <v>44529</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 5926-2024</t>
+          <t>A 59915-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45336</v>
+        <v>45641</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 40743-2024</t>
+          <t>A 20675-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45558</v>
+        <v>46141</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 49617-2023</t>
+          <t>A 42712-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45211</v>
+        <v>45181</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7530,7 +7530,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54279-2024</t>
+          <t>A 54128-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45616</v>
+        <v>45964</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>6.9</v>
+        <v>5.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20131-2025</t>
+          <t>A 50562-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45772</v>
+        <v>45601</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 51993-2022</t>
+          <t>A 20131-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44872</v>
+        <v>45772</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20819-2023</t>
+          <t>A 58853-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45058</v>
+        <v>45987</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34354-2023</t>
+          <t>A 58852-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45139</v>
+        <v>45987</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 33454-2023</t>
+          <t>A 5454-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45130</v>
+        <v>45692</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43752-2023</t>
+          <t>A 59834-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45187</v>
+        <v>45992</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>9.300000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38322-2023</t>
+          <t>A 61319-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45161</v>
+        <v>46000</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58852-2025</t>
+          <t>A 40722-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45987</v>
+        <v>45558</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 34217-2022</t>
+          <t>A 36404-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44791</v>
+        <v>45535</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 58853-2025</t>
+          <t>A 57445-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45987</v>
+        <v>45629</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 59834-2025</t>
+          <t>A 14609-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45992</v>
+        <v>45396</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61319-2025</t>
+          <t>A 49822-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46000</v>
+        <v>44862</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8496,7 +8496,7 @@
         <v>46036</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>46036</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>46044</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 33300-2025</t>
+          <t>A 38322-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45840</v>
+        <v>45161</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 6739-2026</t>
+          <t>A 40743-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46056</v>
+        <v>45558</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5715-2024</t>
+          <t>A 6739-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45334</v>
+        <v>46056</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 5454-2025</t>
+          <t>A 8457-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45692</v>
+        <v>46065</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19005-2023</t>
+          <t>A 24605-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45045</v>
+        <v>46170</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 34056-2024</t>
+          <t>A 49072-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45523</v>
+        <v>45937</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 8457-2026</t>
+          <t>A 9194-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 59915-2024</t>
+          <t>A 9344-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45641</v>
+        <v>46070</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33295-2025</t>
+          <t>A 10118-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45840</v>
+        <v>46075</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33299-2025</t>
+          <t>A 12087-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45840</v>
+        <v>46086</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.4</v>
+        <v>7.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 9344-2026</t>
+          <t>A 25123-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46070</v>
+        <v>46175</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 9194-2026</t>
+          <t>A 25138-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46070</v>
+        <v>46175</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 57877-2022</t>
+          <t>A 20819-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44899</v>
+        <v>45058</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 13378-2023</t>
+          <t>A 25963-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45005</v>
+        <v>46181</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 10118-2026</t>
+          <t>A 34354-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46075</v>
+        <v>45139</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 12087-2026</t>
+          <t>A 17426-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46086</v>
+        <v>46120</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 34502-2025</t>
+          <t>A 6485-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45847</v>
+        <v>45339</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 25925-2024</t>
+          <t>A 49617-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9953,10 +9953,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45467</v>
+        <v>45211</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 34155-2024</t>
+          <t>A 23682-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45524</v>
+        <v>45454</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10085,7 +10085,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 18791-2023</t>
+          <t>A 39206-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45044</v>
+        <v>45548</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10158,7 +10158,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 42712-2023</t>
+          <t>A 5715-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10172,10 +10172,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45181</v>
+        <v>45334</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10231,7 +10231,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 17426-2026</t>
+          <t>A 33789-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46120</v>
+        <v>46251</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10304,7 +10304,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 36722-2025</t>
+          <t>A 34056-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10318,10 +10318,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45872</v>
+        <v>45523</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10377,7 +10377,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 71890-2021</t>
+          <t>A 31029-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44543</v>
+        <v>46213</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 50532-2024</t>
+          <t>A 14547-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45601</v>
+        <v>44655</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 56496-2021</t>
+          <t>A 18791-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44480</v>
+        <v>45044</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>10.3</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10596,7 +10596,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 40328-2025</t>
+          <t>A 28109-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45895</v>
+        <v>45476</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10669,7 +10669,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 46708-2023</t>
+          <t>A 63626-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45198</v>
+        <v>45275</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10742,7 +10742,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 40722-2024</t>
+          <t>A 32175-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10756,10 +10756,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45558</v>
+        <v>45511</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10815,7 +10815,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 62369-2023</t>
+          <t>A 34155-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10829,10 +10829,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45268</v>
+        <v>45524</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 14547-2022</t>
+          <t>A 36428-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44655</v>
+        <v>46269</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10961,7 +10961,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 27277-2025</t>
+          <t>A 46708-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45812</v>
+        <v>45198</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11034,7 +11034,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 23258-2025</t>
+          <t>A 62086-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11048,10 +11048,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45791</v>
+        <v>44919</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11107,7 +11107,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 33296-2025</t>
+          <t>A 57878-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11121,10 +11121,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45840</v>
+        <v>44899</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 34500-2025</t>
+          <t>A 14802-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45847</v>
+        <v>45014</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.4</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11253,7 +11253,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 68727-2021</t>
+          <t>A 2632-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11267,10 +11267,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44529</v>
+        <v>45313</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 54128-2025</t>
+          <t>A 37948-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11340,10 +11340,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45964</v>
+        <v>46280</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11399,7 +11399,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 6485-2024</t>
+          <t>A 33454-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45339</v>
+        <v>45130</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11472,7 +11472,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 13377-2023</t>
+          <t>A 22959-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11486,10 +11486,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45005</v>
+        <v>45790</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11545,7 +11545,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 61302-2024</t>
+          <t>A 14760-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11559,10 +11559,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45645</v>
+        <v>45742</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11618,7 +11618,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 50562-2024</t>
+          <t>A 9937-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11632,10 +11632,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45601</v>
+        <v>45718</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11691,7 +11691,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 20675-2026</t>
+          <t>A 13521-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11705,10 +11705,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46141</v>
+        <v>45736</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11764,7 +11764,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 36999-2023</t>
+          <t>A 13536-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45155</v>
+        <v>45736</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11837,7 +11837,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 14609-2024</t>
+          <t>A 24321-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45396</v>
+        <v>45797</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 49072-2025</t>
+          <t>A 34046-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11924,10 +11924,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45937</v>
+        <v>45523</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11983,7 +11983,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 24605-2026</t>
+          <t>A 44754-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46170</v>
+        <v>45574</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 25123-2026</t>
+          <t>A 44417-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46175</v>
+        <v>45573</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12129,7 +12129,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 25138-2026</t>
+          <t>A 27555-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12143,10 +12143,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46175</v>
+        <v>45813</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12202,7 +12202,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 25963-2026</t>
+          <t>A 54279-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12216,10 +12216,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46181</v>
+        <v>45616</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12275,7 +12275,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33789-2026</t>
+          <t>A 33300-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12289,10 +12289,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46251</v>
+        <v>45840</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12348,7 +12348,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 31029-2026</t>
+          <t>A 33295-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46213</v>
+        <v>45840</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12421,7 +12421,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 36428-2026</t>
+          <t>A 33299-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46269</v>
+        <v>45840</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37948-2026</t>
+          <t>A 34502-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12508,10 +12508,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46280</v>
+        <v>45847</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12584,7 +12584,7 @@
         <v>45937</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>

--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 74306-2021</t>
+          <t>A 49930-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44559</v>
+        <v>45597</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -727,45 +727,269 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.6</v>
+        <v>16.6</v>
       </c>
       <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
       </c>
       <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Svart trolldruva
+Revlummer
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 14805-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
         <v>4</v>
       </c>
-      <c r="U3" t="n">
+      <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönsångare
+Kambräken
+Purpurmylia</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 74306-2021</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44559</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
         <v>4</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Dvärglin
 Kösa
@@ -773,223 +997,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 74306-2021 artfynd.xlsx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 74306-2021 karta.png", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 74306-2021 georefererad karta.tif", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 74306-2021 FSC-klagomål.docx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 74306-2021 FSC-klagomål mail.docx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 74306-2021 tillsynsbegäran.docx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 74306-2021 tillsynsbegäran mail.docx", "A 74306-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 14805-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 65099-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45288</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>2</v>
       </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="n">
-        <v>6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>6</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönsångare
-Kambräken
-Purpurmylia</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 65099-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45288</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="T6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Blockskapania
 Knärot
@@ -997,144 +1105,36 @@
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 49930-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45597</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Svart trolldruva
-Revlummer
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
         <v/>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
         <v>44546</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45336</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 63419-2023</t>
+          <t>A 1663-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45274</v>
+        <v>45306</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1432,156 +1432,156 @@
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Blåbär
+Sälg
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 1663-2024 artfynd.xlsx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 1663-2024 karta.png", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 1663-2024 georefererad karta.tif", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 1663-2024 FSC-klagomål.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 1663-2024 FSC-klagomål mail.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 1663-2024 tillsynsbegäran.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 1663-2024 tillsynsbegäran mail.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 63419-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45274</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Björktrast
 Rödvingetrast
 Gröngöling</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 1663-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Blåbär
-Sälg
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 1663-2024 artfynd.xlsx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 1663-2024 karta.png", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 1663-2024 georefererad karta.tif", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 1663-2024 FSC-klagomål.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 1663-2024 FSC-klagomål mail.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 1663-2024 tillsynsbegäran.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 1663-2024 tillsynsbegäran mail.docx", "A 1663-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 40270-2024</t>
+          <t>A 13220-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45554</v>
+        <v>45386</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1644,10 +1644,10 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1655,42 +1655,42 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 6986-2024</t>
+          <t>A 56035-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1700,14 +1700,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45343</v>
+        <v>45973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1732,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1744,58 +1744,62 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 49047-2025</t>
+          <t>A 12722-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1809,10 +1813,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45937</v>
+        <v>46091</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1825,19 +1829,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1852,7 +1856,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1865,42 +1869,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 56035-2025</t>
+          <t>A 24618-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1910,14 +1918,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45973</v>
+        <v>45460</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1930,7 +1938,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>15.9</v>
+        <v>9.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1942,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1954,55 +1962,51 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
     </row>
@@ -2026,7 +2030,7 @@
         <v>44931</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2118,7 +2122,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 12722-2026</t>
+          <t>A 5634-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2132,10 +2136,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46091</v>
+        <v>45693</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2148,7 +2152,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2181,7 +2185,7 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2192,42 +2196,42 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13220-2024</t>
+          <t>A 49047-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2241,10 +2245,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45386</v>
+        <v>45937</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2257,19 +2261,19 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2284,59 +2288,55 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
-        <v/>
-      </c>
-      <c r="Z17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24618-2024</t>
+          <t>A 5617-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45460</v>
+        <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>9.5</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2390,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2402,46 +2402,50 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
+        <v/>
+      </c>
+      <c r="Z18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20709-2023</t>
+          <t>A 44233-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2455,10 +2459,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45058</v>
+        <v>45183</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2471,7 +2475,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2504,10 +2508,10 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
@@ -2515,42 +2519,42 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 5617-2024</t>
+          <t>A 23921-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2564,10 +2568,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45334</v>
+        <v>46167</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2580,19 +2584,19 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2604,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2616,50 +2620,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23921-2026</t>
+          <t>A 31028-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46167</v>
+        <v>46213</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2729,42 +2729,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31028-2026</t>
+          <t>A 41056-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46213</v>
+        <v>45898</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2834,42 +2834,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 44233-2023</t>
+          <t>A 6986-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2883,10 +2883,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45183</v>
+        <v>45343</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2923,10 +2923,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2935,50 +2935,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
-        <v/>
-      </c>
-      <c r="Z23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41056-2025</t>
+          <t>A 20086-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2992,10 +2988,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45898</v>
+        <v>45054</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3008,20 +3004,20 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -3032,10 +3028,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3044,46 +3040,50 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
+        <v/>
+      </c>
+      <c r="Z24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5634-2025</t>
+          <t>A 20709-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45693</v>
+        <v>45058</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3146,10 +3146,10 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
@@ -3157,42 +3157,42 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20086-2023</t>
+          <t>A 40270-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45054</v>
+        <v>45554</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3266,35 +3266,35 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
         <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44566</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44657</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62369-2023</t>
+          <t>A 34380-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45268</v>
+        <v>44792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34217-2022</t>
+          <t>A 59309-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44791</v>
+        <v>45253</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57877-2022</t>
+          <t>A 39206-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44899</v>
+        <v>45548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22750-2024</t>
+          <t>A 23682-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45448</v>
+        <v>45454</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 36999-2023</t>
+          <t>A 34046-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45155</v>
+        <v>45523</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19005-2023</t>
+          <t>A 22750-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45045</v>
+        <v>45448</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59309-2023</t>
+          <t>A 28109-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45253</v>
+        <v>45476</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55777-2022</t>
+          <t>A 1288-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44888</v>
+        <v>45667</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 43752-2023</t>
+          <t>A 5714-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45187</v>
+        <v>45334</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30440-2024</t>
+          <t>A 24321-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45491</v>
+        <v>45797</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5121,7 +5121,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49115-2024</t>
+          <t>A 55777-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45594</v>
+        <v>44888</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6957-2024</t>
+          <t>A 2435-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45343</v>
+        <v>46036</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13378-2023</t>
+          <t>A 2436-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45005</v>
+        <v>46036</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 51993-2022</t>
+          <t>A 49822-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44872</v>
+        <v>44862</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 25925-2024</t>
+          <t>A 57878-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45467</v>
+        <v>44899</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36722-2025</t>
+          <t>A 4114-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45872</v>
+        <v>46044</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>7.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5559,7 +5559,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 71890-2021</t>
+          <t>A 41063-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44543</v>
+        <v>45898</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50532-2024</t>
+          <t>A 47884-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45601</v>
+        <v>45588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1288-2025</t>
+          <t>A 49115-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45667</v>
+        <v>45594</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 41063-2025</t>
+          <t>A 41881-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45898</v>
+        <v>45903</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47884-2024</t>
+          <t>A 42457-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45588</v>
+        <v>45905</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 41881-2025</t>
+          <t>A 30440-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45903</v>
+        <v>45491</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42457-2025</t>
+          <t>A 6739-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45905</v>
+        <v>46056</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6087,7 +6087,7 @@
         <v>44924</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 5926-2024</t>
+          <t>A 8457-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45336</v>
+        <v>46065</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 23258-2025</t>
+          <t>A 9344-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45791</v>
+        <v>46070</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34500-2025</t>
+          <t>A 9194-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45847</v>
+        <v>46070</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.4</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 27277-2025</t>
+          <t>A 40743-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45812</v>
+        <v>45558</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6435,7 +6435,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20089-2025</t>
+          <t>A 10118-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45771</v>
+        <v>46075</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6508,7 +6508,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61302-2024</t>
+          <t>A 49617-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45645</v>
+        <v>45211</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 48419-2025</t>
+          <t>A 44417-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45934</v>
+        <v>45573</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.7</v>
+        <v>3.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6654,7 +6654,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40328-2025</t>
+          <t>A 12087-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45895</v>
+        <v>46086</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 49365-2025</t>
+          <t>A 48419-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45938</v>
+        <v>45934</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>7.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5714-2024</t>
+          <t>A 49365-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45334</v>
+        <v>45938</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34380-2022</t>
+          <t>A 20131-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44792</v>
+        <v>45772</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33296-2025</t>
+          <t>A 44754-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45840</v>
+        <v>45574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56496-2021</t>
+          <t>A 51993-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44480</v>
+        <v>44872</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>10.3</v>
+        <v>2.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13377-2023</t>
+          <t>A 17426-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45005</v>
+        <v>46120</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7165,7 +7165,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37130-2024</t>
+          <t>A 34354-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45539</v>
+        <v>45139</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 68727-2021</t>
+          <t>A 27555-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44529</v>
+        <v>45813</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59915-2024</t>
+          <t>A 33454-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45641</v>
+        <v>45130</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20675-2026</t>
+          <t>A 54279-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46141</v>
+        <v>45616</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>6.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 42712-2023</t>
+          <t>A 38322-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45181</v>
+        <v>45161</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7530,7 +7530,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54128-2025</t>
+          <t>A 58852-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45964</v>
+        <v>45987</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50562-2024</t>
+          <t>A 57445-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45601</v>
+        <v>45629</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20131-2025</t>
+          <t>A 58853-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45772</v>
+        <v>45987</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58853-2025</t>
+          <t>A 59834-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58852-2025</t>
+          <t>A 56496-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45987</v>
+        <v>44480</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.9</v>
+        <v>10.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 5454-2025</t>
+          <t>A 40328-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45692</v>
+        <v>45895</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59834-2025</t>
+          <t>A 61319-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 61319-2025</t>
+          <t>A 27277-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46000</v>
+        <v>45812</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 40722-2024</t>
+          <t>A 23258-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45558</v>
+        <v>45791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 36404-2024</t>
+          <t>A 33296-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45535</v>
+        <v>45840</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 57445-2024</t>
+          <t>A 14802-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45629</v>
+        <v>45014</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 14609-2024</t>
+          <t>A 34500-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45396</v>
+        <v>45847</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 49822-2022</t>
+          <t>A 68727-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44862</v>
+        <v>44529</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 2435-2026</t>
+          <t>A 54128-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46036</v>
+        <v>45964</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 2436-2026</t>
+          <t>A 20675-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46036</v>
+        <v>46141</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4114-2026</t>
+          <t>A 36404-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46044</v>
+        <v>45535</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>7.1</v>
+        <v>4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38322-2023</t>
+          <t>A 20089-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45161</v>
+        <v>45771</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 40743-2024</t>
+          <t>A 33300-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45558</v>
+        <v>45840</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>6.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 6739-2026</t>
+          <t>A 14609-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46056</v>
+        <v>45396</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 8457-2026</t>
+          <t>A 33295-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46065</v>
+        <v>45840</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24605-2026</t>
+          <t>A 33299-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46170</v>
+        <v>45840</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.9</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 49072-2025</t>
+          <t>A 34502-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45937</v>
+        <v>45847</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 9194-2026</t>
+          <t>A 49072-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46070</v>
+        <v>45937</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 9344-2026</t>
+          <t>A 24605-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46070</v>
+        <v>46170</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 10118-2026</t>
+          <t>A 25123-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46075</v>
+        <v>46175</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 12087-2026</t>
+          <t>A 62086-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46086</v>
+        <v>44919</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 25123-2026</t>
+          <t>A 25138-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9445,7 +9445,7 @@
         <v>46175</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 25138-2026</t>
+          <t>A 6957-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46175</v>
+        <v>45343</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20819-2023</t>
+          <t>A 2632-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45058</v>
+        <v>45313</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9664,7 +9664,7 @@
         <v>46181</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 34354-2023</t>
+          <t>A 32175-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45139</v>
+        <v>45511</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 17426-2026</t>
+          <t>A 63626-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46120</v>
+        <v>45275</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 6485-2024</t>
+          <t>A 37130-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45339</v>
+        <v>45539</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 49617-2023</t>
+          <t>A 36722-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9953,10 +9953,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45211</v>
+        <v>45872</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 23682-2024</t>
+          <t>A 5926-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45454</v>
+        <v>45336</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10085,7 +10085,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 39206-2024</t>
+          <t>A 50532-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45548</v>
+        <v>45601</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10158,7 +10158,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 5715-2024</t>
+          <t>A 20819-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10172,10 +10172,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45334</v>
+        <v>45058</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10248,7 +10248,7 @@
         <v>46251</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 34056-2024</t>
+          <t>A 31029-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10318,10 +10318,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45523</v>
+        <v>46213</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10377,7 +10377,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 31029-2026</t>
+          <t>A 43752-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46213</v>
+        <v>45187</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 14547-2022</t>
+          <t>A 34217-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44655</v>
+        <v>44791</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 18791-2023</t>
+          <t>A 36428-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45044</v>
+        <v>46269</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10596,7 +10596,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 28109-2024</t>
+          <t>A 5715-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45476</v>
+        <v>45334</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10669,7 +10669,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 63626-2023</t>
+          <t>A 37948-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45275</v>
+        <v>46280</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 32175-2024</t>
+          <t>A 5454-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10756,10 +10756,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45511</v>
+        <v>45692</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10815,7 +10815,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 34155-2024</t>
+          <t>A 19005-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10829,10 +10829,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45524</v>
+        <v>45045</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 36428-2026</t>
+          <t>A 34056-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46269</v>
+        <v>45523</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10961,7 +10961,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 46708-2023</t>
+          <t>A 59915-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45198</v>
+        <v>45641</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11034,7 +11034,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 62086-2022</t>
+          <t>A 57877-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11048,10 +11048,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44919</v>
+        <v>44899</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11107,7 +11107,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 57878-2022</t>
+          <t>A 13378-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11121,10 +11121,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44899</v>
+        <v>45005</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 14802-2023</t>
+          <t>A 25925-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45014</v>
+        <v>45467</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11253,7 +11253,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 2632-2024</t>
+          <t>A 34155-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11267,10 +11267,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45313</v>
+        <v>45524</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 37948-2026</t>
+          <t>A 18791-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11340,10 +11340,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46280</v>
+        <v>45044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11399,7 +11399,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 33454-2023</t>
+          <t>A 42712-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45130</v>
+        <v>45181</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11472,7 +11472,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 22959-2025</t>
+          <t>A 71890-2021</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11486,10 +11486,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45790</v>
+        <v>44543</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11545,7 +11545,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 14760-2025</t>
+          <t>A 46708-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11559,10 +11559,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45742</v>
+        <v>45198</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11618,7 +11618,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 9937-2025</t>
+          <t>A 40722-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11632,10 +11632,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45718</v>
+        <v>45558</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11691,7 +11691,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 13521-2025</t>
+          <t>A 62369-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11705,10 +11705,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45736</v>
+        <v>45268</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11764,7 +11764,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 13536-2025</t>
+          <t>A 14547-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45736</v>
+        <v>44655</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.1</v>
+        <v>3.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11837,7 +11837,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 24321-2025</t>
+          <t>A 6485-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45797</v>
+        <v>45339</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 34046-2024</t>
+          <t>A 13377-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11924,10 +11924,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45523</v>
+        <v>45005</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11983,7 +11983,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 44754-2024</t>
+          <t>A 61302-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45574</v>
+        <v>45645</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 44417-2024</t>
+          <t>A 50562-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45573</v>
+        <v>45601</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12129,7 +12129,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 27555-2025</t>
+          <t>A 36999-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12143,10 +12143,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45813</v>
+        <v>45155</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12202,7 +12202,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 54279-2024</t>
+          <t>A 22959-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12216,10 +12216,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45616</v>
+        <v>45790</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>6.9</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12275,7 +12275,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33300-2025</t>
+          <t>A 9937-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12289,10 +12289,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45840</v>
+        <v>45718</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>6.4</v>
+        <v>2.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12348,7 +12348,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 33295-2025</t>
+          <t>A 13521-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45840</v>
+        <v>45736</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12421,7 +12421,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33299-2025</t>
+          <t>A 13536-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45840</v>
+        <v>45736</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 34502-2025</t>
+          <t>A 14760-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12508,10 +12508,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45847</v>
+        <v>45742</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12584,7 +12584,7 @@
         <v>45937</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>

--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45597</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>45014</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>45288</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44546</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45336</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45306</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45386</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>46091</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>45460</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>44931</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45693</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45937</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45183</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46167</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>46213</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>45898</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>45343</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45054</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>45058</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>45554</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44566</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44657</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>44792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>45253</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>45548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45454</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>45523</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>45448</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>45476</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>45667</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45334</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>45797</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>44888</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>46036</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>46036</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>44862</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>44899</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>46044</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>45898</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>45594</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>45903</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>45905</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45491</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>46056</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>44924</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>46065</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>46070</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>46070</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>45558</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>46075</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45211</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>45573</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>46086</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>45934</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45938</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>45772</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44872</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>46120</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>45139</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>45813</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>45130</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>45616</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>45161</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45987</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45629</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>45987</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45992</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44480</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45895</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>46000</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45812</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>45791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>45840</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>45014</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>45847</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>44529</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>45964</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>46141</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>45535</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>45771</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>45840</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>45396</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>45840</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45840</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45847</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45937</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>46170</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>46175</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44919</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>46175</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45343</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45313</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>46181</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45511</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>45275</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45539</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45872</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45336</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45601</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45058</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>46251</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>46213</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45187</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44791</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>46269</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45334</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>46280</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45692</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45045</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>45523</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45641</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44899</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45005</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45467</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45524</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45181</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>44543</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45198</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45558</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45268</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>44655</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45339</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45005</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45645</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45601</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45155</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45790</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45718</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45736</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45736</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45742</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45937</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>

--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45597</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>45014</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>45288</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44546</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45336</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45306</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45386</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>46091</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>45460</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>44931</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45693</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45937</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45183</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46167</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>46213</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>45898</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>45343</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45054</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>45058</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>45554</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44566</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44657</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>44792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>45253</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>45548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45454</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>45523</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>45448</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>45476</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>45667</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45334</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>45797</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>44888</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>46036</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>46036</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>44862</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>44899</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>46044</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>45898</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>45594</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>45903</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>45905</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45491</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>46056</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>44924</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>46065</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>46070</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>46070</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>45558</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>46075</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45211</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>45573</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>46086</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>45934</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45938</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>45772</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44872</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>46120</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>45139</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>45813</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>45130</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>45616</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>45161</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45987</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45629</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>45987</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45992</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44480</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45895</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>46000</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45812</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>45791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>45840</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>45014</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>45847</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>44529</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>45964</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>46141</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>45535</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>45771</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>45840</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>45396</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>45840</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45840</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45847</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45937</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>46170</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>46175</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44919</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>46175</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45343</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45313</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>46181</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45511</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>45275</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45539</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45872</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45336</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45601</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45058</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>46251</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>46213</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45187</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44791</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>46269</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45334</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>46280</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45692</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45045</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>45523</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45641</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44899</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45005</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45467</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45524</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45181</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>44543</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45198</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45558</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45268</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>44655</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45339</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45005</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45645</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45601</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45155</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45790</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45718</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45736</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45736</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45742</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45937</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>

--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49930-2024</t>
+          <t>A 74306-2021</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45597</v>
+        <v>44559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -727,45 +727,381 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>16.6</v>
+        <v>14.6</v>
       </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
         <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
       </c>
       <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Dvärglin
+Kösa
+Åkerrödtoppa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 74306-2021 artfynd.xlsx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 74306-2021 karta.png", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 74306-2021 georefererad karta.tif", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 74306-2021 FSC-klagomål.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 74306-2021 FSC-klagomål mail.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 74306-2021 tillsynsbegäran.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 74306-2021 tillsynsbegäran mail.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 14805-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
         <v>6</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönsångare
+Kambräken
+Purpurmylia</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 65099-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45288</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Blockskapania
+Knärot
+Grov fjädermossa
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 49930-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Svart trolldruva
@@ -773,368 +1109,32 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 14805-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>6</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönsångare
-Kambräken
-Purpurmylia</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 74306-2021</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44559</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>4</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Dvärglin
-Kösa
-Åkerrödtoppa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 74306-2021 artfynd.xlsx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 74306-2021 karta.png", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 74306-2021 georefererad karta.tif", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 74306-2021 FSC-klagomål.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 74306-2021 FSC-klagomål mail.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 74306-2021 tillsynsbegäran.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 74306-2021 tillsynsbegäran mail.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 65099-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45288</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Blockskapania
-Knärot
-Grov fjädermossa
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
         <v/>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
         <v>44546</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45336</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1663-2024</t>
+          <t>A 63419-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45306</v>
+        <v>45274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1432,156 +1432,156 @@
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Björktrast
+Rödvingetrast
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 1663-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45306</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Blåbär
 Sälg
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 1663-2024 artfynd.xlsx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 1663-2024 karta.png", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 1663-2024 georefererad karta.tif", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 1663-2024 FSC-klagomål.docx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 1663-2024 FSC-klagomål mail.docx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 1663-2024 tillsynsbegäran.docx", "A 1663-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 1663-2024 tillsynsbegäran mail.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 63419-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45274</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Björktrast
-Rödvingetrast
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13220-2024</t>
+          <t>A 40270-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45386</v>
+        <v>45554</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1644,10 +1644,10 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1655,35 +1655,35 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
         <v>45973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12722-2026</t>
+          <t>A 6986-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46091</v>
+        <v>45343</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1853,10 +1853,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1865,50 +1865,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24618-2024</t>
+          <t>A 12722-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1922,10 +1918,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45460</v>
+        <v>46091</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1938,7 +1934,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>9.5</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1950,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1962,10 +1958,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1978,42 +1974,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 771-2023</t>
+          <t>A 49047-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44931</v>
+        <v>45937</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2043,17 +2043,17 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2083,46 +2083,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5634-2025</t>
+          <t>A 771-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2136,10 +2132,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45693</v>
+        <v>44931</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2148,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2164,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2176,62 +2172,62 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
-        <v/>
-      </c>
-      <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 49047-2025</t>
+          <t>A 13220-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2245,10 +2241,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45937</v>
+        <v>45386</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2261,19 +2257,19 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2288,55 +2284,59 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
+        <v/>
+      </c>
+      <c r="Z17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 5617-2024</t>
+          <t>A 24618-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45334</v>
+        <v>45460</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2390,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2402,50 +2402,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
-        <v/>
-      </c>
-      <c r="Z18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 44233-2023</t>
+          <t>A 20709-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2459,10 +2455,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45183</v>
+        <v>45058</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2475,7 +2471,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2508,10 +2504,10 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
@@ -2519,42 +2515,42 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23921-2026</t>
+          <t>A 5617-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2568,10 +2564,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46167</v>
+        <v>45334</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2584,20 +2580,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -2608,10 +2604,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2620,46 +2616,50 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31028-2026</t>
+          <t>A 23921-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46213</v>
+        <v>46167</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2729,42 +2729,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41056-2025</t>
+          <t>A 44233-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45898</v>
+        <v>45183</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2794,20 +2794,20 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -2818,10 +2818,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2834,42 +2834,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
+        <v/>
+      </c>
+      <c r="Z22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6986-2024</t>
+          <t>A 31028-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2883,10 +2887,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45343</v>
+        <v>46213</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2899,13 +2903,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2935,46 +2939,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20086-2023</t>
+          <t>A 41056-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2988,10 +2992,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45054</v>
+        <v>45898</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3004,19 +3008,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3028,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3040,50 +3044,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20709-2023</t>
+          <t>A 5634-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45058</v>
+        <v>45693</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3146,10 +3146,10 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
@@ -3157,42 +3157,42 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 40270-2024</t>
+          <t>A 20086-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45554</v>
+        <v>45054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3266,35 +3266,35 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
         <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44566</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44657</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34380-2022</t>
+          <t>A 62369-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44792</v>
+        <v>45268</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59309-2023</t>
+          <t>A 57877-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45253</v>
+        <v>44899</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39206-2024</t>
+          <t>A 22750-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45548</v>
+        <v>45448</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23682-2024</t>
+          <t>A 36999-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45454</v>
+        <v>45155</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34046-2024</t>
+          <t>A 19005-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45523</v>
+        <v>45045</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22750-2024</t>
+          <t>A 59309-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45448</v>
+        <v>45253</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 28109-2024</t>
+          <t>A 34217-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45476</v>
+        <v>44791</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1288-2025</t>
+          <t>A 22959-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45667</v>
+        <v>45790</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 5714-2024</t>
+          <t>A 14760-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45334</v>
+        <v>45742</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24321-2025</t>
+          <t>A 9937-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45797</v>
+        <v>45718</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5121,7 +5121,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 55777-2022</t>
+          <t>A 13521-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44888</v>
+        <v>45736</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2435-2026</t>
+          <t>A 13536-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46036</v>
+        <v>45736</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2436-2026</t>
+          <t>A 24321-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46036</v>
+        <v>45797</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 49822-2022</t>
+          <t>A 34046-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44862</v>
+        <v>45523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57878-2022</t>
+          <t>A 41063-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44899</v>
+        <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 4114-2026</t>
+          <t>A 47884-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46044</v>
+        <v>45588</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5559,7 +5559,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 41063-2025</t>
+          <t>A 41881-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45898</v>
+        <v>45903</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 47884-2024</t>
+          <t>A 55777-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45588</v>
+        <v>44888</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49115-2024</t>
+          <t>A 44754-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45594</v>
+        <v>45574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 41881-2025</t>
+          <t>A 42457-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45903</v>
+        <v>45905</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 42457-2025</t>
+          <t>A 44417-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45905</v>
+        <v>45573</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30440-2024</t>
+          <t>A 27555-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45491</v>
+        <v>45813</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6739-2026</t>
+          <t>A 54279-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46056</v>
+        <v>45616</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.8</v>
+        <v>6.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62516-2022</t>
+          <t>A 43752-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44924</v>
+        <v>45187</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 8457-2026</t>
+          <t>A 30440-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46065</v>
+        <v>45491</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9344-2026</t>
+          <t>A 48419-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46070</v>
+        <v>45934</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9194-2026</t>
+          <t>A 49115-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46070</v>
+        <v>45594</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 40743-2024</t>
+          <t>A 33300-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45558</v>
+        <v>45840</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>6.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6435,7 +6435,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10118-2026</t>
+          <t>A 49365-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46075</v>
+        <v>45938</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6508,7 +6508,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49617-2023</t>
+          <t>A 33295-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45211</v>
+        <v>45840</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 44417-2024</t>
+          <t>A 33299-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45573</v>
+        <v>45840</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6654,7 +6654,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 12087-2026</t>
+          <t>A 34502-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46086</v>
+        <v>45847</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.6</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 48419-2025</t>
+          <t>A 71890-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45934</v>
+        <v>44543</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7.7</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 49365-2025</t>
+          <t>A 36722-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45938</v>
+        <v>45872</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20131-2025</t>
+          <t>A 6957-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45772</v>
+        <v>45343</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44754-2024</t>
+          <t>A 51993-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45574</v>
+        <v>44872</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 51993-2022</t>
+          <t>A 13378-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44872</v>
+        <v>45005</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17426-2026</t>
+          <t>A 50532-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46120</v>
+        <v>45601</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7165,7 +7165,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34354-2023</t>
+          <t>A 1288-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45139</v>
+        <v>45667</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 27555-2025</t>
+          <t>A 2435-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45813</v>
+        <v>46036</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 33454-2023</t>
+          <t>A 2436-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45130</v>
+        <v>46036</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 54279-2024</t>
+          <t>A 25925-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45616</v>
+        <v>45467</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.9</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38322-2023</t>
+          <t>A 4114-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45161</v>
+        <v>46044</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7530,7 +7530,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58852-2025</t>
+          <t>A 58853-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7547,7 +7547,7 @@
         <v>45987</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 57445-2024</t>
+          <t>A 58852-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45629</v>
+        <v>45987</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 58853-2025</t>
+          <t>A 59834-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 59834-2025</t>
+          <t>A 61319-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56496-2021</t>
+          <t>A 62516-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44480</v>
+        <v>44924</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>10.3</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 40328-2025</t>
+          <t>A 6739-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45895</v>
+        <v>46056</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 61319-2025</t>
+          <t>A 8457-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46000</v>
+        <v>46065</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 27277-2025</t>
+          <t>A 9194-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45812</v>
+        <v>46070</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23258-2025</t>
+          <t>A 9344-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45791</v>
+        <v>46070</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 33296-2025</t>
+          <t>A 5926-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45840</v>
+        <v>45336</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 14802-2023</t>
+          <t>A 10118-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45014</v>
+        <v>46075</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 34500-2025</t>
+          <t>A 20089-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45847</v>
+        <v>45771</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7.4</v>
+        <v>2.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 68727-2021</t>
+          <t>A 12087-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44529</v>
+        <v>46086</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 54128-2025</t>
+          <t>A 61302-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45964</v>
+        <v>45645</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 20675-2026</t>
+          <t>A 5714-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46141</v>
+        <v>45334</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 36404-2024</t>
+          <t>A 34380-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45535</v>
+        <v>44792</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20089-2025</t>
+          <t>A 13377-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45771</v>
+        <v>45005</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 33300-2025</t>
+          <t>A 37130-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45840</v>
+        <v>45539</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 14609-2024</t>
+          <t>A 59915-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45396</v>
+        <v>45641</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33295-2025</t>
+          <t>A 17426-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45840</v>
+        <v>46120</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 33299-2025</t>
+          <t>A 42712-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45840</v>
+        <v>45181</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 34502-2025</t>
+          <t>A 50562-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45847</v>
+        <v>45601</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 49072-2025</t>
+          <t>A 20131-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45937</v>
+        <v>45772</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 24605-2026</t>
+          <t>A 5454-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46170</v>
+        <v>45692</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 25123-2026</t>
+          <t>A 40722-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46175</v>
+        <v>45558</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 62086-2022</t>
+          <t>A 36404-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44919</v>
+        <v>45535</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 25138-2026</t>
+          <t>A 23258-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46175</v>
+        <v>45791</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 6957-2024</t>
+          <t>A 34500-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45343</v>
+        <v>45847</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 2632-2024</t>
+          <t>A 57445-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45313</v>
+        <v>45629</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>8.199999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 25963-2026</t>
+          <t>A 27277-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46181</v>
+        <v>45812</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 32175-2024</t>
+          <t>A 40328-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45511</v>
+        <v>45895</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 63626-2023</t>
+          <t>A 33296-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45275</v>
+        <v>45840</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 37130-2024</t>
+          <t>A 56496-2021</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45539</v>
+        <v>44480</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>10.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 36722-2025</t>
+          <t>A 68727-2021</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9953,10 +9953,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45872</v>
+        <v>44529</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 5926-2024</t>
+          <t>A 49822-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45336</v>
+        <v>44862</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10085,7 +10085,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 50532-2024</t>
+          <t>A 20675-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45601</v>
+        <v>46141</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10158,7 +10158,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 20819-2023</t>
+          <t>A 54128-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10172,10 +10172,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45058</v>
+        <v>45964</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10231,7 +10231,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 33789-2026</t>
+          <t>A 38322-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46251</v>
+        <v>45161</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10304,7 +10304,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 31029-2026</t>
+          <t>A 40743-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10318,10 +10318,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46213</v>
+        <v>45558</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10377,7 +10377,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 43752-2023</t>
+          <t>A 14609-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45187</v>
+        <v>45396</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>9.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 34217-2022</t>
+          <t>A 20819-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44791</v>
+        <v>45058</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 36428-2026</t>
+          <t>A 24605-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46269</v>
+        <v>46170</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10596,7 +10596,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 5715-2024</t>
+          <t>A 49072-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45334</v>
+        <v>45937</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10669,7 +10669,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 37948-2026</t>
+          <t>A 34354-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46280</v>
+        <v>45139</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10742,7 +10742,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 5454-2025</t>
+          <t>A 25123-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10756,10 +10756,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45692</v>
+        <v>46175</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10815,7 +10815,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 19005-2023</t>
+          <t>A 25138-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10829,10 +10829,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45045</v>
+        <v>46175</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 34056-2024</t>
+          <t>A 6485-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45523</v>
+        <v>45339</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10961,7 +10961,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 59915-2024</t>
+          <t>A 25963-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45641</v>
+        <v>46181</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11034,7 +11034,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 57877-2022</t>
+          <t>A 49617-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11048,10 +11048,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44899</v>
+        <v>45211</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11107,7 +11107,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 13378-2023</t>
+          <t>A 23682-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11121,10 +11121,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45005</v>
+        <v>45454</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 25925-2024</t>
+          <t>A 39206-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45467</v>
+        <v>45548</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11253,7 +11253,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 34155-2024</t>
+          <t>A 5715-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11267,10 +11267,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45524</v>
+        <v>45334</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 18791-2023</t>
+          <t>A 34056-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11340,10 +11340,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45044</v>
+        <v>45523</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11399,7 +11399,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 42712-2023</t>
+          <t>A 14547-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45181</v>
+        <v>44655</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11472,7 +11472,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 71890-2021</t>
+          <t>A 18791-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11486,10 +11486,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44543</v>
+        <v>45044</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11545,7 +11545,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 46708-2023</t>
+          <t>A 28109-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11559,10 +11559,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45198</v>
+        <v>45476</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11618,7 +11618,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 40722-2024</t>
+          <t>A 31029-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11632,10 +11632,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45558</v>
+        <v>46213</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11691,7 +11691,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 62369-2023</t>
+          <t>A 63626-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11705,10 +11705,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45268</v>
+        <v>45275</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11764,7 +11764,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 14547-2022</t>
+          <t>A 32175-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44655</v>
+        <v>45511</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.8</v>
+        <v>0.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11837,7 +11837,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 6485-2024</t>
+          <t>A 34155-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45339</v>
+        <v>45524</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 13377-2023</t>
+          <t>A 46708-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11924,10 +11924,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45005</v>
+        <v>45198</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11983,7 +11983,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 61302-2024</t>
+          <t>A 62086-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45645</v>
+        <v>44919</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 50562-2024</t>
+          <t>A 36428-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45601</v>
+        <v>46269</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12129,7 +12129,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 36999-2023</t>
+          <t>A 57878-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12143,10 +12143,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45155</v>
+        <v>44899</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12202,7 +12202,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 22959-2025</t>
+          <t>A 14802-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12216,10 +12216,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45790</v>
+        <v>45014</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12275,7 +12275,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 9937-2025</t>
+          <t>A 2632-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12289,10 +12289,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45718</v>
+        <v>45313</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12348,7 +12348,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 13521-2025</t>
+          <t>A 33454-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45736</v>
+        <v>45130</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12421,7 +12421,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 13536-2025</t>
+          <t>A 37948-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45736</v>
+        <v>46280</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.1</v>
+        <v>2.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 14760-2025</t>
+          <t>A 33789-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12508,10 +12508,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45742</v>
+        <v>46251</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12584,7 +12584,7 @@
         <v>45937</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>

--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 74306-2021</t>
+          <t>A 49930-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44559</v>
+        <v>45597</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -727,45 +727,269 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.6</v>
+        <v>16.6</v>
       </c>
       <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
       </c>
       <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Svart trolldruva
+Revlummer
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 14805-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
         <v>4</v>
       </c>
-      <c r="U3" t="n">
+      <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönsångare
+Kambräken
+Purpurmylia</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 74306-2021</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44559</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
         <v>4</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Dvärglin
 Kösa
@@ -773,223 +997,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 74306-2021 artfynd.xlsx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 74306-2021 karta.png", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 74306-2021 georefererad karta.tif", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 74306-2021 FSC-klagomål.docx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 74306-2021 FSC-klagomål mail.docx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 74306-2021 tillsynsbegäran.docx", "A 74306-2021")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 74306-2021 tillsynsbegäran mail.docx", "A 74306-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 14805-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 65099-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45288</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>2</v>
       </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="n">
-        <v>6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>6</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönsångare
-Kambräken
-Purpurmylia</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 65099-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45288</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="T6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Blockskapania
 Knärot
@@ -997,144 +1105,36 @@
 Stor revmossa</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 49930-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45597</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Svart trolldruva
-Revlummer
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
         <v/>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
         <v>44546</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45336</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 63419-2023</t>
+          <t>A 1663-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45274</v>
+        <v>45306</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1432,156 +1432,156 @@
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Blåbär
+Sälg
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 1663-2024 artfynd.xlsx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 1663-2024 karta.png", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 1663-2024 georefererad karta.tif", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 1663-2024 FSC-klagomål.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 1663-2024 FSC-klagomål mail.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 1663-2024 tillsynsbegäran.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 1663-2024 tillsynsbegäran mail.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 63419-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45274</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Björktrast
 Rödvingetrast
 Gröngöling</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 63419-2023 artfynd.xlsx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 63419-2023 karta.png", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 63419-2023 georefererad karta.tif", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 63419-2023 FSC-klagomål.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 63419-2023 FSC-klagomål mail.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 63419-2023 tillsynsbegäran.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 63419-2023 tillsynsbegäran mail.docx", "A 63419-2023")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 63419-2023 prioriterade fågelarter.docx", "A 63419-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 1663-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Blåbär
-Sälg
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 1663-2024 artfynd.xlsx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 1663-2024 karta.png", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 1663-2024 georefererad karta.tif", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 1663-2024 FSC-klagomål.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 1663-2024 FSC-klagomål mail.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 1663-2024 tillsynsbegäran.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 1663-2024 tillsynsbegäran mail.docx", "A 1663-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 40270-2024</t>
+          <t>A 13220-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45554</v>
+        <v>45386</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1644,10 +1644,10 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1655,42 +1655,42 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 56035-2025</t>
+          <t>A 24618-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1700,14 +1700,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45973</v>
+        <v>45460</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>15.9</v>
+        <v>9.5</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1732,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1744,62 +1744,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 6986-2024</t>
+          <t>A 56035-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1809,14 +1805,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45343</v>
+        <v>45973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1829,7 +1825,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1841,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1853,58 +1849,62 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 12722-2026</t>
+          <t>A 771-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46091</v>
+        <v>44931</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1958,10 +1958,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1974,46 +1974,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 49047-2025</t>
+          <t>A 5634-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45937</v>
+        <v>45693</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2043,19 +2043,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2070,55 +2070,59 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <v/>
+      </c>
+      <c r="Z15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 771-2023</t>
+          <t>A 12722-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2132,10 +2136,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44931</v>
+        <v>46091</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2148,7 +2152,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2160,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2172,10 +2176,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2188,46 +2192,46 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 771-2023 artfynd.xlsx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 771-2023 karta.png", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 771-2023 georefererad karta.tif", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
+        <v/>
+      </c>
+      <c r="Z16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 771-2023 FSC-klagomål.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 771-2023 FSC-klagomål mail.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 771-2023 tillsynsbegäran.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 771-2023 tillsynsbegäran mail.docx", "A 771-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 771-2023 prioriterade fågelarter.docx", "A 771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13220-2024</t>
+          <t>A 49047-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2241,10 +2245,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45386</v>
+        <v>45937</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2257,19 +2261,19 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2284,59 +2288,55 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
-        <v/>
-      </c>
-      <c r="Z17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24618-2024</t>
+          <t>A 5617-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45460</v>
+        <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>9.5</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2390,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2402,46 +2402,50 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
+        <v/>
+      </c>
+      <c r="Z18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20709-2023</t>
+          <t>A 44233-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2455,10 +2459,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45058</v>
+        <v>45183</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2471,7 +2475,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2504,10 +2508,10 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
@@ -2515,42 +2519,42 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 5617-2024</t>
+          <t>A 6986-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2564,10 +2568,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45334</v>
+        <v>45343</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2580,7 +2584,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2592,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2604,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2620,39 +2624,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
         <v>46167</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 44233-2023</t>
+          <t>A 20086-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45183</v>
+        <v>45054</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2830,7 +2830,7 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
@@ -2838,35 +2838,35 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Z22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
         <v>46213</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>45898</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5634-2025</t>
+          <t>A 20709-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45693</v>
+        <v>45058</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3146,10 +3146,10 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
@@ -3157,42 +3157,42 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20086-2023</t>
+          <t>A 40270-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45054</v>
+        <v>45554</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3266,35 +3266,35 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
         <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44566</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44657</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62369-2023</t>
+          <t>A 34380-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45268</v>
+        <v>44792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57877-2022</t>
+          <t>A 59309-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44899</v>
+        <v>45253</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22750-2024</t>
+          <t>A 39206-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45448</v>
+        <v>45548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 36999-2023</t>
+          <t>A 9937-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45155</v>
+        <v>45718</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19005-2023</t>
+          <t>A 13521-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45045</v>
+        <v>45736</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59309-2023</t>
+          <t>A 13536-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45253</v>
+        <v>45736</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34217-2022</t>
+          <t>A 14760-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44791</v>
+        <v>45742</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22959-2025</t>
+          <t>A 23682-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45790</v>
+        <v>45454</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14760-2025</t>
+          <t>A 34046-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45742</v>
+        <v>45523</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9937-2025</t>
+          <t>A 1288-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45718</v>
+        <v>45667</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5121,7 +5121,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13521-2025</t>
+          <t>A 22750-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45736</v>
+        <v>45448</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13536-2025</t>
+          <t>A 28109-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45736</v>
+        <v>45476</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24321-2025</t>
+          <t>A 5714-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45797</v>
+        <v>45334</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34046-2024</t>
+          <t>A 24321-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45523</v>
+        <v>45797</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 41063-2025</t>
+          <t>A 55777-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45898</v>
+        <v>44888</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47884-2024</t>
+          <t>A 41063-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45588</v>
+        <v>45898</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5559,7 +5559,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 41881-2025</t>
+          <t>A 47884-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45903</v>
+        <v>45588</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 55777-2022</t>
+          <t>A 49822-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44888</v>
+        <v>44862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44754-2024</t>
+          <t>A 57878-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45574</v>
+        <v>44899</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 42457-2025</t>
+          <t>A 41881-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45905</v>
+        <v>45903</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44417-2024</t>
+          <t>A 49115-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45573</v>
+        <v>45594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 27555-2025</t>
+          <t>A 42457-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45813</v>
+        <v>45905</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 54279-2024</t>
+          <t>A 44417-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45616</v>
+        <v>45573</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.9</v>
+        <v>3.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 43752-2023</t>
+          <t>A 44754-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45187</v>
+        <v>45574</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>9.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30440-2024</t>
+          <t>A 27555-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45491</v>
+        <v>45813</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48419-2025</t>
+          <t>A 30440-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45934</v>
+        <v>45491</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.7</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 49115-2024</t>
+          <t>A 54279-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45594</v>
+        <v>45616</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 33300-2025</t>
+          <t>A 62516-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45840</v>
+        <v>44924</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6435,7 +6435,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49365-2025</t>
+          <t>A 2435-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45938</v>
+        <v>46036</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6508,7 +6508,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 33295-2025</t>
+          <t>A 2436-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45840</v>
+        <v>46036</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33299-2025</t>
+          <t>A 40743-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45840</v>
+        <v>45558</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6654,7 +6654,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 34502-2025</t>
+          <t>A 49617-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45847</v>
+        <v>45211</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 71890-2021</t>
+          <t>A 4114-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44543</v>
+        <v>46044</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>7.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36722-2025</t>
+          <t>A 33300-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45872</v>
+        <v>45840</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>6.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6957-2024</t>
+          <t>A 33295-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45343</v>
+        <v>45840</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 51993-2022</t>
+          <t>A 33299-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44872</v>
+        <v>45840</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13378-2023</t>
+          <t>A 48419-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45005</v>
+        <v>45934</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 50532-2024</t>
+          <t>A 49365-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45601</v>
+        <v>45938</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7165,7 +7165,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 1288-2025</t>
+          <t>A 20131-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45667</v>
+        <v>45772</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2435-2026</t>
+          <t>A 34502-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46036</v>
+        <v>45847</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2436-2026</t>
+          <t>A 51993-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46036</v>
+        <v>44872</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 25925-2024</t>
+          <t>A 36722-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45467</v>
+        <v>45872</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4114-2026</t>
+          <t>A 6739-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46044</v>
+        <v>46056</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7.1</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7530,7 +7530,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58853-2025</t>
+          <t>A 50532-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45987</v>
+        <v>45601</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 58852-2025</t>
+          <t>A 34354-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45987</v>
+        <v>45139</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 59834-2025</t>
+          <t>A 8457-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45992</v>
+        <v>46065</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 61319-2025</t>
+          <t>A 33454-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46000</v>
+        <v>45130</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 62516-2022</t>
+          <t>A 9344-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44924</v>
+        <v>46070</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 6739-2026</t>
+          <t>A 9194-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46056</v>
+        <v>46070</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 8457-2026</t>
+          <t>A 38322-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46065</v>
+        <v>45161</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9194-2026</t>
+          <t>A 10118-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46070</v>
+        <v>46075</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 9344-2026</t>
+          <t>A 58852-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46070</v>
+        <v>45987</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 5926-2024</t>
+          <t>A 57445-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45336</v>
+        <v>45629</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 10118-2026</t>
+          <t>A 58853-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46075</v>
+        <v>45987</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 20089-2025</t>
+          <t>A 59834-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45771</v>
+        <v>45992</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 12087-2026</t>
+          <t>A 61319-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46086</v>
+        <v>46000</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.6</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 61302-2024</t>
+          <t>A 12087-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45645</v>
+        <v>46086</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 5714-2024</t>
+          <t>A 14802-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45334</v>
+        <v>45014</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34380-2022</t>
+          <t>A 36404-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44792</v>
+        <v>45535</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 13377-2023</t>
+          <t>A 17426-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45005</v>
+        <v>46120</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 37130-2024</t>
+          <t>A 20089-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45539</v>
+        <v>45771</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 59915-2024</t>
+          <t>A 56496-2021</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45641</v>
+        <v>44480</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>10.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17426-2026</t>
+          <t>A 40328-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46120</v>
+        <v>45895</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 42712-2023</t>
+          <t>A 62086-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45181</v>
+        <v>44919</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 50562-2024</t>
+          <t>A 27277-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45601</v>
+        <v>45812</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 20131-2025</t>
+          <t>A 23258-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45772</v>
+        <v>45791</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 5454-2025</t>
+          <t>A 33296-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45692</v>
+        <v>45840</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 40722-2024</t>
+          <t>A 6957-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45558</v>
+        <v>45343</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 36404-2024</t>
+          <t>A 2632-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45535</v>
+        <v>45313</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 23258-2025</t>
+          <t>A 34500-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45791</v>
+        <v>45847</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 34500-2025</t>
+          <t>A 32175-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45847</v>
+        <v>45511</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>7.4</v>
+        <v>0.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 57445-2024</t>
+          <t>A 63626-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45629</v>
+        <v>45275</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 27277-2025</t>
+          <t>A 68727-2021</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45812</v>
+        <v>44529</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 40328-2025</t>
+          <t>A 54128-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45895</v>
+        <v>45964</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 33296-2025</t>
+          <t>A 37130-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45840</v>
+        <v>45539</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 56496-2021</t>
+          <t>A 20675-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44480</v>
+        <v>46141</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>10.3</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 68727-2021</t>
+          <t>A 5926-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9953,10 +9953,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44529</v>
+        <v>45336</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 49822-2022</t>
+          <t>A 20819-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44862</v>
+        <v>45058</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10085,7 +10085,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20675-2026</t>
+          <t>A 14609-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46141</v>
+        <v>45396</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10158,7 +10158,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 54128-2025</t>
+          <t>A 49072-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10172,10 +10172,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45964</v>
+        <v>45937</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.6</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10231,7 +10231,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 38322-2023</t>
+          <t>A 43752-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45161</v>
+        <v>45187</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10304,7 +10304,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 40743-2024</t>
+          <t>A 24605-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10318,10 +10318,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45558</v>
+        <v>46170</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10377,7 +10377,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 14609-2024</t>
+          <t>A 34217-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45396</v>
+        <v>44791</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 20819-2023</t>
+          <t>A 25123-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45058</v>
+        <v>46175</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 24605-2026</t>
+          <t>A 25138-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10596,7 +10596,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 49072-2025</t>
+          <t>A 25963-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45937</v>
+        <v>46181</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10669,7 +10669,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 34354-2023</t>
+          <t>A 5715-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45139</v>
+        <v>45334</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10742,7 +10742,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 25123-2026</t>
+          <t>A 5454-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10756,10 +10756,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46175</v>
+        <v>45692</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10815,7 +10815,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 25138-2026</t>
+          <t>A 19005-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10829,10 +10829,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46175</v>
+        <v>45045</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 6485-2024</t>
+          <t>A 34056-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45339</v>
+        <v>45523</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10961,7 +10961,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 25963-2026</t>
+          <t>A 59915-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46181</v>
+        <v>45641</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11034,7 +11034,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 49617-2023</t>
+          <t>A 57877-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11048,10 +11048,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45211</v>
+        <v>44899</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11107,7 +11107,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 23682-2024</t>
+          <t>A 13378-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11121,10 +11121,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45454</v>
+        <v>45005</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 39206-2024</t>
+          <t>A 25925-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45548</v>
+        <v>45467</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11253,7 +11253,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 5715-2024</t>
+          <t>A 31029-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11267,10 +11267,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45334</v>
+        <v>46213</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 34056-2024</t>
+          <t>A 34155-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11340,10 +11340,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45523</v>
+        <v>45524</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11399,7 +11399,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 14547-2022</t>
+          <t>A 18791-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44655</v>
+        <v>45044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11472,7 +11472,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 18791-2023</t>
+          <t>A 42712-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11486,10 +11486,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45044</v>
+        <v>45181</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11545,7 +11545,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 28109-2024</t>
+          <t>A 71890-2021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11559,10 +11559,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45476</v>
+        <v>44543</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11618,7 +11618,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 31029-2026</t>
+          <t>A 36428-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11632,10 +11632,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46213</v>
+        <v>46269</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11691,7 +11691,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 63626-2023</t>
+          <t>A 46708-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11705,10 +11705,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45275</v>
+        <v>45198</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11764,7 +11764,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 32175-2024</t>
+          <t>A 40722-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45511</v>
+        <v>45558</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11837,7 +11837,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 34155-2024</t>
+          <t>A 62369-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45524</v>
+        <v>45268</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 46708-2023</t>
+          <t>A 14547-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11924,10 +11924,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45198</v>
+        <v>44655</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11983,7 +11983,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 62086-2022</t>
+          <t>A 37948-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44919</v>
+        <v>46280</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 36428-2026</t>
+          <t>A 6485-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46269</v>
+        <v>45339</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12129,7 +12129,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 57878-2022</t>
+          <t>A 13377-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12143,10 +12143,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44899</v>
+        <v>45005</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12202,7 +12202,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 14802-2023</t>
+          <t>A 61302-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12216,10 +12216,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45014</v>
+        <v>45645</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12275,7 +12275,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 2632-2024</t>
+          <t>A 50562-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12289,10 +12289,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45313</v>
+        <v>45601</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12348,7 +12348,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 33454-2023</t>
+          <t>A 36999-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45130</v>
+        <v>45155</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12421,7 +12421,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 37948-2026</t>
+          <t>A 22959-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46280</v>
+        <v>45790</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12511,7 +12511,7 @@
         <v>46251</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45937</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>

--- a/Översikt ORUST.xlsx
+++ b/Översikt ORUST.xlsx
@@ -601,7 +601,7 @@
         <v>44476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49930-2024</t>
+          <t>A 14805-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45597</v>
+        <v>45014</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>16.6</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" t="n">
         <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -763,9 +763,345 @@
         <v>6</v>
       </c>
       <c r="U3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönsångare
+Kambräken
+Purpurmylia</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="Z3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 74306-2021</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44559</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Dvärglin
+Kösa
+Åkerrödtoppa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 74306-2021 artfynd.xlsx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 74306-2021 karta.png", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 74306-2021 georefererad karta.tif", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 74306-2021 FSC-klagomål.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 74306-2021 FSC-klagomål mail.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 74306-2021 tillsynsbegäran.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 74306-2021 tillsynsbegäran mail.docx", "A 74306-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 65099-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45288</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Blockskapania
+Knärot
+Grov fjädermossa
+Stor revmossa</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 49930-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Svart trolldruva
@@ -773,368 +1109,32 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49930-2024 artfynd.xlsx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49930-2024 karta.png", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49930-2024 georefererad karta.tif", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49930-2024 FSC-klagomål.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49930-2024 FSC-klagomål mail.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49930-2024 tillsynsbegäran.docx", "A 49930-2024")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49930-2024 tillsynsbegäran mail.docx", "A 49930-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 14805-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>6</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönsångare
-Kambräken
-Purpurmylia</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 14805-2023 artfynd.xlsx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 14805-2023 karta.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 14805-2023 georefererad karta.tif", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 14805-2023 karta knärot.png", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 14805-2023 FSC-klagomål.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 14805-2023 FSC-klagomål mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 14805-2023 tillsynsbegäran.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 14805-2023 tillsynsbegäran mail.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/fåglar/A 14805-2023 prioriterade fågelarter.docx", "A 14805-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 74306-2021</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44559</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>4</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Dvärglin
-Kösa
-Åkerrödtoppa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 74306-2021 artfynd.xlsx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 74306-2021 karta.png", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 74306-2021 georefererad karta.tif", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 74306-2021 FSC-klagomål.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 74306-2021 FSC-klagomål mail.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 74306-2021 tillsynsbegäran.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 74306-2021 tillsynsbegäran mail.docx", "A 74306-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 65099-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45288</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Blockskapania
-Knärot
-Grov fjädermossa
-Stor revmossa</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 65099-2023 artfynd.xlsx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 65099-2023 karta.png", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 65099-2023 georefererad karta.tif", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 65099-2023 karta knärot.png", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 65099-2023 FSC-klagomål.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 65099-2023 FSC-klagomål mail.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 65099-2023 tillsynsbegäran.docx", "A 65099-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 65099-2023 tillsynsbegäran mail.docx", "A 65099-2023")</f>
         <v/>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
         <v>44546</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6055-2024</t>
+          <t>A 1663-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45336</v>
+        <v>45306</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>24.1</v>
+        <v>6.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1319,151 +1319,151 @@
         <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Blåbär
+Sälg
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 1663-2024 artfynd.xlsx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 1663-2024 karta.png", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 1663-2024 georefererad karta.tif", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 1663-2024 FSC-klagomål.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 1663-2024 FSC-klagomål mail.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 1663-2024 tillsynsbegäran.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 1663-2024 tillsynsbegäran mail.docx", "A 1663-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 6055-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45336</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ORUST</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)
 Revlummer
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6055-2024 artfynd.xlsx", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6055-2024 karta.png", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6055-2024 georefererad karta.tif", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6055-2024 FSC-klagomål.docx", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6055-2024 FSC-klagomål mail.docx", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6055-2024 tillsynsbegäran.docx", "A 6055-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6055-2024 tillsynsbegäran mail.docx", "A 6055-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 1663-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ORUST</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Blåbär
-Sälg
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 1663-2024 artfynd.xlsx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 1663-2024 karta.png", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 1663-2024 georefererad karta.tif", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 1663-2024 FSC-klagomål.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 1663-2024 FSC-klagomål mail.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 1663-2024 tillsynsbegäran.docx", "A 1663-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 1663-2024 tillsynsbegäran mail.docx", "A 1663-2024")</f>
         <v/>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13220-2024</t>
+          <t>A 40270-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45386</v>
+        <v>45554</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1644,10 +1644,10 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1655,42 +1655,42 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 24618-2024</t>
+          <t>A 5634-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45460</v>
+        <v>45693</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>9.5</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1732,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1744,58 +1744,62 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 56035-2025</t>
+          <t>A 20086-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1805,14 +1809,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45973</v>
+        <v>45054</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1825,7 +1829,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>15.9</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1858,10 +1862,10 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
@@ -1869,35 +1873,35 @@
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
         <v/>
       </c>
     </row>
@@ -1921,7 +1925,7 @@
         <v>44931</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2013,7 +2017,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 5634-2025</t>
+          <t>A 13220-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2027,10 +2031,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45693</v>
+        <v>45386</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2043,7 +2047,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2087,42 +2091,42 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5634-2025 artfynd.xlsx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13220-2024 artfynd.xlsx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5634-2025 karta.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13220-2024 karta.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5634-2025 georefererad karta.tif", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13220-2024 georefererad karta.tif", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="Z15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5634-2025 karta knärot.png", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 13220-2024 karta knärot.png", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5634-2025 FSC-klagomål.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13220-2024 FSC-klagomål.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5634-2025 FSC-klagomål mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13220-2024 FSC-klagomål mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5634-2025 tillsynsbegäran.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13220-2024 tillsynsbegäran.docx", "A 13220-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5634-2025 tillsynsbegäran mail.docx", "A 5634-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13220-2024 tillsynsbegäran mail.docx", "A 13220-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 12722-2026</t>
+          <t>A 6986-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2136,10 +2140,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46091</v>
+        <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2156,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2164,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2176,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2188,50 +2192,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
-        <v/>
-      </c>
-      <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 49047-2025</t>
+          <t>A 24618-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45937</v>
+        <v>45460</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2261,16 +2261,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.2</v>
+        <v>9.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2285,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2301,42 +2301,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 24618-2024 artfynd.xlsx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 24618-2024 karta.png", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 24618-2024 georefererad karta.tif", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 24618-2024 FSC-klagomål.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 24618-2024 FSC-klagomål mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 24618-2024 tillsynsbegäran.docx", "A 24618-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 24618-2024 tillsynsbegäran mail.docx", "A 24618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 5617-2024</t>
+          <t>A 20709-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45334</v>
+        <v>45058</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2399,10 +2399,10 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
@@ -2410,42 +2410,42 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="Z18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 44233-2023</t>
+          <t>A 13243-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45183</v>
+        <v>45002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2475,19 +2475,19 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2502,7 +2502,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2515,46 +2515,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13243-2023 artfynd.xlsx", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13243-2023 karta.png", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
-        <v/>
-      </c>
-      <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13243-2023 georefererad karta.tif", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13243-2023 FSC-klagomål.docx", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13243-2023 FSC-klagomål mail.docx", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13243-2023 tillsynsbegäran.docx", "A 13243-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13243-2023 tillsynsbegäran mail.docx", "A 13243-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6986-2024</t>
+          <t>A 5617-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2568,10 +2564,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45343</v>
+        <v>45334</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2584,7 +2580,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2596,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2608,10 +2604,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2624,42 +2620,46 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 6986-2024 artfynd.xlsx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 5617-2024 artfynd.xlsx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 6986-2024 karta.png", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 5617-2024 karta.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 6986-2024 georefererad karta.tif", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 5617-2024 georefererad karta.tif", "A 5617-2024")</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 5617-2024 karta knärot.png", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 6986-2024 FSC-klagomål.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 5617-2024 FSC-klagomål.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 6986-2024 FSC-klagomål mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 5617-2024 FSC-klagomål mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 6986-2024 tillsynsbegäran.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 5617-2024 tillsynsbegäran.docx", "A 5617-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 6986-2024 tillsynsbegäran mail.docx", "A 6986-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 5617-2024 tillsynsbegäran mail.docx", "A 5617-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23921-2026</t>
+          <t>A 44233-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46167</v>
+        <v>45183</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
@@ -2713,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2729,42 +2729,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 44233-2023 artfynd.xlsx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 44233-2023 karta.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 44233-2023 georefererad karta.tif", "A 44233-2023")</f>
+        <v/>
+      </c>
+      <c r="Z21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 44233-2023 karta knärot.png", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 44233-2023 FSC-klagomål.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 44233-2023 FSC-klagomål mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 44233-2023 tillsynsbegäran.docx", "A 44233-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 44233-2023 tillsynsbegäran mail.docx", "A 44233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20086-2023</t>
+          <t>A 56035-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2774,14 +2778,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45054</v>
+        <v>45973</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2794,7 +2798,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>15.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2827,10 +2831,10 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
@@ -2838,42 +2842,42 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20086-2023 artfynd.xlsx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 56035-2025 artfynd.xlsx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20086-2023 karta.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 56035-2025 karta.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20086-2023 georefererad karta.tif", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 56035-2025 georefererad karta.tif", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="Z22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20086-2023 karta knärot.png", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 56035-2025 karta knärot.png", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20086-2023 FSC-klagomål.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 56035-2025 FSC-klagomål.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20086-2023 FSC-klagomål mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 56035-2025 FSC-klagomål mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20086-2023 tillsynsbegäran.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 56035-2025 tillsynsbegäran.docx", "A 56035-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20086-2023 tillsynsbegäran mail.docx", "A 20086-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 56035-2025 tillsynsbegäran mail.docx", "A 56035-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31028-2026</t>
+          <t>A 12722-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2887,10 +2891,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46213</v>
+        <v>46091</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2903,20 +2907,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -2927,10 +2931,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2943,42 +2947,46 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 12722-2026 artfynd.xlsx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 12722-2026 karta.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 12722-2026 georefererad karta.tif", "A 12722-2026")</f>
+        <v/>
+      </c>
+      <c r="Z23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 12722-2026 karta knärot.png", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 12722-2026 FSC-klagomål.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 12722-2026 FSC-klagomål mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 12722-2026 tillsynsbegäran.docx", "A 12722-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 12722-2026 tillsynsbegäran mail.docx", "A 12722-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41056-2025</t>
+          <t>A 49047-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2992,10 +3000,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45898</v>
+        <v>45937</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3008,17 +3016,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3032,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3048,42 +3056,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 49047-2025 artfynd.xlsx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 49047-2025 karta.png", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 49047-2025 georefererad karta.tif", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 49047-2025 FSC-klagomål.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 49047-2025 FSC-klagomål mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 49047-2025 tillsynsbegäran.docx", "A 49047-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 49047-2025 tillsynsbegäran mail.docx", "A 49047-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20709-2023</t>
+          <t>A 23921-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3097,10 +3105,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45058</v>
+        <v>46167</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3113,19 +3121,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3137,62 +3145,58 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 20709-2023 artfynd.xlsx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 23921-2026 artfynd.xlsx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 20709-2023 karta.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 23921-2026 karta.png", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 20709-2023 georefererad karta.tif", "A 20709-2023")</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 20709-2023 karta knärot.png", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 23921-2026 georefererad karta.tif", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 20709-2023 FSC-klagomål.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 23921-2026 FSC-klagomål.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 20709-2023 FSC-klagomål mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 23921-2026 FSC-klagomål mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 20709-2023 tillsynsbegäran.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 23921-2026 tillsynsbegäran.docx", "A 23921-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 20709-2023 tillsynsbegäran mail.docx", "A 20709-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 23921-2026 tillsynsbegäran mail.docx", "A 23921-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 40270-2024</t>
+          <t>A 31028-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3206,10 +3210,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45554</v>
+        <v>46213</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3222,19 +3226,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3246,10 +3250,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3258,50 +3262,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 40270-2024 artfynd.xlsx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 31028-2026 artfynd.xlsx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 40270-2024 karta.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 31028-2026 karta.png", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 40270-2024 georefererad karta.tif", "A 40270-2024")</f>
-        <v/>
-      </c>
-      <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/knärot/A 40270-2024 karta knärot.png", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 31028-2026 georefererad karta.tif", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 40270-2024 FSC-klagomål.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 31028-2026 FSC-klagomål.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 40270-2024 FSC-klagomål mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 31028-2026 FSC-klagomål mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 40270-2024 tillsynsbegäran.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 31028-2026 tillsynsbegäran.docx", "A 31028-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 40270-2024 tillsynsbegäran mail.docx", "A 40270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 31028-2026 tillsynsbegäran mail.docx", "A 31028-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13243-2023</t>
+          <t>A 41056-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45002</v>
+        <v>45898</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3331,16 +3331,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3371,35 +3371,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 13243-2023 artfynd.xlsx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/artfynd/A 41056-2025 artfynd.xlsx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 13243-2023 karta.png", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor/A 41056-2025 karta.png", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 13243-2023 georefererad karta.tif", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/kartor_geotiff/A 41056-2025 georefererad karta.tif", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 13243-2023 FSC-klagomål.docx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomål/A 41056-2025 FSC-klagomål.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 13243-2023 FSC-klagomål mail.docx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/klagomålsmail/A 41056-2025 FSC-klagomål mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 13243-2023 tillsynsbegäran.docx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsyn/A 41056-2025 tillsynsbegäran.docx", "A 41056-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 13243-2023 tillsynsbegäran mail.docx", "A 13243-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1421/tillsynsmail/A 41056-2025 tillsynsbegäran mail.docx", "A 41056-2025")</f>
         <v/>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
         <v>45425</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 564-2022</t>
+          <t>A 15006-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44566</v>
+        <v>44657</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55791-2022</t>
+          <t>A 564-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44888</v>
+        <v>44566</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 63141-2021</t>
+          <t>A 8286-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44505</v>
+        <v>44610</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3880,7 +3880,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 15006-2022</t>
+          <t>A 73292-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44657</v>
+        <v>44550</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3953,7 +3953,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8286-2022</t>
+          <t>A 19784-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44610</v>
+        <v>44694</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4026,7 +4026,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 73292-2021</t>
+          <t>A 19785-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44550</v>
+        <v>44694</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19784-2022</t>
+          <t>A 55791-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44694</v>
+        <v>44888</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19785-2022</t>
+          <t>A 63141-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44694</v>
+        <v>44505</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4262,7 +4262,7 @@
         <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34380-2022</t>
+          <t>A 6957-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44792</v>
+        <v>45343</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59309-2023</t>
+          <t>A 51993-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45253</v>
+        <v>44872</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39206-2024</t>
+          <t>A 62369-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45548</v>
+        <v>45268</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9937-2025</t>
+          <t>A 13378-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45718</v>
+        <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13521-2025</t>
+          <t>A 25925-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45736</v>
+        <v>45467</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13536-2025</t>
+          <t>A 63626-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45736</v>
+        <v>45275</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.1</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14760-2025</t>
+          <t>A 38322-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45742</v>
+        <v>45161</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 23682-2024</t>
+          <t>A 32175-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45454</v>
+        <v>45511</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.1</v>
+        <v>0.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34046-2024</t>
+          <t>A 40743-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45523</v>
+        <v>45558</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1288-2025</t>
+          <t>A 34155-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45667</v>
+        <v>45524</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5121,7 +5121,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22750-2024</t>
+          <t>A 34217-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45448</v>
+        <v>44791</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28109-2024</t>
+          <t>A 57877-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45476</v>
+        <v>44899</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5714-2024</t>
+          <t>A 46708-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45334</v>
+        <v>45198</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24321-2025</t>
+          <t>A 22750-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45797</v>
+        <v>45448</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 55777-2022</t>
+          <t>A 62086-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44888</v>
+        <v>44919</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 41063-2025</t>
+          <t>A 36999-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45898</v>
+        <v>45155</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5559,7 +5559,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 47884-2024</t>
+          <t>A 57878-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45588</v>
+        <v>44899</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 49822-2022</t>
+          <t>A 62516-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44862</v>
+        <v>44924</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57878-2022</t>
+          <t>A 20819-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44899</v>
+        <v>45058</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 41881-2025</t>
+          <t>A 14802-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45903</v>
+        <v>45014</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 49115-2024</t>
+          <t>A 19005-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45594</v>
+        <v>45045</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 42457-2025</t>
+          <t>A 59309-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45905</v>
+        <v>45253</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44417-2024</t>
+          <t>A 2632-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45573</v>
+        <v>45313</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44754-2024</t>
+          <t>A 34354-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45574</v>
+        <v>45139</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27555-2025</t>
+          <t>A 5926-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45813</v>
+        <v>45336</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30440-2024</t>
+          <t>A 33454-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45491</v>
+        <v>45130</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 54279-2024</t>
+          <t>A 20089-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45616</v>
+        <v>45771</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.9</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62516-2022</t>
+          <t>A 61302-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44924</v>
+        <v>45645</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6435,7 +6435,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2435-2026</t>
+          <t>A 6485-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46036</v>
+        <v>45339</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6508,7 +6508,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2436-2026</t>
+          <t>A 5714-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46036</v>
+        <v>45334</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 40743-2024</t>
+          <t>A 34380-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45558</v>
+        <v>44792</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6671,7 +6671,7 @@
         <v>45211</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4114-2026</t>
+          <t>A 22959-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46044</v>
+        <v>45790</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7.1</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 33300-2025</t>
+          <t>A 13377-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45840</v>
+        <v>45005</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 33295-2025</t>
+          <t>A 37130-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45840</v>
+        <v>45539</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33299-2025</t>
+          <t>A 14760-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45840</v>
+        <v>45742</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48419-2025</t>
+          <t>A 9937-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45934</v>
+        <v>45718</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>7.7</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 49365-2025</t>
+          <t>A 13521-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45938</v>
+        <v>45736</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7165,7 +7165,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 20131-2025</t>
+          <t>A 13536-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45772</v>
+        <v>45736</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 34502-2025</t>
+          <t>A 23682-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45847</v>
+        <v>45454</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 51993-2022</t>
+          <t>A 59915-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44872</v>
+        <v>45641</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 36722-2025</t>
+          <t>A 39206-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45872</v>
+        <v>45548</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 6739-2026</t>
+          <t>A 24321-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46056</v>
+        <v>45797</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7530,7 +7530,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50532-2024</t>
+          <t>A 34046-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45601</v>
+        <v>45523</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34354-2023</t>
+          <t>A 55777-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45139</v>
+        <v>44888</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 8457-2026</t>
+          <t>A 5715-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46065</v>
+        <v>45334</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33454-2023</t>
+          <t>A 42712-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45130</v>
+        <v>45181</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 9344-2026</t>
+          <t>A 50562-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46070</v>
+        <v>45601</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 9194-2026</t>
+          <t>A 44754-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46070</v>
+        <v>45574</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 38322-2023</t>
+          <t>A 44417-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45161</v>
+        <v>45573</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10118-2026</t>
+          <t>A 20131-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46075</v>
+        <v>45772</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58852-2025</t>
+          <t>A 34056-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45987</v>
+        <v>45523</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 57445-2024</t>
+          <t>A 27555-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45629</v>
+        <v>45813</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 58853-2025</t>
+          <t>A 5454-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45987</v>
+        <v>45692</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 59834-2025</t>
+          <t>A 54279-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45992</v>
+        <v>45616</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.1</v>
+        <v>6.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61319-2025</t>
+          <t>A 43752-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46000</v>
+        <v>45187</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 12087-2026</t>
+          <t>A 30440-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46086</v>
+        <v>45491</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.6</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 14802-2023</t>
+          <t>A 40722-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45014</v>
+        <v>45558</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8642,7 +8642,7 @@
         <v>45535</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17426-2026</t>
+          <t>A 49115-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46120</v>
+        <v>45594</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20089-2025</t>
+          <t>A 57445-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45771</v>
+        <v>45629</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56496-2021</t>
+          <t>A 33300-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44480</v>
+        <v>45840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>10.3</v>
+        <v>6.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40328-2025</t>
+          <t>A 14547-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45895</v>
+        <v>44655</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 62086-2022</t>
+          <t>A 33295-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44919</v>
+        <v>45840</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 27277-2025</t>
+          <t>A 33299-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45812</v>
+        <v>45840</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 23258-2025</t>
+          <t>A 18791-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45791</v>
+        <v>45044</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 33296-2025</t>
+          <t>A 28109-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45840</v>
+        <v>45476</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 6957-2024</t>
+          <t>A 34502-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45343</v>
+        <v>45847</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 2632-2024</t>
+          <t>A 49822-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45313</v>
+        <v>44862</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>8.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 34500-2025</t>
+          <t>A 36722-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45847</v>
+        <v>45872</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 32175-2024</t>
+          <t>A 71890-2021</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45511</v>
+        <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 63626-2023</t>
+          <t>A 48419-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45275</v>
+        <v>45934</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.4</v>
+        <v>7.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 68727-2021</t>
+          <t>A 49365-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44529</v>
+        <v>45938</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 54128-2025</t>
+          <t>A 50532-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45964</v>
+        <v>45601</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 37130-2024</t>
+          <t>A 1288-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45539</v>
+        <v>45667</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20675-2026</t>
+          <t>A 41063-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46141</v>
+        <v>45898</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 5926-2024</t>
+          <t>A 47884-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9953,10 +9953,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45336</v>
+        <v>45588</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 20819-2023</t>
+          <t>A 41881-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45058</v>
+        <v>45903</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10085,7 +10085,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 14609-2024</t>
+          <t>A 42457-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45396</v>
+        <v>45905</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10158,7 +10158,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 49072-2025</t>
+          <t>A 58853-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10172,10 +10172,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45937</v>
+        <v>45987</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10231,7 +10231,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 43752-2023</t>
+          <t>A 58852-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45187</v>
+        <v>45987</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>9.300000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10304,7 +10304,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 24605-2026</t>
+          <t>A 59834-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10318,10 +10318,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46170</v>
+        <v>45992</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10377,7 +10377,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 34217-2022</t>
+          <t>A 61319-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44791</v>
+        <v>46000</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 25123-2026</t>
+          <t>A 2435-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46175</v>
+        <v>46036</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 25138-2026</t>
+          <t>A 2436-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46175</v>
+        <v>46036</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10596,7 +10596,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 25963-2026</t>
+          <t>A 4114-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46181</v>
+        <v>46044</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.8</v>
+        <v>7.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10669,7 +10669,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 5715-2024</t>
+          <t>A 6739-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45334</v>
+        <v>46056</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10742,7 +10742,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 5454-2025</t>
+          <t>A 8457-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10756,10 +10756,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45692</v>
+        <v>46065</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10815,7 +10815,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 19005-2023</t>
+          <t>A 9194-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10829,10 +10829,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45045</v>
+        <v>46070</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 34056-2024</t>
+          <t>A 9344-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45523</v>
+        <v>46070</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10961,7 +10961,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 59915-2024</t>
+          <t>A 10118-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45641</v>
+        <v>46075</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11034,7 +11034,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 57877-2022</t>
+          <t>A 12087-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11048,10 +11048,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44899</v>
+        <v>46086</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11107,7 +11107,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 13378-2023</t>
+          <t>A 17426-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11121,10 +11121,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45005</v>
+        <v>46120</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 25925-2024</t>
+          <t>A 23258-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45467</v>
+        <v>45791</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11253,7 +11253,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 31029-2026</t>
+          <t>A 34500-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11267,10 +11267,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46213</v>
+        <v>45847</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 34155-2024</t>
+          <t>A 27277-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11340,10 +11340,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45524</v>
+        <v>45812</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11399,7 +11399,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 18791-2023</t>
+          <t>A 40328-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45044</v>
+        <v>45895</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11472,7 +11472,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 42712-2023</t>
+          <t>A 33296-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11486,10 +11486,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45181</v>
+        <v>45840</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11545,7 +11545,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 71890-2021</t>
+          <t>A 56496-2021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11559,10 +11559,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44543</v>
+        <v>44480</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.4</v>
+        <v>10.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11618,7 +11618,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 36428-2026</t>
+          <t>A 68727-2021</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11632,10 +11632,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46269</v>
+        <v>44529</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.4</v>
+        <v>2.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11691,7 +11691,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 46708-2023</t>
+          <t>A 20675-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11705,10 +11705,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45198</v>
+        <v>46141</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11764,7 +11764,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 40722-2024</t>
+          <t>A 54128-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45558</v>
+        <v>45964</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11837,7 +11837,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 62369-2023</t>
+          <t>A 14609-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45268</v>
+        <v>45396</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c